--- a/Versão5/ABNT/Ontologia_15965_2Q.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_2Q.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158AE65F-04D4-4F04-BE40-55F027F1694C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02EE61AF-2E26-48A3-8123-808E881546FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13583" uniqueCount="1329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13583" uniqueCount="1339">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -4078,13 +4078,43 @@
   </si>
   <si>
     <t>Código.ABNT</t>
+  </si>
+  <si>
+    <t>2Q.06.02.06.02.aa</t>
+  </si>
+  <si>
+    <t>2Q.42.aa</t>
+  </si>
+  <si>
+    <t>2Q.42.bb</t>
+  </si>
+  <si>
+    <t>2Q.58.18.10</t>
+  </si>
+  <si>
+    <t>2Q.58.18.14</t>
+  </si>
+  <si>
+    <t>2Q.62.34.30</t>
+  </si>
+  <si>
+    <t>2Q.62.34.34</t>
+  </si>
+  <si>
+    <t>2Q.62.34.38</t>
+  </si>
+  <si>
+    <t>2Q.62.34.42</t>
+  </si>
+  <si>
+    <t>2Q.62.38</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <color theme="1"/>
@@ -4163,6 +4193,12 @@
       <b/>
       <sz val="5"/>
       <color rgb="FF000000"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial Nova Cond Light"/>
       <family val="2"/>
     </font>
@@ -4415,7 +4451,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4604,12 +4640,33 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{FD276809-E4C5-4861-8007-253055573830}"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -5165,7 +5222,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46139.32715740741</v>
+        <v>46146.338399305554</v>
       </c>
       <c r="C18" s="51" t="s">
         <v>1315</v>
@@ -5465,7 +5522,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="AA1:AA2">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5675,7 +5732,7 @@
     <col min="6" max="6" width="5" style="28" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.796875" style="28" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5" style="28" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.5" style="28" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5" style="28" customWidth="1"/>
     <col min="10" max="10" width="7" style="28" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="49.19921875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.796875" style="28" customWidth="1"/>
@@ -7751,7 +7808,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="35" t="s">
-        <v>669</v>
+        <v>1329</v>
       </c>
       <c r="C30" s="34" t="s">
         <v>1328</v>
@@ -14496,7 +14553,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="35" t="s">
-        <v>763</v>
+        <v>1330</v>
       </c>
       <c r="C125" s="34" t="s">
         <v>1328</v>
@@ -14567,7 +14624,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="35" t="s">
-        <v>763</v>
+        <v>1331</v>
       </c>
       <c r="C126" s="34" t="s">
         <v>1328</v>
@@ -35511,8 +35568,8 @@
       <c r="A421" s="29">
         <v>421</v>
       </c>
-      <c r="B421" s="35" t="s">
-        <v>1057</v>
+      <c r="B421" s="64" t="s">
+        <v>1332</v>
       </c>
       <c r="C421" s="34" t="s">
         <v>1328</v>
@@ -35582,8 +35639,8 @@
       <c r="A422" s="29">
         <v>422</v>
       </c>
-      <c r="B422" s="35" t="s">
-        <v>1057</v>
+      <c r="B422" s="64" t="s">
+        <v>1333</v>
       </c>
       <c r="C422" s="34" t="s">
         <v>1328</v>
@@ -39274,7 +39331,7 @@
       <c r="A474" s="29">
         <v>474</v>
       </c>
-      <c r="B474" s="35" t="s">
+      <c r="B474" s="64" t="s">
         <v>1109</v>
       </c>
       <c r="C474" s="34" t="s">
@@ -39345,8 +39402,8 @@
       <c r="A475" s="29">
         <v>475</v>
       </c>
-      <c r="B475" s="35" t="s">
-        <v>1102</v>
+      <c r="B475" s="64" t="s">
+        <v>1334</v>
       </c>
       <c r="C475" s="34" t="s">
         <v>1328</v>
@@ -39416,8 +39473,8 @@
       <c r="A476" s="29">
         <v>476</v>
       </c>
-      <c r="B476" s="35" t="s">
-        <v>1102</v>
+      <c r="B476" s="64" t="s">
+        <v>1335</v>
       </c>
       <c r="C476" s="34" t="s">
         <v>1328</v>
@@ -39487,8 +39544,8 @@
       <c r="A477" s="29">
         <v>477</v>
       </c>
-      <c r="B477" s="35" t="s">
-        <v>1102</v>
+      <c r="B477" s="64" t="s">
+        <v>1336</v>
       </c>
       <c r="C477" s="34" t="s">
         <v>1328</v>
@@ -39558,8 +39615,8 @@
       <c r="A478" s="29">
         <v>478</v>
       </c>
-      <c r="B478" s="35" t="s">
-        <v>1102</v>
+      <c r="B478" s="64" t="s">
+        <v>1337</v>
       </c>
       <c r="C478" s="34" t="s">
         <v>1328</v>
@@ -41546,8 +41603,8 @@
       <c r="A506" s="29">
         <v>506</v>
       </c>
-      <c r="B506" s="35" t="s">
-        <v>1102</v>
+      <c r="B506" s="64" t="s">
+        <v>1338</v>
       </c>
       <c r="C506" s="34" t="s">
         <v>1328</v>
@@ -49000,9 +49057,12 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="R1:W1048576">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Versão5/ABNT/Ontologia_15965_2Q.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_2Q.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06890FD-FE2B-4BB6-A3DC-29F20D2803CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -5341,14 +5341,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{436D4E89-FEA8-43EC-BA63-D5F572124283}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -5359,7 +5359,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>625</v>
       </c>
@@ -5370,7 +5370,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>626</v>
       </c>
@@ -5381,7 +5381,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -5392,7 +5392,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -5404,7 +5404,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -5416,7 +5416,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -5427,7 +5427,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="40" t="s">
         <v>9</v>
       </c>
@@ -5438,7 +5438,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>627</v>
       </c>
@@ -5449,7 +5449,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>629</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>630</v>
       </c>
@@ -5471,7 +5471,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -5482,7 +5482,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>631</v>
       </c>
@@ -5493,7 +5493,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>632</v>
       </c>
@@ -5504,7 +5504,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>633</v>
       </c>
@@ -5515,7 +5515,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>634</v>
       </c>
@@ -5526,7 +5526,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -5537,19 +5537,19 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>635</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46148.623518981483</v>
+        <v>46157.683236921293</v>
       </c>
       <c r="C18" s="43" t="s">
         <v>1311</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>1320</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="40" t="s">
         <v>1314</v>
       </c>
@@ -5572,7 +5572,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="40" t="s">
         <v>1321</v>
       </c>
@@ -5584,7 +5584,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>624</v>
       </c>
@@ -5595,7 +5595,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>636</v>
       </c>
@@ -5606,7 +5606,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>641</v>
       </c>
@@ -5617,7 +5617,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>643</v>
       </c>
@@ -5628,7 +5628,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="44" customFormat="1" ht="8.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" s="44" customFormat="1" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="40" t="s">
         <v>1306</v>
       </c>
@@ -5648,25 +5648,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1778FB64-75F3-4573-A6F2-8AC25FEAA02B}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA19"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="6.83203125" style="35" customWidth="1"/>
+    <col min="1" max="1" width="2.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="6.796875" style="35" customWidth="1"/>
     <col min="6" max="6" width="10" style="35" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.6640625" style="35" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.69921875" style="35" bestFit="1" customWidth="1"/>
     <col min="12" max="15" width="7" customWidth="1"/>
-    <col min="16" max="16" width="42.6640625" customWidth="1"/>
-    <col min="17" max="17" width="44.33203125" customWidth="1"/>
-    <col min="18" max="18" width="5.83203125" customWidth="1"/>
+    <col min="16" max="16" width="42.69921875" customWidth="1"/>
+    <col min="17" max="17" width="44.296875" customWidth="1"/>
+    <col min="18" max="18" width="5.796875" customWidth="1"/>
     <col min="19" max="19" width="7" customWidth="1"/>
-    <col min="20" max="20" width="6.6640625" customWidth="1"/>
-    <col min="21" max="21" width="5.83203125" customWidth="1"/>
-    <col min="22" max="22" width="8.1640625" customWidth="1"/>
-    <col min="23" max="23" width="8.6640625" customWidth="1"/>
-    <col min="27" max="27" width="37.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.69921875" customWidth="1"/>
+    <col min="21" max="21" width="5.796875" customWidth="1"/>
+    <col min="22" max="22" width="8.19921875" customWidth="1"/>
+    <col min="23" max="23" width="8.69921875" customWidth="1"/>
+    <col min="27" max="27" width="37.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="57.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="30.9" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>1251</v>
       </c>
@@ -5749,7 +5749,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="57">
         <v>2</v>
       </c>
@@ -5840,7 +5840,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="57">
         <v>3</v>
       </c>
@@ -5931,7 +5931,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="57">
         <v>4</v>
       </c>
@@ -6022,7 +6022,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="57">
         <v>5</v>
       </c>
@@ -6113,7 +6113,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="57">
         <v>6</v>
       </c>
@@ -6204,7 +6204,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="57">
         <v>7</v>
       </c>
@@ -6295,7 +6295,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="57">
         <v>8</v>
       </c>
@@ -6386,7 +6386,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="57">
         <v>9</v>
       </c>
@@ -6477,7 +6477,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="57">
         <v>10</v>
       </c>
@@ -6568,7 +6568,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="57">
         <v>11</v>
       </c>
@@ -6659,7 +6659,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="57">
         <v>12</v>
       </c>
@@ -6750,7 +6750,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="57">
         <v>13</v>
       </c>
@@ -6841,7 +6841,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="57">
         <v>14</v>
       </c>
@@ -6932,7 +6932,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="57">
         <v>15</v>
       </c>
@@ -7023,7 +7023,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="57">
         <v>16</v>
       </c>
@@ -7114,7 +7114,7 @@
         <v>1396</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="57">
         <v>17</v>
       </c>
@@ -7205,7 +7205,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="57">
         <v>18</v>
       </c>
@@ -7296,7 +7296,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="57">
         <v>19</v>
       </c>
@@ -7415,13 +7415,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{649E5DE9-BD63-4EDF-814C-ADC7DFAABB6E}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>1252</v>
       </c>
@@ -7486,7 +7486,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="16">
         <v>2</v>
       </c>
@@ -7563,13 +7563,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FBF1699-AA28-4D60-8669-5674605C36B3}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="3" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.69921875" customWidth="1"/>
+    <col min="2" max="3" width="14.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="19">
         <v>1</v>
       </c>
@@ -7580,7 +7580,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>2</v>
       </c>
@@ -7600,31 +7600,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B79BA5E7-BFBD-4AC9-B36C-B9776AA17B75}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y610"/>
-  <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.296875" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.296875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="2" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" style="22" customWidth="1"/>
-    <col min="4" max="4" width="10.1640625" style="22" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.6640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.69921875" style="22" customWidth="1"/>
+    <col min="4" max="4" width="10.19921875" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.69921875" style="22" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5" style="22" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.1640625" style="22" customWidth="1"/>
+    <col min="7" max="7" width="9.19921875" style="22" customWidth="1"/>
     <col min="8" max="8" width="5" style="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.83203125" style="22" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.796875" style="22" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5" style="22" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" style="22" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.83203125" style="22" customWidth="1"/>
-    <col min="13" max="13" width="28.6640625" style="22" customWidth="1"/>
+    <col min="12" max="12" width="5.796875" style="22" customWidth="1"/>
+    <col min="13" max="13" width="28.69921875" style="22" customWidth="1"/>
     <col min="14" max="14" width="7" style="22" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="49.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.83203125" style="22" customWidth="1"/>
-    <col min="17" max="17" width="5.33203125" style="22" customWidth="1"/>
-    <col min="18" max="19" width="5.83203125" style="22" customWidth="1"/>
-    <col min="20" max="25" width="4.6640625" style="22" customWidth="1"/>
-    <col min="26" max="16384" width="11.33203125" style="2"/>
+    <col min="15" max="15" width="49.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.796875" style="22" customWidth="1"/>
+    <col min="17" max="17" width="5.296875" style="22" customWidth="1"/>
+    <col min="18" max="19" width="5.796875" style="22" customWidth="1"/>
+    <col min="20" max="25" width="4.69921875" style="22" customWidth="1"/>
+    <col min="26" max="16384" width="11.296875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>637</v>
       </c>
@@ -7701,7 +7701,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="45">
         <v>2</v>
       </c>
@@ -7778,7 +7778,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="45">
         <v>3</v>
       </c>
@@ -7855,7 +7855,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="45">
         <v>4</v>
       </c>
@@ -7932,7 +7932,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="45">
         <v>5</v>
       </c>
@@ -8009,7 +8009,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="45">
         <v>6</v>
       </c>
@@ -8086,7 +8086,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="45">
         <v>7</v>
       </c>
@@ -8163,7 +8163,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="45">
         <v>8</v>
       </c>
@@ -8240,7 +8240,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="45">
         <v>9</v>
       </c>
@@ -8317,7 +8317,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="45">
         <v>10</v>
       </c>
@@ -8394,7 +8394,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="45">
         <v>11</v>
       </c>
@@ -8471,7 +8471,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="45">
         <v>12</v>
       </c>
@@ -8548,7 +8548,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="45">
         <v>13</v>
       </c>
@@ -8625,7 +8625,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="45">
         <v>14</v>
       </c>
@@ -8702,7 +8702,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="45">
         <v>15</v>
       </c>
@@ -8779,7 +8779,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="45">
         <v>16</v>
       </c>
@@ -8856,7 +8856,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="45">
         <v>17</v>
       </c>
@@ -8933,7 +8933,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="45">
         <v>18</v>
       </c>
@@ -9010,7 +9010,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="45">
         <v>19</v>
       </c>
@@ -9087,7 +9087,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="45">
         <v>20</v>
       </c>
@@ -9164,7 +9164,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="45">
         <v>21</v>
       </c>
@@ -9241,7 +9241,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="45">
         <v>22</v>
       </c>
@@ -9318,7 +9318,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="45">
         <v>23</v>
       </c>
@@ -9395,7 +9395,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="45">
         <v>24</v>
       </c>
@@ -9472,7 +9472,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="45">
         <v>25</v>
       </c>
@@ -9549,7 +9549,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="45">
         <v>26</v>
       </c>
@@ -9626,7 +9626,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="45">
         <v>27</v>
       </c>
@@ -9703,7 +9703,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="45">
         <v>28</v>
       </c>
@@ -9780,7 +9780,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="45">
         <v>29</v>
       </c>
@@ -9857,7 +9857,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="45">
         <v>30</v>
       </c>
@@ -9934,7 +9934,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="45">
         <v>31</v>
       </c>
@@ -10011,7 +10011,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="45">
         <v>32</v>
       </c>
@@ -10088,7 +10088,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="45">
         <v>33</v>
       </c>
@@ -10165,7 +10165,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="45">
         <v>34</v>
       </c>
@@ -10242,7 +10242,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="45">
         <v>35</v>
       </c>
@@ -10319,7 +10319,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="45">
         <v>36</v>
       </c>
@@ -10396,7 +10396,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="45">
         <v>37</v>
       </c>
@@ -10473,7 +10473,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="45">
         <v>38</v>
       </c>
@@ -10550,7 +10550,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="45">
         <v>39</v>
       </c>
@@ -10627,7 +10627,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="45">
         <v>40</v>
       </c>
@@ -10704,7 +10704,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="45">
         <v>41</v>
       </c>
@@ -10781,7 +10781,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="45">
         <v>42</v>
       </c>
@@ -10858,7 +10858,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="45">
         <v>43</v>
       </c>
@@ -10935,7 +10935,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="45">
         <v>44</v>
       </c>
@@ -11012,7 +11012,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="45">
         <v>45</v>
       </c>
@@ -11089,7 +11089,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="45">
         <v>46</v>
       </c>
@@ -11166,7 +11166,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="45">
         <v>47</v>
       </c>
@@ -11243,7 +11243,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="45">
         <v>48</v>
       </c>
@@ -11320,7 +11320,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="45">
         <v>49</v>
       </c>
@@ -11397,7 +11397,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="45">
         <v>50</v>
       </c>
@@ -11474,7 +11474,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="45">
         <v>51</v>
       </c>
@@ -11551,7 +11551,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="45">
         <v>52</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="45">
         <v>53</v>
       </c>
@@ -11705,7 +11705,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="45">
         <v>54</v>
       </c>
@@ -11782,7 +11782,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="45">
         <v>55</v>
       </c>
@@ -11859,7 +11859,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="45">
         <v>56</v>
       </c>
@@ -11936,7 +11936,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="45">
         <v>57</v>
       </c>
@@ -12013,7 +12013,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="45">
         <v>58</v>
       </c>
@@ -12090,7 +12090,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="45">
         <v>59</v>
       </c>
@@ -12167,7 +12167,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="45">
         <v>60</v>
       </c>
@@ -12244,7 +12244,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="45">
         <v>61</v>
       </c>
@@ -12321,7 +12321,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="45">
         <v>62</v>
       </c>
@@ -12398,7 +12398,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="45">
         <v>63</v>
       </c>
@@ -12475,7 +12475,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="45">
         <v>64</v>
       </c>
@@ -12552,7 +12552,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="45">
         <v>65</v>
       </c>
@@ -12629,7 +12629,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="45">
         <v>66</v>
       </c>
@@ -12706,7 +12706,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="45">
         <v>67</v>
       </c>
@@ -12783,7 +12783,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="45">
         <v>68</v>
       </c>
@@ -12860,7 +12860,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="45">
         <v>69</v>
       </c>
@@ -12937,7 +12937,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="45">
         <v>70</v>
       </c>
@@ -13014,7 +13014,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="45">
         <v>71</v>
       </c>
@@ -13091,7 +13091,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="45">
         <v>72</v>
       </c>
@@ -13168,7 +13168,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="45">
         <v>73</v>
       </c>
@@ -13245,7 +13245,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="45">
         <v>74</v>
       </c>
@@ -13322,7 +13322,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="45">
         <v>75</v>
       </c>
@@ -13399,7 +13399,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="45">
         <v>76</v>
       </c>
@@ -13476,7 +13476,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="45">
         <v>77</v>
       </c>
@@ -13553,7 +13553,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="45">
         <v>78</v>
       </c>
@@ -13630,7 +13630,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="45">
         <v>79</v>
       </c>
@@ -13707,7 +13707,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="45">
         <v>80</v>
       </c>
@@ -13784,7 +13784,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="45">
         <v>81</v>
       </c>
@@ -13861,7 +13861,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="45">
         <v>82</v>
       </c>
@@ -13938,7 +13938,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="45">
         <v>83</v>
       </c>
@@ -14015,7 +14015,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="45">
         <v>84</v>
       </c>
@@ -14092,7 +14092,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="45">
         <v>85</v>
       </c>
@@ -14169,7 +14169,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="45">
         <v>86</v>
       </c>
@@ -14246,7 +14246,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="45">
         <v>87</v>
       </c>
@@ -14323,7 +14323,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="45">
         <v>88</v>
       </c>
@@ -14400,7 +14400,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="45">
         <v>89</v>
       </c>
@@ -14477,7 +14477,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="45">
         <v>90</v>
       </c>
@@ -14554,7 +14554,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="45">
         <v>91</v>
       </c>
@@ -14631,7 +14631,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="45">
         <v>92</v>
       </c>
@@ -14708,7 +14708,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="45">
         <v>93</v>
       </c>
@@ -14785,7 +14785,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="45">
         <v>94</v>
       </c>
@@ -14862,7 +14862,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="45">
         <v>95</v>
       </c>
@@ -14939,7 +14939,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="45">
         <v>96</v>
       </c>
@@ -15016,7 +15016,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="45">
         <v>97</v>
       </c>
@@ -15093,7 +15093,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="45">
         <v>98</v>
       </c>
@@ -15170,7 +15170,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="45">
         <v>99</v>
       </c>
@@ -15247,7 +15247,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="45">
         <v>100</v>
       </c>
@@ -15324,7 +15324,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="45">
         <v>101</v>
       </c>
@@ -15401,7 +15401,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="45">
         <v>102</v>
       </c>
@@ -15478,7 +15478,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="45">
         <v>103</v>
       </c>
@@ -15555,7 +15555,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="45">
         <v>104</v>
       </c>
@@ -15632,7 +15632,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="45">
         <v>105</v>
       </c>
@@ -15709,7 +15709,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="45">
         <v>106</v>
       </c>
@@ -15786,7 +15786,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="45">
         <v>107</v>
       </c>
@@ -15863,7 +15863,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="45">
         <v>108</v>
       </c>
@@ -15940,7 +15940,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="45">
         <v>109</v>
       </c>
@@ -16017,7 +16017,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="45">
         <v>110</v>
       </c>
@@ -16094,7 +16094,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="45">
         <v>111</v>
       </c>
@@ -16171,7 +16171,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="45">
         <v>112</v>
       </c>
@@ -16248,7 +16248,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="45">
         <v>113</v>
       </c>
@@ -16325,7 +16325,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="45">
         <v>114</v>
       </c>
@@ -16402,7 +16402,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="45">
         <v>115</v>
       </c>
@@ -16479,7 +16479,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="45">
         <v>116</v>
       </c>
@@ -16556,7 +16556,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="45">
         <v>117</v>
       </c>
@@ -16633,7 +16633,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="45">
         <v>118</v>
       </c>
@@ -16710,7 +16710,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="45">
         <v>119</v>
       </c>
@@ -16787,7 +16787,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="45">
         <v>120</v>
       </c>
@@ -16864,7 +16864,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="45">
         <v>121</v>
       </c>
@@ -16941,7 +16941,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="45">
         <v>122</v>
       </c>
@@ -17018,7 +17018,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="45">
         <v>123</v>
       </c>
@@ -17095,7 +17095,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="45">
         <v>124</v>
       </c>
@@ -17172,7 +17172,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="45">
         <v>125</v>
       </c>
@@ -17249,7 +17249,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="45">
         <v>126</v>
       </c>
@@ -17326,7 +17326,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="45">
         <v>127</v>
       </c>
@@ -17403,7 +17403,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="45">
         <v>128</v>
       </c>
@@ -17480,7 +17480,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="45">
         <v>129</v>
       </c>
@@ -17557,7 +17557,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="45">
         <v>130</v>
       </c>
@@ -17634,7 +17634,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="45">
         <v>131</v>
       </c>
@@ -17711,7 +17711,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="45">
         <v>132</v>
       </c>
@@ -17788,7 +17788,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="45">
         <v>133</v>
       </c>
@@ -17865,7 +17865,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="45">
         <v>134</v>
       </c>
@@ -17942,7 +17942,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="45">
         <v>135</v>
       </c>
@@ -18019,7 +18019,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="45">
         <v>136</v>
       </c>
@@ -18096,7 +18096,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="45">
         <v>137</v>
       </c>
@@ -18173,7 +18173,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="45">
         <v>138</v>
       </c>
@@ -18250,7 +18250,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="45">
         <v>139</v>
       </c>
@@ -18327,7 +18327,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="45">
         <v>140</v>
       </c>
@@ -18404,7 +18404,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="45">
         <v>141</v>
       </c>
@@ -18481,7 +18481,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="45">
         <v>142</v>
       </c>
@@ -18558,7 +18558,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="45">
         <v>143</v>
       </c>
@@ -18635,7 +18635,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="45">
         <v>144</v>
       </c>
@@ -18712,7 +18712,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="45">
         <v>145</v>
       </c>
@@ -18789,7 +18789,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="45">
         <v>146</v>
       </c>
@@ -18866,7 +18866,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="45">
         <v>147</v>
       </c>
@@ -18943,7 +18943,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="45">
         <v>148</v>
       </c>
@@ -19020,7 +19020,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="45">
         <v>149</v>
       </c>
@@ -19097,7 +19097,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="45">
         <v>150</v>
       </c>
@@ -19174,7 +19174,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="45">
         <v>151</v>
       </c>
@@ -19251,7 +19251,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="45">
         <v>152</v>
       </c>
@@ -19328,7 +19328,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="45">
         <v>153</v>
       </c>
@@ -19405,7 +19405,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="45">
         <v>154</v>
       </c>
@@ -19482,7 +19482,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="45">
         <v>155</v>
       </c>
@@ -19559,7 +19559,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="45">
         <v>156</v>
       </c>
@@ -19636,7 +19636,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="45">
         <v>157</v>
       </c>
@@ -19713,7 +19713,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="45">
         <v>158</v>
       </c>
@@ -19790,7 +19790,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="45">
         <v>159</v>
       </c>
@@ -19867,7 +19867,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="45">
         <v>160</v>
       </c>
@@ -19944,7 +19944,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="45">
         <v>161</v>
       </c>
@@ -20021,7 +20021,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="45">
         <v>162</v>
       </c>
@@ -20098,7 +20098,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="45">
         <v>163</v>
       </c>
@@ -20175,7 +20175,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="45">
         <v>164</v>
       </c>
@@ -20252,7 +20252,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="45">
         <v>165</v>
       </c>
@@ -20329,7 +20329,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="45">
         <v>166</v>
       </c>
@@ -20406,7 +20406,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="45">
         <v>167</v>
       </c>
@@ -20483,7 +20483,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="45">
         <v>168</v>
       </c>
@@ -20560,7 +20560,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="45">
         <v>169</v>
       </c>
@@ -20637,7 +20637,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="45">
         <v>170</v>
       </c>
@@ -20714,7 +20714,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="45">
         <v>171</v>
       </c>
@@ -20791,7 +20791,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="45">
         <v>172</v>
       </c>
@@ -20868,7 +20868,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="45">
         <v>173</v>
       </c>
@@ -20945,7 +20945,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="45">
         <v>174</v>
       </c>
@@ -21022,7 +21022,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="45">
         <v>175</v>
       </c>
@@ -21099,7 +21099,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="45">
         <v>176</v>
       </c>
@@ -21176,7 +21176,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="177" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="45">
         <v>177</v>
       </c>
@@ -21253,7 +21253,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="45">
         <v>178</v>
       </c>
@@ -21330,7 +21330,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="179" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="45">
         <v>179</v>
       </c>
@@ -21407,7 +21407,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="180" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="45">
         <v>180</v>
       </c>
@@ -21484,7 +21484,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="181" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="45">
         <v>181</v>
       </c>
@@ -21561,7 +21561,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="182" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="45">
         <v>182</v>
       </c>
@@ -21638,7 +21638,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="183" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="45">
         <v>183</v>
       </c>
@@ -21715,7 +21715,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="184" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="45">
         <v>184</v>
       </c>
@@ -21792,7 +21792,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="185" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="45">
         <v>185</v>
       </c>
@@ -21869,7 +21869,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="186" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="45">
         <v>186</v>
       </c>
@@ -21946,7 +21946,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="187" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="45">
         <v>187</v>
       </c>
@@ -22023,7 +22023,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="188" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="45">
         <v>188</v>
       </c>
@@ -22100,7 +22100,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="189" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="45">
         <v>189</v>
       </c>
@@ -22177,7 +22177,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="190" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="45">
         <v>190</v>
       </c>
@@ -22254,7 +22254,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="191" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="45">
         <v>191</v>
       </c>
@@ -22331,7 +22331,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="192" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="45">
         <v>192</v>
       </c>
@@ -22408,7 +22408,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="193" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="45">
         <v>193</v>
       </c>
@@ -22485,7 +22485,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="194" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="45">
         <v>194</v>
       </c>
@@ -22562,7 +22562,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="195" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="45">
         <v>195</v>
       </c>
@@ -22639,7 +22639,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="196" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="45">
         <v>196</v>
       </c>
@@ -22716,7 +22716,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="197" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="45">
         <v>197</v>
       </c>
@@ -22793,7 +22793,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="198" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="45">
         <v>198</v>
       </c>
@@ -22870,7 +22870,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="199" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="45">
         <v>199</v>
       </c>
@@ -22947,7 +22947,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="200" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="45">
         <v>200</v>
       </c>
@@ -23024,7 +23024,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="201" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="45">
         <v>201</v>
       </c>
@@ -23101,7 +23101,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="202" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="45">
         <v>202</v>
       </c>
@@ -23178,7 +23178,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="203" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="45">
         <v>203</v>
       </c>
@@ -23255,7 +23255,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="204" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="45">
         <v>204</v>
       </c>
@@ -23332,7 +23332,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="205" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="45">
         <v>205</v>
       </c>
@@ -23409,7 +23409,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="206" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="45">
         <v>206</v>
       </c>
@@ -23486,7 +23486,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="207" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="45">
         <v>207</v>
       </c>
@@ -23563,7 +23563,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="208" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="45">
         <v>208</v>
       </c>
@@ -23640,7 +23640,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="209" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="45">
         <v>209</v>
       </c>
@@ -23717,7 +23717,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="210" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="45">
         <v>210</v>
       </c>
@@ -23794,7 +23794,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="211" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="45">
         <v>211</v>
       </c>
@@ -23871,7 +23871,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="212" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="45">
         <v>212</v>
       </c>
@@ -23948,7 +23948,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="213" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="45">
         <v>213</v>
       </c>
@@ -24025,7 +24025,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="214" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="45">
         <v>214</v>
       </c>
@@ -24102,7 +24102,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="215" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="45">
         <v>215</v>
       </c>
@@ -24179,7 +24179,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="216" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="45">
         <v>216</v>
       </c>
@@ -24256,7 +24256,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="217" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="45">
         <v>217</v>
       </c>
@@ -24333,7 +24333,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="218" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="45">
         <v>218</v>
       </c>
@@ -24410,7 +24410,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="219" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="45">
         <v>219</v>
       </c>
@@ -24487,7 +24487,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="220" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="45">
         <v>220</v>
       </c>
@@ -24564,7 +24564,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="221" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="45">
         <v>221</v>
       </c>
@@ -24641,7 +24641,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="222" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="45">
         <v>222</v>
       </c>
@@ -24718,7 +24718,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="223" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="45">
         <v>223</v>
       </c>
@@ -24795,7 +24795,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="224" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="45">
         <v>224</v>
       </c>
@@ -24872,7 +24872,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="225" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="45">
         <v>225</v>
       </c>
@@ -24949,7 +24949,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="226" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="45">
         <v>226</v>
       </c>
@@ -25026,7 +25026,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="227" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="45">
         <v>227</v>
       </c>
@@ -25103,7 +25103,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="228" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="45">
         <v>228</v>
       </c>
@@ -25180,7 +25180,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="229" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="45">
         <v>229</v>
       </c>
@@ -25257,7 +25257,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="230" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="45">
         <v>230</v>
       </c>
@@ -25334,7 +25334,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="231" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="45">
         <v>231</v>
       </c>
@@ -25411,7 +25411,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="232" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="45">
         <v>232</v>
       </c>
@@ -25488,7 +25488,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="233" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="45">
         <v>233</v>
       </c>
@@ -25565,7 +25565,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="234" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="45">
         <v>234</v>
       </c>
@@ -25642,7 +25642,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="235" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="45">
         <v>235</v>
       </c>
@@ -25719,7 +25719,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="236" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="45">
         <v>236</v>
       </c>
@@ -25796,7 +25796,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="237" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="45">
         <v>237</v>
       </c>
@@ -25873,7 +25873,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="238" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="45">
         <v>238</v>
       </c>
@@ -25950,7 +25950,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="239" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="45">
         <v>239</v>
       </c>
@@ -26027,7 +26027,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="240" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="45">
         <v>240</v>
       </c>
@@ -26104,7 +26104,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="241" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="45">
         <v>241</v>
       </c>
@@ -26181,7 +26181,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="242" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="45">
         <v>242</v>
       </c>
@@ -26258,7 +26258,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="243" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="45">
         <v>243</v>
       </c>
@@ -26335,7 +26335,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="244" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="45">
         <v>244</v>
       </c>
@@ -26412,7 +26412,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="245" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="45">
         <v>245</v>
       </c>
@@ -26489,7 +26489,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="246" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="45">
         <v>246</v>
       </c>
@@ -26566,7 +26566,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="247" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="45">
         <v>247</v>
       </c>
@@ -26643,7 +26643,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="248" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="45">
         <v>248</v>
       </c>
@@ -26720,7 +26720,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="249" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="45">
         <v>249</v>
       </c>
@@ -26797,7 +26797,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="250" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="45">
         <v>250</v>
       </c>
@@ -26874,7 +26874,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="251" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="45">
         <v>251</v>
       </c>
@@ -26951,7 +26951,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="252" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="45">
         <v>252</v>
       </c>
@@ -27028,7 +27028,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="253" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="45">
         <v>253</v>
       </c>
@@ -27105,7 +27105,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="254" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="45">
         <v>254</v>
       </c>
@@ -27182,7 +27182,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="255" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="45">
         <v>255</v>
       </c>
@@ -27259,7 +27259,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="256" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="45">
         <v>256</v>
       </c>
@@ -27336,7 +27336,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="257" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="45">
         <v>257</v>
       </c>
@@ -27413,7 +27413,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="258" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="45">
         <v>258</v>
       </c>
@@ -27490,7 +27490,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="259" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="45">
         <v>259</v>
       </c>
@@ -27567,7 +27567,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="260" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="45">
         <v>260</v>
       </c>
@@ -27644,7 +27644,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="261" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="45">
         <v>261</v>
       </c>
@@ -27721,7 +27721,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="262" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="45">
         <v>262</v>
       </c>
@@ -27798,7 +27798,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="263" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="45">
         <v>263</v>
       </c>
@@ -27875,7 +27875,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="264" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="45">
         <v>264</v>
       </c>
@@ -27952,7 +27952,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="265" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="45">
         <v>265</v>
       </c>
@@ -28029,7 +28029,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="266" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="45">
         <v>266</v>
       </c>
@@ -28106,7 +28106,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="267" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="45">
         <v>267</v>
       </c>
@@ -28183,7 +28183,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="268" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="45">
         <v>268</v>
       </c>
@@ -28260,7 +28260,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="269" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="45">
         <v>269</v>
       </c>
@@ -28337,7 +28337,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="270" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="45">
         <v>270</v>
       </c>
@@ -28414,7 +28414,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="271" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="45">
         <v>271</v>
       </c>
@@ -28491,7 +28491,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="272" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="45">
         <v>272</v>
       </c>
@@ -28568,7 +28568,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="273" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="45">
         <v>273</v>
       </c>
@@ -28645,7 +28645,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="274" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="45">
         <v>274</v>
       </c>
@@ -28722,7 +28722,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="275" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="45">
         <v>275</v>
       </c>
@@ -28799,7 +28799,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="276" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="45">
         <v>276</v>
       </c>
@@ -28876,7 +28876,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="277" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="45">
         <v>277</v>
       </c>
@@ -28953,7 +28953,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="278" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="45">
         <v>278</v>
       </c>
@@ -29030,7 +29030,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="279" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="45">
         <v>279</v>
       </c>
@@ -29107,7 +29107,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="280" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="45">
         <v>280</v>
       </c>
@@ -29184,7 +29184,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="281" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="45">
         <v>281</v>
       </c>
@@ -29261,7 +29261,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="282" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="45">
         <v>282</v>
       </c>
@@ -29338,7 +29338,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="283" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="45">
         <v>283</v>
       </c>
@@ -29415,7 +29415,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="284" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="45">
         <v>284</v>
       </c>
@@ -29492,7 +29492,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="285" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="45">
         <v>285</v>
       </c>
@@ -29569,7 +29569,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="286" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="45">
         <v>286</v>
       </c>
@@ -29646,7 +29646,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="287" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="45">
         <v>287</v>
       </c>
@@ -29723,7 +29723,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="288" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="45">
         <v>288</v>
       </c>
@@ -29800,7 +29800,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="289" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="45">
         <v>289</v>
       </c>
@@ -29877,7 +29877,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="290" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="45">
         <v>290</v>
       </c>
@@ -29954,7 +29954,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="291" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="45">
         <v>291</v>
       </c>
@@ -30031,7 +30031,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="292" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="45">
         <v>292</v>
       </c>
@@ -30108,7 +30108,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="293" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="45">
         <v>293</v>
       </c>
@@ -30185,7 +30185,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="294" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="45">
         <v>294</v>
       </c>
@@ -30262,7 +30262,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="295" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="45">
         <v>295</v>
       </c>
@@ -30339,7 +30339,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="296" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="45">
         <v>296</v>
       </c>
@@ -30416,7 +30416,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="297" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="45">
         <v>297</v>
       </c>
@@ -30493,7 +30493,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="298" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="45">
         <v>298</v>
       </c>
@@ -30570,7 +30570,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="299" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="45">
         <v>299</v>
       </c>
@@ -30647,7 +30647,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="300" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="45">
         <v>300</v>
       </c>
@@ -30724,7 +30724,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="301" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="45">
         <v>301</v>
       </c>
@@ -30801,7 +30801,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="302" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="45">
         <v>302</v>
       </c>
@@ -30878,7 +30878,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="303" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="45">
         <v>303</v>
       </c>
@@ -30955,7 +30955,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="304" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="45">
         <v>304</v>
       </c>
@@ -31032,7 +31032,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="305" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="45">
         <v>305</v>
       </c>
@@ -31109,7 +31109,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="306" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="45">
         <v>306</v>
       </c>
@@ -31186,7 +31186,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="307" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="45">
         <v>307</v>
       </c>
@@ -31263,7 +31263,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="308" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="45">
         <v>308</v>
       </c>
@@ -31340,7 +31340,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="309" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="45">
         <v>309</v>
       </c>
@@ -31417,7 +31417,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="310" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="45">
         <v>310</v>
       </c>
@@ -31494,7 +31494,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="311" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="45">
         <v>311</v>
       </c>
@@ -31571,7 +31571,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="312" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="45">
         <v>312</v>
       </c>
@@ -31648,7 +31648,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="313" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="45">
         <v>313</v>
       </c>
@@ -31725,7 +31725,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="314" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="45">
         <v>314</v>
       </c>
@@ -31802,7 +31802,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="315" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="45">
         <v>315</v>
       </c>
@@ -31879,7 +31879,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="316" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="45">
         <v>316</v>
       </c>
@@ -31956,7 +31956,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="317" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="45">
         <v>317</v>
       </c>
@@ -32033,7 +32033,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="318" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="45">
         <v>318</v>
       </c>
@@ -32110,7 +32110,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="319" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="45">
         <v>319</v>
       </c>
@@ -32187,7 +32187,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="320" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="45">
         <v>320</v>
       </c>
@@ -32264,7 +32264,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="321" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="45">
         <v>321</v>
       </c>
@@ -32341,7 +32341,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="322" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="45">
         <v>322</v>
       </c>
@@ -32418,7 +32418,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="323" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="45">
         <v>323</v>
       </c>
@@ -32495,7 +32495,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="324" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="45">
         <v>324</v>
       </c>
@@ -32572,7 +32572,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="325" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="45">
         <v>325</v>
       </c>
@@ -32649,7 +32649,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="326" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="45">
         <v>326</v>
       </c>
@@ -32726,7 +32726,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="327" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="45">
         <v>327</v>
       </c>
@@ -32803,7 +32803,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="328" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="45">
         <v>328</v>
       </c>
@@ -32880,7 +32880,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="329" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="45">
         <v>329</v>
       </c>
@@ -32957,7 +32957,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="330" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="45">
         <v>330</v>
       </c>
@@ -33034,7 +33034,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="331" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="45">
         <v>331</v>
       </c>
@@ -33111,7 +33111,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="332" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="45">
         <v>332</v>
       </c>
@@ -33188,7 +33188,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="333" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="45">
         <v>333</v>
       </c>
@@ -33265,7 +33265,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="334" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="45">
         <v>334</v>
       </c>
@@ -33342,7 +33342,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="335" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="45">
         <v>335</v>
       </c>
@@ -33419,7 +33419,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="336" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="45">
         <v>336</v>
       </c>
@@ -33496,7 +33496,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="337" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="45">
         <v>337</v>
       </c>
@@ -33573,7 +33573,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="338" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="45">
         <v>338</v>
       </c>
@@ -33650,7 +33650,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="339" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="45">
         <v>339</v>
       </c>
@@ -33727,7 +33727,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="340" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="45">
         <v>340</v>
       </c>
@@ -33804,7 +33804,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="341" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="45">
         <v>341</v>
       </c>
@@ -33881,7 +33881,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="342" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="45">
         <v>342</v>
       </c>
@@ -33958,7 +33958,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="343" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="45">
         <v>343</v>
       </c>
@@ -34035,7 +34035,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="344" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="45">
         <v>344</v>
       </c>
@@ -34112,7 +34112,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="345" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="45">
         <v>345</v>
       </c>
@@ -34189,7 +34189,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="346" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="45">
         <v>346</v>
       </c>
@@ -34266,7 +34266,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="347" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="45">
         <v>347</v>
       </c>
@@ -34343,7 +34343,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="348" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="45">
         <v>348</v>
       </c>
@@ -34420,7 +34420,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="349" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="45">
         <v>349</v>
       </c>
@@ -34497,7 +34497,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="350" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="45">
         <v>350</v>
       </c>
@@ -34574,7 +34574,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="351" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="45">
         <v>351</v>
       </c>
@@ -34651,7 +34651,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="352" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="45">
         <v>352</v>
       </c>
@@ -34728,7 +34728,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="353" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="45">
         <v>353</v>
       </c>
@@ -34805,7 +34805,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="354" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="45">
         <v>354</v>
       </c>
@@ -34882,7 +34882,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="355" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="45">
         <v>355</v>
       </c>
@@ -34959,7 +34959,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="356" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="45">
         <v>356</v>
       </c>
@@ -35036,7 +35036,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="357" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="45">
         <v>357</v>
       </c>
@@ -35113,7 +35113,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="358" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="45">
         <v>358</v>
       </c>
@@ -35190,7 +35190,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="359" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="45">
         <v>359</v>
       </c>
@@ -35267,7 +35267,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="360" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="45">
         <v>360</v>
       </c>
@@ -35344,7 +35344,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="361" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="45">
         <v>361</v>
       </c>
@@ -35421,7 +35421,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="362" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="45">
         <v>362</v>
       </c>
@@ -35498,7 +35498,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="363" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="45">
         <v>363</v>
       </c>
@@ -35575,7 +35575,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="364" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="45">
         <v>364</v>
       </c>
@@ -35652,7 +35652,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="365" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="45">
         <v>365</v>
       </c>
@@ -35729,7 +35729,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="366" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="45">
         <v>366</v>
       </c>
@@ -35806,7 +35806,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="367" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="45">
         <v>367</v>
       </c>
@@ -35883,7 +35883,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="368" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="45">
         <v>368</v>
       </c>
@@ -35960,7 +35960,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="369" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="45">
         <v>369</v>
       </c>
@@ -36037,7 +36037,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="370" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="45">
         <v>370</v>
       </c>
@@ -36114,7 +36114,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="371" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="45">
         <v>371</v>
       </c>
@@ -36191,7 +36191,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="372" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="45">
         <v>372</v>
       </c>
@@ -36268,7 +36268,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="373" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="45">
         <v>373</v>
       </c>
@@ -36345,7 +36345,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="374" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="45">
         <v>374</v>
       </c>
@@ -36422,7 +36422,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="375" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="45">
         <v>375</v>
       </c>
@@ -36499,7 +36499,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="376" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="45">
         <v>376</v>
       </c>
@@ -36576,7 +36576,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="377" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="45">
         <v>377</v>
       </c>
@@ -36653,7 +36653,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="378" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="45">
         <v>378</v>
       </c>
@@ -36730,7 +36730,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="379" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="45">
         <v>379</v>
       </c>
@@ -36807,7 +36807,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="380" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="45">
         <v>380</v>
       </c>
@@ -36884,7 +36884,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="381" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="45">
         <v>381</v>
       </c>
@@ -36961,7 +36961,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="382" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="45">
         <v>382</v>
       </c>
@@ -37038,7 +37038,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="383" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="45">
         <v>383</v>
       </c>
@@ -37115,7 +37115,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="384" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="45">
         <v>384</v>
       </c>
@@ -37192,7 +37192,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="385" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="45">
         <v>385</v>
       </c>
@@ -37269,7 +37269,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="386" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="45">
         <v>386</v>
       </c>
@@ -37346,7 +37346,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="387" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="45">
         <v>387</v>
       </c>
@@ -37423,7 +37423,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="388" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="45">
         <v>388</v>
       </c>
@@ -37500,7 +37500,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="389" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="45">
         <v>389</v>
       </c>
@@ -37577,7 +37577,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="390" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="45">
         <v>390</v>
       </c>
@@ -37654,7 +37654,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="391" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="45">
         <v>391</v>
       </c>
@@ -37731,7 +37731,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="392" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="45">
         <v>392</v>
       </c>
@@ -37808,7 +37808,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="393" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="45">
         <v>393</v>
       </c>
@@ -37885,7 +37885,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="394" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="45">
         <v>394</v>
       </c>
@@ -37962,7 +37962,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="395" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="45">
         <v>395</v>
       </c>
@@ -38039,7 +38039,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="396" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="45">
         <v>396</v>
       </c>
@@ -38116,7 +38116,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="397" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="45">
         <v>397</v>
       </c>
@@ -38193,7 +38193,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="398" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="45">
         <v>398</v>
       </c>
@@ -38270,7 +38270,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="399" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="45">
         <v>399</v>
       </c>
@@ -38347,7 +38347,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="400" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="45">
         <v>400</v>
       </c>
@@ -38424,7 +38424,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="401" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="45">
         <v>401</v>
       </c>
@@ -38501,7 +38501,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="402" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="45">
         <v>402</v>
       </c>
@@ -38578,7 +38578,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="403" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="45">
         <v>403</v>
       </c>
@@ -38655,7 +38655,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="404" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="45">
         <v>404</v>
       </c>
@@ -38732,7 +38732,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="405" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="45">
         <v>405</v>
       </c>
@@ -38809,7 +38809,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="406" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="45">
         <v>406</v>
       </c>
@@ -38886,7 +38886,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="407" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="45">
         <v>407</v>
       </c>
@@ -38963,7 +38963,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="408" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="45">
         <v>408</v>
       </c>
@@ -39040,7 +39040,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="409" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="45">
         <v>409</v>
       </c>
@@ -39117,7 +39117,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="410" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="45">
         <v>410</v>
       </c>
@@ -39194,7 +39194,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="411" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="45">
         <v>411</v>
       </c>
@@ -39271,7 +39271,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="412" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="45">
         <v>412</v>
       </c>
@@ -39348,7 +39348,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="413" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="45">
         <v>413</v>
       </c>
@@ -39425,7 +39425,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="414" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="45">
         <v>414</v>
       </c>
@@ -39502,7 +39502,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="415" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="45">
         <v>415</v>
       </c>
@@ -39579,7 +39579,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="416" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="45">
         <v>416</v>
       </c>
@@ -39656,7 +39656,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="417" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="45">
         <v>417</v>
       </c>
@@ -39733,7 +39733,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="418" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="45">
         <v>418</v>
       </c>
@@ -39810,7 +39810,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="419" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="45">
         <v>419</v>
       </c>
@@ -39887,7 +39887,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="420" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="45">
         <v>420</v>
       </c>
@@ -39964,7 +39964,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="421" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="45">
         <v>421</v>
       </c>
@@ -40041,7 +40041,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="422" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="45">
         <v>422</v>
       </c>
@@ -40118,7 +40118,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="423" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="45">
         <v>423</v>
       </c>
@@ -40195,7 +40195,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="424" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="45">
         <v>424</v>
       </c>
@@ -40272,7 +40272,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="425" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="45">
         <v>425</v>
       </c>
@@ -40349,7 +40349,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="426" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="45">
         <v>426</v>
       </c>
@@ -40426,7 +40426,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="427" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="45">
         <v>427</v>
       </c>
@@ -40503,7 +40503,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="428" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="45">
         <v>428</v>
       </c>
@@ -40580,7 +40580,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="429" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="45">
         <v>429</v>
       </c>
@@ -40657,7 +40657,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="430" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="45">
         <v>430</v>
       </c>
@@ -40734,7 +40734,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="431" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="45">
         <v>431</v>
       </c>
@@ -40811,7 +40811,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="432" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="45">
         <v>432</v>
       </c>
@@ -40888,7 +40888,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="433" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="45">
         <v>433</v>
       </c>
@@ -40965,7 +40965,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="434" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="45">
         <v>434</v>
       </c>
@@ -41042,7 +41042,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="435" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="45">
         <v>435</v>
       </c>
@@ -41119,7 +41119,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="436" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="45">
         <v>436</v>
       </c>
@@ -41196,7 +41196,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="437" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="45">
         <v>437</v>
       </c>
@@ -41273,7 +41273,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="438" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="45">
         <v>438</v>
       </c>
@@ -41350,7 +41350,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="439" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="45">
         <v>439</v>
       </c>
@@ -41427,7 +41427,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="440" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="45">
         <v>440</v>
       </c>
@@ -41504,7 +41504,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="441" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="45">
         <v>441</v>
       </c>
@@ -41581,7 +41581,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="442" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="45">
         <v>442</v>
       </c>
@@ -41658,7 +41658,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="443" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="45">
         <v>443</v>
       </c>
@@ -41735,7 +41735,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="444" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="45">
         <v>444</v>
       </c>
@@ -41812,7 +41812,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="445" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="45">
         <v>445</v>
       </c>
@@ -41889,7 +41889,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="446" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="45">
         <v>446</v>
       </c>
@@ -41966,7 +41966,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="447" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="45">
         <v>447</v>
       </c>
@@ -42043,7 +42043,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="448" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="45">
         <v>448</v>
       </c>
@@ -42120,7 +42120,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="449" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="45">
         <v>449</v>
       </c>
@@ -42197,7 +42197,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="450" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="45">
         <v>450</v>
       </c>
@@ -42274,7 +42274,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="451" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="45">
         <v>451</v>
       </c>
@@ -42351,7 +42351,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="452" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="45">
         <v>452</v>
       </c>
@@ -42428,7 +42428,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="453" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="45">
         <v>453</v>
       </c>
@@ -42505,7 +42505,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="454" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="45">
         <v>454</v>
       </c>
@@ -42582,7 +42582,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="455" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="45">
         <v>455</v>
       </c>
@@ -42659,7 +42659,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="456" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="45">
         <v>456</v>
       </c>
@@ -42736,7 +42736,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="457" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="45">
         <v>457</v>
       </c>
@@ -42813,7 +42813,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="458" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="45">
         <v>458</v>
       </c>
@@ -42890,7 +42890,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="459" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="45">
         <v>459</v>
       </c>
@@ -42967,7 +42967,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="460" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="45">
         <v>460</v>
       </c>
@@ -43044,7 +43044,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="461" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="45">
         <v>461</v>
       </c>
@@ -43121,7 +43121,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="462" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="45">
         <v>462</v>
       </c>
@@ -43198,7 +43198,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="463" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="45">
         <v>463</v>
       </c>
@@ -43275,7 +43275,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="464" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="45">
         <v>464</v>
       </c>
@@ -43352,7 +43352,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="465" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="45">
         <v>465</v>
       </c>
@@ -43429,7 +43429,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="466" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="45">
         <v>466</v>
       </c>
@@ -43506,7 +43506,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="467" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="45">
         <v>467</v>
       </c>
@@ -43583,7 +43583,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="468" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="45">
         <v>468</v>
       </c>
@@ -43660,7 +43660,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="469" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="45">
         <v>469</v>
       </c>
@@ -43737,7 +43737,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="470" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="45">
         <v>470</v>
       </c>
@@ -43814,7 +43814,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="471" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="45">
         <v>471</v>
       </c>
@@ -43891,7 +43891,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="472" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="45">
         <v>472</v>
       </c>
@@ -43968,7 +43968,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="473" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="45">
         <v>473</v>
       </c>
@@ -44045,7 +44045,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="474" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="45">
         <v>474</v>
       </c>
@@ -44122,7 +44122,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="475" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="45">
         <v>475</v>
       </c>
@@ -44199,7 +44199,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="476" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="45">
         <v>476</v>
       </c>
@@ -44276,7 +44276,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="477" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="45">
         <v>477</v>
       </c>
@@ -44353,7 +44353,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="478" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="45">
         <v>478</v>
       </c>
@@ -44430,7 +44430,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="479" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="45">
         <v>479</v>
       </c>
@@ -44507,7 +44507,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="480" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="45">
         <v>480</v>
       </c>
@@ -44584,7 +44584,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="481" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="45">
         <v>481</v>
       </c>
@@ -44661,7 +44661,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="482" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="45">
         <v>482</v>
       </c>
@@ -44738,7 +44738,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="483" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="45">
         <v>483</v>
       </c>
@@ -44815,7 +44815,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="484" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="45">
         <v>484</v>
       </c>
@@ -44892,7 +44892,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="485" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="45">
         <v>485</v>
       </c>
@@ -44969,7 +44969,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="486" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="45">
         <v>486</v>
       </c>
@@ -45046,7 +45046,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="487" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="45">
         <v>487</v>
       </c>
@@ -45123,7 +45123,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="488" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="45">
         <v>488</v>
       </c>
@@ -45200,7 +45200,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="489" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="45">
         <v>489</v>
       </c>
@@ -45277,7 +45277,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="490" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="45">
         <v>490</v>
       </c>
@@ -45354,7 +45354,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="491" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="45">
         <v>491</v>
       </c>
@@ -45431,7 +45431,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="492" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="45">
         <v>492</v>
       </c>
@@ -45508,7 +45508,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="493" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="45">
         <v>493</v>
       </c>
@@ -45585,7 +45585,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="494" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="45">
         <v>494</v>
       </c>
@@ -45662,7 +45662,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="495" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="45">
         <v>495</v>
       </c>
@@ -45739,7 +45739,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="496" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="45">
         <v>496</v>
       </c>
@@ -45816,7 +45816,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="497" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="45">
         <v>497</v>
       </c>
@@ -45893,7 +45893,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="498" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="45">
         <v>498</v>
       </c>
@@ -45970,7 +45970,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="499" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="45">
         <v>499</v>
       </c>
@@ -46047,7 +46047,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="500" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="45">
         <v>500</v>
       </c>
@@ -46124,7 +46124,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="501" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="45">
         <v>501</v>
       </c>
@@ -46201,7 +46201,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="502" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="45">
         <v>502</v>
       </c>
@@ -46278,7 +46278,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="503" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="45">
         <v>503</v>
       </c>
@@ -46355,7 +46355,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="504" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="45">
         <v>504</v>
       </c>
@@ -46432,7 +46432,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="505" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="45">
         <v>505</v>
       </c>
@@ -46509,7 +46509,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="506" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="45">
         <v>506</v>
       </c>
@@ -46586,7 +46586,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="507" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="45">
         <v>507</v>
       </c>
@@ -46663,7 +46663,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="508" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="45">
         <v>508</v>
       </c>
@@ -46740,7 +46740,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="509" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="45">
         <v>509</v>
       </c>
@@ -46817,7 +46817,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="510" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="45">
         <v>510</v>
       </c>
@@ -46894,7 +46894,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="511" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="45">
         <v>511</v>
       </c>
@@ -46971,7 +46971,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="512" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="45">
         <v>512</v>
       </c>
@@ -47048,7 +47048,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="513" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="45">
         <v>513</v>
       </c>
@@ -47125,7 +47125,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="514" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="45">
         <v>514</v>
       </c>
@@ -47202,7 +47202,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="515" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="45">
         <v>515</v>
       </c>
@@ -47279,7 +47279,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="516" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="45">
         <v>516</v>
       </c>
@@ -47356,7 +47356,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="517" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="45">
         <v>517</v>
       </c>
@@ -47433,7 +47433,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="518" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="45">
         <v>518</v>
       </c>
@@ -47510,7 +47510,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="519" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="45">
         <v>519</v>
       </c>
@@ -47587,7 +47587,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="520" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="45">
         <v>520</v>
       </c>
@@ -47664,7 +47664,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="521" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="45">
         <v>521</v>
       </c>
@@ -47741,7 +47741,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="522" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="45">
         <v>522</v>
       </c>
@@ -47818,7 +47818,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="523" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="45">
         <v>523</v>
       </c>
@@ -47895,7 +47895,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="524" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="45">
         <v>524</v>
       </c>
@@ -47972,7 +47972,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="525" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="45">
         <v>525</v>
       </c>
@@ -48049,7 +48049,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="526" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="45">
         <v>526</v>
       </c>
@@ -48126,7 +48126,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="527" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="45">
         <v>527</v>
       </c>
@@ -48203,7 +48203,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="528" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="45">
         <v>528</v>
       </c>
@@ -48280,7 +48280,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="529" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="45">
         <v>529</v>
       </c>
@@ -48357,7 +48357,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="530" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="45">
         <v>530</v>
       </c>
@@ -48434,7 +48434,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="531" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="45">
         <v>531</v>
       </c>
@@ -48511,7 +48511,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="532" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="45">
         <v>532</v>
       </c>
@@ -48588,7 +48588,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="533" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="45">
         <v>533</v>
       </c>
@@ -48665,7 +48665,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="534" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="45">
         <v>534</v>
       </c>
@@ -48742,7 +48742,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="535" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="45">
         <v>535</v>
       </c>
@@ -48819,7 +48819,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="536" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="45">
         <v>536</v>
       </c>
@@ -48896,7 +48896,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="537" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="45">
         <v>537</v>
       </c>
@@ -48973,7 +48973,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="538" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="45">
         <v>538</v>
       </c>
@@ -49050,7 +49050,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="539" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="45">
         <v>539</v>
       </c>
@@ -49127,7 +49127,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="540" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="45">
         <v>540</v>
       </c>
@@ -49204,7 +49204,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="541" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="45">
         <v>541</v>
       </c>
@@ -49281,7 +49281,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="542" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="45">
         <v>542</v>
       </c>
@@ -49358,7 +49358,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="543" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="45">
         <v>543</v>
       </c>
@@ -49435,7 +49435,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="544" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="45">
         <v>544</v>
       </c>
@@ -49512,7 +49512,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="545" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="45">
         <v>545</v>
       </c>
@@ -49589,7 +49589,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="546" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="45">
         <v>546</v>
       </c>
@@ -49666,7 +49666,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="547" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="45">
         <v>547</v>
       </c>
@@ -49743,7 +49743,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="548" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="45">
         <v>548</v>
       </c>
@@ -49820,7 +49820,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="549" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="45">
         <v>549</v>
       </c>
@@ -49897,7 +49897,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="550" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="45">
         <v>550</v>
       </c>
@@ -49974,7 +49974,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="551" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="45">
         <v>551</v>
       </c>
@@ -50051,7 +50051,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="552" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="45">
         <v>552</v>
       </c>
@@ -50128,7 +50128,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="553" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="45">
         <v>553</v>
       </c>
@@ -50205,7 +50205,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="554" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="45">
         <v>554</v>
       </c>
@@ -50282,7 +50282,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="555" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="45">
         <v>555</v>
       </c>
@@ -50359,7 +50359,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="556" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="45">
         <v>556</v>
       </c>
@@ -50436,7 +50436,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="557" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="45">
         <v>557</v>
       </c>
@@ -50513,7 +50513,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="558" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="45">
         <v>558</v>
       </c>
@@ -50590,7 +50590,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="559" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="45">
         <v>559</v>
       </c>
@@ -50667,7 +50667,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="560" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="45">
         <v>560</v>
       </c>
@@ -50744,7 +50744,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="561" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="45">
         <v>561</v>
       </c>
@@ -50821,7 +50821,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="562" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="45">
         <v>562</v>
       </c>
@@ -50898,7 +50898,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="563" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="45">
         <v>563</v>
       </c>
@@ -50975,7 +50975,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="564" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="45">
         <v>564</v>
       </c>
@@ -51052,7 +51052,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="565" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="45">
         <v>565</v>
       </c>
@@ -51129,7 +51129,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="566" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="45">
         <v>566</v>
       </c>
@@ -51206,7 +51206,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="567" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="45">
         <v>567</v>
       </c>
@@ -51283,7 +51283,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="568" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="45">
         <v>568</v>
       </c>
@@ -51360,7 +51360,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="569" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="45">
         <v>569</v>
       </c>
@@ -51437,7 +51437,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="570" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="45">
         <v>570</v>
       </c>
@@ -51514,7 +51514,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="571" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="45">
         <v>571</v>
       </c>
@@ -51591,7 +51591,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="572" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="45">
         <v>572</v>
       </c>
@@ -51668,7 +51668,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="573" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="45">
         <v>573</v>
       </c>
@@ -51745,7 +51745,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="574" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="45">
         <v>574</v>
       </c>
@@ -51822,7 +51822,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="575" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="45">
         <v>575</v>
       </c>
@@ -51899,7 +51899,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="576" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="45">
         <v>576</v>
       </c>
@@ -51976,7 +51976,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="577" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="45">
         <v>577</v>
       </c>
@@ -52053,7 +52053,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="578" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="45">
         <v>578</v>
       </c>
@@ -52130,7 +52130,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="579" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="45">
         <v>579</v>
       </c>
@@ -52207,7 +52207,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="580" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="45">
         <v>580</v>
       </c>
@@ -52284,7 +52284,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="581" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="45">
         <v>581</v>
       </c>
@@ -52361,7 +52361,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="582" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="45">
         <v>582</v>
       </c>
@@ -52438,7 +52438,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="583" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="45">
         <v>583</v>
       </c>
@@ -52515,7 +52515,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="584" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="45">
         <v>584</v>
       </c>
@@ -52592,7 +52592,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="585" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="45">
         <v>585</v>
       </c>
@@ -52669,7 +52669,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="586" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="45">
         <v>586</v>
       </c>
@@ -52746,7 +52746,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="587" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="45">
         <v>587</v>
       </c>
@@ -52823,7 +52823,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="588" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="45">
         <v>588</v>
       </c>
@@ -52900,7 +52900,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="589" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="45">
         <v>589</v>
       </c>
@@ -52977,7 +52977,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="590" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="45">
         <v>590</v>
       </c>
@@ -53054,7 +53054,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="591" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="45">
         <v>591</v>
       </c>
@@ -53131,7 +53131,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="592" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="45">
         <v>592</v>
       </c>
@@ -53208,7 +53208,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="593" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="45">
         <v>593</v>
       </c>
@@ -53285,7 +53285,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="594" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="45">
         <v>594</v>
       </c>
@@ -53362,7 +53362,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="595" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="45">
         <v>595</v>
       </c>
@@ -53439,7 +53439,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="596" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="45">
         <v>596</v>
       </c>
@@ -53516,7 +53516,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="597" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="45">
         <v>597</v>
       </c>
@@ -53593,7 +53593,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="598" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="45">
         <v>598</v>
       </c>
@@ -53670,7 +53670,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="599" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="45">
         <v>599</v>
       </c>
@@ -53747,7 +53747,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="600" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="45">
         <v>600</v>
       </c>
@@ -53824,7 +53824,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="601" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="45">
         <v>601</v>
       </c>
@@ -53901,7 +53901,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="602" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="45">
         <v>602</v>
       </c>
@@ -53978,7 +53978,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="603" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="45">
         <v>603</v>
       </c>
@@ -54055,7 +54055,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="604" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="45">
         <v>604</v>
       </c>
@@ -54132,7 +54132,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="605" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="45">
         <v>605</v>
       </c>
@@ -54209,7 +54209,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="606" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="45">
         <v>606</v>
       </c>
@@ -54286,7 +54286,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="607" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="45">
         <v>607</v>
       </c>
@@ -54363,7 +54363,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="608" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="45">
         <v>608</v>
       </c>
@@ -54440,7 +54440,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="609" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="45">
         <v>609</v>
       </c>
@@ -54517,7 +54517,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="610" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:25" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="45">
         <v>610</v>
       </c>

--- a/Versão5/ABNT/Ontologia_15965_2Q.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_2Q.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743F9B59-36BD-4D4E-AA8D-8767AA6BDF53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9B2E3E-D5F5-4253-8ECA-CB592AD61095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15286" uniqueCount="1467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15430" uniqueCount="1500">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -4311,9 +4311,6 @@
     <t>NBR.Parte</t>
   </si>
   <si>
-    <t>NBR.Q.Software</t>
-  </si>
-  <si>
     <t>NBR.Q.Perfurar.Cortar</t>
   </si>
   <si>
@@ -4329,21 +4326,6 @@
     <t>NBR.Q.Bombear.Tunelar</t>
   </si>
   <si>
-    <t>NBR.Q.Construir</t>
-  </si>
-  <si>
-    <t>NBR.Q.Testar</t>
-  </si>
-  <si>
-    <t>NBR.Q.Monitorar</t>
-  </si>
-  <si>
-    <t>NBR.Q.Medir</t>
-  </si>
-  <si>
-    <t>NBR.Q.Ferramenta</t>
-  </si>
-  <si>
     <t>[ 2Q.02 ]</t>
   </si>
   <si>
@@ -4362,9 +4344,6 @@
     <t>[ 2Q.42 ]</t>
   </si>
   <si>
-    <t>[ 2Q.58.02 ]</t>
-  </si>
-  <si>
     <t>[ 2Q.58.10 ]</t>
   </si>
   <si>
@@ -4419,39 +4398,12 @@
     <t>NBR.Tema</t>
   </si>
   <si>
-    <t>Software</t>
-  </si>
-  <si>
-    <t>Produzir Concreto</t>
-  </si>
-  <si>
-    <t>Bombear e Tunelar</t>
-  </si>
-  <si>
-    <t>Perfurar e Cortar</t>
-  </si>
-  <si>
-    <t>Demolir e Terraplanar</t>
-  </si>
-  <si>
-    <t>Limpar e Manter Fachada</t>
-  </si>
-  <si>
-    <t>Ferramentas</t>
-  </si>
-  <si>
     <t>Ferramentas de Medição</t>
   </si>
   <si>
-    <t>Ferramentas de Monitorar</t>
-  </si>
-  <si>
     <t>Ferramentas de Teste</t>
   </si>
   <si>
-    <t>NBR.Q.Obra</t>
-  </si>
-  <si>
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requisitos Espaciais do Projeto.</t>
   </si>
   <si>
@@ -4492,6 +4444,153 @@
   </si>
   <si>
     <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de Instalaciones del Proyecto.</t>
+  </si>
+  <si>
+    <t>NBR.Q.Ferramenta.de.Construção</t>
+  </si>
+  <si>
+    <t>NBR.Q.Ferramenta.de.Canteiro</t>
+  </si>
+  <si>
+    <t>NBR.Q.Ferramenta.de.Acabamento</t>
+  </si>
+  <si>
+    <t>NBR.Q.Ferramenta.de.Transporte</t>
+  </si>
+  <si>
+    <t>NBR.Q.Ferramenta.Motorizada</t>
+  </si>
+  <si>
+    <t>NBR.Q.Ferramenta.de.Controle</t>
+  </si>
+  <si>
+    <t>NBR.Q.Ferramenta.de.EPI</t>
+  </si>
+  <si>
+    <t>NBR.Q.Ferramenta.de.Construção.Geral</t>
+  </si>
+  <si>
+    <t>NBR.Q.Ferramenta.de.Medição</t>
+  </si>
+  <si>
+    <t>NBR.Q.Ferramenta.de.Monitoração</t>
+  </si>
+  <si>
+    <t>NBR.Q.Ferramenta.de.Teste</t>
+  </si>
+  <si>
+    <t>"Ferramentas de acabamento"</t>
+  </si>
+  <si>
+    <t>"Ferramentas de transporte ou içamento"</t>
+  </si>
+  <si>
+    <t>"Ferramentas de controle"</t>
+  </si>
+  <si>
+    <t>"Ferramentas de proteção EPI"</t>
+  </si>
+  <si>
+    <t>"Ferramentas de canteiro de obra"</t>
+  </si>
+  <si>
+    <t>"Ferramentas de apoio construtivo"</t>
+  </si>
+  <si>
+    <t>NBR.Q.Ferramenta.de.Suporte</t>
+  </si>
+  <si>
+    <t>[ 2Q.42.02.18 ]</t>
+  </si>
+  <si>
+    <t>[ 2Q.42.02.22 ]</t>
+  </si>
+  <si>
+    <t>[ 2Q.42.06 ]</t>
+  </si>
+  <si>
+    <t>[ 2Q.42.10 ]</t>
+  </si>
+  <si>
+    <t>[ 2Q.42.22 ]</t>
+  </si>
+  <si>
+    <t>[ 2Q.42.26 ]</t>
+  </si>
+  <si>
+    <t>[ 2Q.50 ]</t>
+  </si>
+  <si>
+    <t>[ 2Q.54 ]</t>
+  </si>
+  <si>
+    <t>[ 2Q.58 ]</t>
+  </si>
+  <si>
+    <t>Equipamentos de Bombeamento e Tunelação</t>
+  </si>
+  <si>
+    <t>Equipamentos para Produção de Concreto</t>
+  </si>
+  <si>
+    <t>Equipamentos para Perfuração e Corte</t>
+  </si>
+  <si>
+    <t>Equipamentos para Demolição e Terraplanagem</t>
+  </si>
+  <si>
+    <t>Equipamentos para Limpeza e Manutenção de Fachadas</t>
+  </si>
+  <si>
+    <t>Ferramentas de Suporte</t>
+  </si>
+  <si>
+    <t>Ferramentas de Monitoração</t>
+  </si>
+  <si>
+    <t>Ferramentas de Acabamento</t>
+  </si>
+  <si>
+    <t>Ferramentas de Transporte</t>
+  </si>
+  <si>
+    <t>Ferramentas de Controle</t>
+  </si>
+  <si>
+    <t>Ferramentas de Construção Geral</t>
+  </si>
+  <si>
+    <t>Ferramentas de Canteiro</t>
+  </si>
+  <si>
+    <t>Ferramentas Motorizadas</t>
+  </si>
+  <si>
+    <t>Ferramentas de Proteção Individual EPI</t>
+  </si>
+  <si>
+    <t>NBR.Equipamentos</t>
+  </si>
+  <si>
+    <t>NBR.Q.Ferramenta.Hardware</t>
+  </si>
+  <si>
+    <t>NBR.Q.Ferramenta.Software</t>
+  </si>
+  <si>
+    <t>Ferramentas de Hardware de projeto, gráficas e de TI</t>
+  </si>
+  <si>
+    <t>Ferramentas de Software para o projeto, gráficas ou de gestão</t>
+  </si>
+  <si>
+    <t>NBR.Q.Ferramenta.TI.Rede</t>
+  </si>
+  <si>
+    <t>Ferramentas de Rede TI</t>
+  </si>
+  <si>
+    <t>[ 2Q.06.06 ]</t>
   </si>
 </sst>
 </file>
@@ -5045,7 +5144,7 @@
     <xf numFmtId="0" fontId="8" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5053,55 +5152,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{FD276809-E4C5-4861-8007-253055573830}"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="9">
     <dxf>
       <font>
         <b val="0"/>
@@ -5183,24 +5234,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5741,7 +5774,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46167.413635185185</v>
+        <v>46167.463621759256</v>
       </c>
       <c r="C18" s="43" t="s">
         <v>1309</v>
@@ -5845,26 +5878,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1778FB64-75F3-4573-A6F2-8AC25FEAA02B}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA30"/>
+  <dimension ref="A1:AA39"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="6.55" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.8984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.296875" style="35" customWidth="1"/>
     <col min="3" max="3" width="7.8984375" style="35" customWidth="1"/>
     <col min="4" max="4" width="8.5" style="35"/>
-    <col min="5" max="5" width="7.296875" style="35" customWidth="1"/>
-    <col min="6" max="6" width="14" style="35" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.59765625" style="35" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" style="35" customWidth="1"/>
     <col min="7" max="11" width="8.5" style="35"/>
     <col min="14" max="14" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.19921875" customWidth="1"/>
-    <col min="16" max="16" width="58.09765625" customWidth="1"/>
-    <col min="17" max="17" width="45.59765625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21" customWidth="1"/>
+    <col min="16" max="16" width="57.69921875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="60.69921875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.5" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="10.69921875" customWidth="1"/>
     <col min="27" max="27" width="64.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" ht="36.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>1251</v>
       </c>
@@ -5998,10 +6031,10 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="39" t="s">
-        <v>1460</v>
+        <v>1444</v>
       </c>
       <c r="Q2" s="39" t="s">
-        <v>1461</v>
+        <v>1445</v>
       </c>
       <c r="R2" s="62" t="s">
         <v>638</v>
@@ -6035,7 +6068,7 @@
         <v>638</v>
       </c>
       <c r="AA2" s="39" t="s">
-        <v>1462</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.3">
@@ -6089,10 +6122,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="39" t="s">
-        <v>1453</v>
+        <v>1437</v>
       </c>
       <c r="Q3" s="39" t="s">
-        <v>1463</v>
+        <v>1447</v>
       </c>
       <c r="R3" s="62" t="s">
         <v>638</v>
@@ -6180,10 +6213,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="39" t="s">
-        <v>1454</v>
+        <v>1438</v>
       </c>
       <c r="Q4" s="39" t="s">
-        <v>1464</v>
+        <v>1448</v>
       </c>
       <c r="R4" s="62" t="s">
         <v>638</v>
@@ -6271,10 +6304,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="39" t="s">
-        <v>1455</v>
+        <v>1439</v>
       </c>
       <c r="Q5" s="39" t="s">
-        <v>1465</v>
+        <v>1449</v>
       </c>
       <c r="R5" s="62" t="s">
         <v>638</v>
@@ -6362,10 +6395,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="39" t="s">
-        <v>1456</v>
+        <v>1440</v>
       </c>
       <c r="Q6" s="39" t="s">
-        <v>1466</v>
+        <v>1450</v>
       </c>
       <c r="R6" s="62" t="s">
         <v>638</v>
@@ -6419,7 +6452,7 @@
         <v>1405</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>1428</v>
+        <v>1421</v>
       </c>
       <c r="G7" s="37" t="s">
         <v>638</v>
@@ -6437,7 +6470,7 @@
         <v>638</v>
       </c>
       <c r="L7" s="61" t="str">
-        <f t="shared" ref="L2:N17" si="4">CONCATENATE("", C7)</f>
+        <f t="shared" ref="L7:N17" si="4">CONCATENATE("", C7)</f>
         <v>Norma</v>
       </c>
       <c r="M7" s="61" t="str">
@@ -6449,7 +6482,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="O7" s="61" t="str">
-        <f t="shared" ref="O7:O19" si="5">F7</f>
+        <f t="shared" ref="O7:O20" si="5">F7</f>
         <v>NBR.0M</v>
       </c>
       <c r="P7" s="61" t="s">
@@ -6462,7 +6495,7 @@
         <v>638</v>
       </c>
       <c r="S7" s="63" t="str">
-        <f t="shared" ref="S7:U19" si="6">SUBSTITUTE(C7, "_", " ")</f>
+        <f t="shared" ref="S7:U20" si="6">SUBSTITUTE(C7, "_", " ")</f>
         <v>Norma</v>
       </c>
       <c r="T7" s="63" t="str">
@@ -6477,7 +6510,7 @@
         <v>1335</v>
       </c>
       <c r="W7" s="64" t="str">
-        <f t="shared" ref="W7:W19" si="7">CONCATENATE("Key.ABNT.",A7)</f>
+        <f t="shared" ref="W7:W20" si="7">CONCATENATE("Key.ABNT.",A7)</f>
         <v>Key.ABNT.7</v>
       </c>
       <c r="X7" s="39" t="s">
@@ -6510,7 +6543,7 @@
         <v>1405</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>1429</v>
+        <v>1422</v>
       </c>
       <c r="G8" s="37" t="s">
         <v>638</v>
@@ -6601,7 +6634,7 @@
         <v>1405</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>1430</v>
+        <v>1423</v>
       </c>
       <c r="G9" s="37" t="s">
         <v>638</v>
@@ -6692,7 +6725,7 @@
         <v>1405</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>1431</v>
+        <v>1424</v>
       </c>
       <c r="G10" s="37" t="s">
         <v>638</v>
@@ -6783,7 +6816,7 @@
         <v>1405</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>1432</v>
+        <v>1425</v>
       </c>
       <c r="G11" s="37" t="s">
         <v>638</v>
@@ -6874,7 +6907,7 @@
         <v>1405</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>1433</v>
+        <v>1426</v>
       </c>
       <c r="G12" s="37" t="s">
         <v>638</v>
@@ -6965,7 +6998,7 @@
         <v>1405</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>1434</v>
+        <v>1427</v>
       </c>
       <c r="G13" s="37" t="s">
         <v>638</v>
@@ -7147,7 +7180,7 @@
         <v>1405</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>1435</v>
+        <v>1428</v>
       </c>
       <c r="G15" s="37" t="s">
         <v>638</v>
@@ -7238,7 +7271,7 @@
         <v>1405</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>1436</v>
+        <v>1429</v>
       </c>
       <c r="G16" s="37" t="s">
         <v>638</v>
@@ -7329,7 +7362,7 @@
         <v>1405</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>1437</v>
+        <v>1430</v>
       </c>
       <c r="G17" s="37" t="s">
         <v>638</v>
@@ -7420,7 +7453,7 @@
         <v>1405</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>1438</v>
+        <v>1431</v>
       </c>
       <c r="G18" s="37" t="s">
         <v>638</v>
@@ -7438,7 +7471,7 @@
         <v>638</v>
       </c>
       <c r="L18" s="61" t="str">
-        <f t="shared" ref="L18:N19" si="8">CONCATENATE("", C18)</f>
+        <f t="shared" ref="L18:N20" si="8">CONCATENATE("", C18)</f>
         <v>Norma</v>
       </c>
       <c r="M18" s="61" t="str">
@@ -7511,7 +7544,7 @@
         <v>1405</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>1439</v>
+        <v>1432</v>
       </c>
       <c r="G19" s="37" t="s">
         <v>638</v>
@@ -7593,16 +7626,16 @@
         <v>1297</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>1440</v>
+        <v>1433</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>1452</v>
+        <v>1492</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="G20" s="37" t="s">
         <v>638</v>
@@ -7620,48 +7653,48 @@
         <v>638</v>
       </c>
       <c r="L20" s="61" t="str">
-        <f t="shared" ref="L20:L30" si="9">CONCATENATE("", C20)</f>
+        <f t="shared" si="8"/>
         <v>NBR.Tema</v>
       </c>
       <c r="M20" s="61" t="str">
-        <f t="shared" ref="M20:M30" si="10">CONCATENATE("", D20)</f>
+        <f t="shared" si="8"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="N20" s="61" t="str">
-        <f t="shared" ref="N20:N30" si="11">CONCATENATE("", E20)</f>
-        <v>NBR.Q.Obra</v>
+        <f t="shared" si="8"/>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="O20" s="61" t="str">
-        <f t="shared" ref="O20:O30" si="12">F20</f>
-        <v>NBR.Q.Ferramenta</v>
+        <f t="shared" si="5"/>
+        <v>NBR.Q.Ferramenta.Hardware</v>
       </c>
       <c r="P20" s="61" t="s">
-        <v>1448</v>
+        <v>1495</v>
       </c>
       <c r="Q20" s="61" t="str">
         <f>_xlfn.TRANSLATE(P20,"pt","es")</f>
-        <v>Herramientas</v>
+        <v>Herramientas de diseño, gráficos y hardware de TI</v>
       </c>
       <c r="R20" s="62" t="s">
         <v>638</v>
       </c>
       <c r="S20" s="63" t="str">
-        <f t="shared" ref="S20" si="13">SUBSTITUTE(C20, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>NBR.Tema</v>
       </c>
       <c r="T20" s="63" t="str">
-        <f t="shared" ref="T20" si="14">SUBSTITUTE(D20, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="U20" s="61" t="str">
-        <f t="shared" ref="U20" si="15">SUBSTITUTE(E20, "_", " ")</f>
-        <v>NBR.Q.Obra</v>
+        <f t="shared" si="6"/>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="V20" s="39" t="s">
         <v>1335</v>
       </c>
       <c r="W20" s="64" t="str">
-        <f t="shared" ref="W20" si="16">CONCATENATE("Key.ABNT.",A20)</f>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.20</v>
       </c>
       <c r="X20" s="39" t="s">
@@ -7671,11 +7704,11 @@
         <v>638</v>
       </c>
       <c r="Z20" s="69" t="s">
-        <v>1417</v>
+        <v>1411</v>
       </c>
       <c r="AA20" s="65" t="str">
         <f>_xlfn.TRANSLATE(P20,"pt","en")</f>
-        <v>Tools</v>
+        <v>Design, Graphic, and IT Hardware Tools</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -7686,16 +7719,16 @@
         <v>1297</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>1440</v>
+        <v>1433</v>
       </c>
       <c r="E21" s="33" t="s">
-        <v>1452</v>
+        <v>1492</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>1406</v>
+        <v>1497</v>
       </c>
       <c r="G21" s="37" t="s">
         <v>638</v>
@@ -7713,48 +7746,48 @@
         <v>638</v>
       </c>
       <c r="L21" s="61" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="L21:L31" si="9">CONCATENATE("", C21)</f>
         <v>NBR.Tema</v>
       </c>
       <c r="M21" s="61" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="M21:M31" si="10">CONCATENATE("", D21)</f>
         <v>NBR.Subtema</v>
       </c>
       <c r="N21" s="61" t="str">
-        <f t="shared" si="11"/>
-        <v>NBR.Q.Obra</v>
+        <f t="shared" ref="N21:N31" si="11">CONCATENATE("", E21)</f>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="O21" s="61" t="str">
-        <f t="shared" si="12"/>
-        <v>NBR.Q.Software</v>
+        <f t="shared" ref="O21:O31" si="12">F21</f>
+        <v>NBR.Q.Ferramenta.TI.Rede</v>
       </c>
       <c r="P21" s="61" t="s">
-        <v>1442</v>
+        <v>1498</v>
       </c>
       <c r="Q21" s="61" t="str">
-        <f t="shared" ref="Q21:Q30" si="17">_xlfn.TRANSLATE(P21,"pt","es")</f>
-        <v>Software</v>
+        <f>_xlfn.TRANSLATE(P21,"pt","es")</f>
+        <v>Herramientas de Red TI</v>
       </c>
       <c r="R21" s="62" t="s">
         <v>638</v>
       </c>
       <c r="S21" s="63" t="str">
-        <f t="shared" ref="S21:S30" si="18">SUBSTITUTE(C21, "_", " ")</f>
+        <f t="shared" ref="S21" si="13">SUBSTITUTE(C21, "_", " ")</f>
         <v>NBR.Tema</v>
       </c>
       <c r="T21" s="63" t="str">
-        <f t="shared" ref="T21:T30" si="19">SUBSTITUTE(D21, "_", " ")</f>
+        <f t="shared" ref="T21" si="14">SUBSTITUTE(D21, "_", " ")</f>
         <v>NBR.Subtema</v>
       </c>
       <c r="U21" s="61" t="str">
-        <f t="shared" ref="U21:U30" si="20">SUBSTITUTE(E21, "_", " ")</f>
-        <v>NBR.Q.Obra</v>
+        <f t="shared" ref="U21" si="15">SUBSTITUTE(E21, "_", " ")</f>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="V21" s="39" t="s">
         <v>1335</v>
       </c>
       <c r="W21" s="64" t="str">
-        <f t="shared" ref="W21:W30" si="21">CONCATENATE("Key.ABNT.",A21)</f>
+        <f t="shared" ref="W21" si="16">CONCATENATE("Key.ABNT.",A21)</f>
         <v>Key.ABNT.21</v>
       </c>
       <c r="X21" s="39" t="s">
@@ -7764,11 +7797,11 @@
         <v>638</v>
       </c>
       <c r="Z21" s="69" t="s">
-        <v>1418</v>
+        <v>1499</v>
       </c>
       <c r="AA21" s="65" t="str">
-        <f t="shared" ref="AA21:AA30" si="22">_xlfn.TRANSLATE(P21,"pt","en")</f>
-        <v>Software</v>
+        <f>_xlfn.TRANSLATE(P21,"pt","en")</f>
+        <v>IT Network Tools</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -7779,16 +7812,16 @@
         <v>1297</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>1440</v>
+        <v>1433</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>1452</v>
+        <v>1492</v>
       </c>
       <c r="F22" s="27" t="s">
-        <v>1415</v>
+        <v>1494</v>
       </c>
       <c r="G22" s="37" t="s">
         <v>638</v>
@@ -7815,39 +7848,39 @@
       </c>
       <c r="N22" s="61" t="str">
         <f t="shared" si="11"/>
-        <v>NBR.Q.Obra</v>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="O22" s="61" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Q.Medir</v>
+        <v>NBR.Q.Ferramenta.Software</v>
       </c>
       <c r="P22" s="61" t="s">
-        <v>1449</v>
+        <v>1496</v>
       </c>
       <c r="Q22" s="61" t="str">
-        <f t="shared" si="17"/>
-        <v>Herramientas de medición</v>
+        <f t="shared" ref="Q22:Q31" si="17">_xlfn.TRANSLATE(P22,"pt","es")</f>
+        <v>Herramientas de software para diseño, gráficos o gestión</v>
       </c>
       <c r="R22" s="62" t="s">
         <v>638</v>
       </c>
       <c r="S22" s="63" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="S22:S31" si="18">SUBSTITUTE(C22, "_", " ")</f>
         <v>NBR.Tema</v>
       </c>
       <c r="T22" s="63" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="T22:T31" si="19">SUBSTITUTE(D22, "_", " ")</f>
         <v>NBR.Subtema</v>
       </c>
       <c r="U22" s="61" t="str">
-        <f t="shared" si="20"/>
-        <v>NBR.Q.Obra</v>
+        <f t="shared" ref="U22:U31" si="20">SUBSTITUTE(E22, "_", " ")</f>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="V22" s="39" t="s">
         <v>1335</v>
       </c>
       <c r="W22" s="64" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="W22:W31" si="21">CONCATENATE("Key.ABNT.",A22)</f>
         <v>Key.ABNT.22</v>
       </c>
       <c r="X22" s="39" t="s">
@@ -7857,11 +7890,11 @@
         <v>638</v>
       </c>
       <c r="Z22" s="69" t="s">
-        <v>1419</v>
+        <v>1412</v>
       </c>
       <c r="AA22" s="65" t="str">
-        <f t="shared" si="22"/>
-        <v>Measurement Tools</v>
+        <f t="shared" ref="AA22:AA39" si="22">_xlfn.TRANSLATE(P22,"pt","en")</f>
+        <v>Software tools for design, graphics or management</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -7872,16 +7905,16 @@
         <v>1297</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>1440</v>
+        <v>1433</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>1452</v>
+        <v>1492</v>
       </c>
       <c r="F23" s="27" t="s">
-        <v>1414</v>
+        <v>1459</v>
       </c>
       <c r="G23" s="37" t="s">
         <v>638</v>
@@ -7908,18 +7941,18 @@
       </c>
       <c r="N23" s="61" t="str">
         <f t="shared" si="11"/>
-        <v>NBR.Q.Obra</v>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="O23" s="61" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Q.Monitorar</v>
+        <v>NBR.Q.Ferramenta.de.Medição</v>
       </c>
       <c r="P23" s="61" t="s">
-        <v>1450</v>
+        <v>1435</v>
       </c>
       <c r="Q23" s="61" t="str">
         <f t="shared" si="17"/>
-        <v>Herramientas de monitorización</v>
+        <v>Herramientas de medición</v>
       </c>
       <c r="R23" s="62" t="s">
         <v>638</v>
@@ -7934,7 +7967,7 @@
       </c>
       <c r="U23" s="61" t="str">
         <f t="shared" si="20"/>
-        <v>NBR.Q.Obra</v>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="V23" s="39" t="s">
         <v>1335</v>
@@ -7950,11 +7983,11 @@
         <v>638</v>
       </c>
       <c r="Z23" s="69" t="s">
-        <v>1420</v>
+        <v>1413</v>
       </c>
       <c r="AA23" s="65" t="str">
         <f t="shared" si="22"/>
-        <v>Monitoring Tools</v>
+        <v>Measurement Tools</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -7965,16 +7998,16 @@
         <v>1297</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>1440</v>
+        <v>1433</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>1452</v>
+        <v>1492</v>
       </c>
       <c r="F24" s="27" t="s">
-        <v>1413</v>
+        <v>1460</v>
       </c>
       <c r="G24" s="37" t="s">
         <v>638</v>
@@ -8001,18 +8034,18 @@
       </c>
       <c r="N24" s="61" t="str">
         <f t="shared" si="11"/>
-        <v>NBR.Q.Obra</v>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="O24" s="61" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Q.Testar</v>
+        <v>NBR.Q.Ferramenta.de.Monitoração</v>
       </c>
       <c r="P24" s="61" t="s">
-        <v>1451</v>
+        <v>1484</v>
       </c>
       <c r="Q24" s="61" t="str">
         <f t="shared" si="17"/>
-        <v>Herramientas de prueba</v>
+        <v>Herramientas de monitorización</v>
       </c>
       <c r="R24" s="62" t="s">
         <v>638</v>
@@ -8027,7 +8060,7 @@
       </c>
       <c r="U24" s="61" t="str">
         <f t="shared" si="20"/>
-        <v>NBR.Q.Obra</v>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="V24" s="39" t="s">
         <v>1335</v>
@@ -8043,11 +8076,11 @@
         <v>638</v>
       </c>
       <c r="Z24" s="69" t="s">
-        <v>1421</v>
+        <v>1414</v>
       </c>
       <c r="AA24" s="65" t="str">
         <f t="shared" si="22"/>
-        <v>Testing Tools</v>
+        <v>Monitoring Tools</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -8058,16 +8091,16 @@
         <v>1297</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>1440</v>
+        <v>1433</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>1452</v>
+        <v>1492</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>1412</v>
+        <v>1461</v>
       </c>
       <c r="G25" s="37" t="s">
         <v>638</v>
@@ -8094,18 +8127,18 @@
       </c>
       <c r="N25" s="61" t="str">
         <f t="shared" si="11"/>
-        <v>NBR.Q.Obra</v>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="O25" s="61" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Q.Construir</v>
+        <v>NBR.Q.Ferramenta.de.Teste</v>
       </c>
       <c r="P25" s="61" t="s">
-        <v>1457</v>
+        <v>1436</v>
       </c>
       <c r="Q25" s="61" t="str">
         <f t="shared" si="17"/>
-        <v>Herramientas de construcción</v>
+        <v>Herramientas de prueba</v>
       </c>
       <c r="R25" s="62" t="s">
         <v>638</v>
@@ -8120,7 +8153,7 @@
       </c>
       <c r="U25" s="61" t="str">
         <f t="shared" si="20"/>
-        <v>NBR.Q.Obra</v>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="V25" s="39" t="s">
         <v>1335</v>
@@ -8136,11 +8169,11 @@
         <v>638</v>
       </c>
       <c r="Z25" s="69" t="s">
-        <v>1422</v>
+        <v>1415</v>
       </c>
       <c r="AA25" s="65" t="str">
         <f t="shared" si="22"/>
-        <v>Construction Tools</v>
+        <v>Testing Tools</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -8151,16 +8184,16 @@
         <v>1297</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>1440</v>
+        <v>1433</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>1452</v>
+        <v>1492</v>
       </c>
       <c r="F26" s="27" t="s">
-        <v>1411</v>
+        <v>1451</v>
       </c>
       <c r="G26" s="37" t="s">
         <v>638</v>
@@ -8187,18 +8220,18 @@
       </c>
       <c r="N26" s="61" t="str">
         <f t="shared" si="11"/>
-        <v>NBR.Q.Obra</v>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="O26" s="61" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Q.Bombear.Tunelar</v>
+        <v>NBR.Q.Ferramenta.de.Construção</v>
       </c>
       <c r="P26" s="61" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="Q26" s="61" t="str">
         <f t="shared" si="17"/>
-        <v>Bombeo y túnel</v>
+        <v>Herramientas de construcción</v>
       </c>
       <c r="R26" s="62" t="s">
         <v>638</v>
@@ -8213,7 +8246,7 @@
       </c>
       <c r="U26" s="61" t="str">
         <f t="shared" si="20"/>
-        <v>NBR.Q.Obra</v>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="V26" s="39" t="s">
         <v>1335</v>
@@ -8229,11 +8262,11 @@
         <v>638</v>
       </c>
       <c r="Z26" s="69" t="s">
-        <v>1423</v>
+        <v>1416</v>
       </c>
       <c r="AA26" s="65" t="str">
         <f t="shared" si="22"/>
-        <v>Pumping and Tunneling</v>
+        <v>Construction Tools</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -8244,16 +8277,16 @@
         <v>1297</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>1440</v>
+        <v>1433</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>1452</v>
+        <v>1492</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>1410</v>
+        <v>1453</v>
       </c>
       <c r="G27" s="37" t="s">
         <v>638</v>
@@ -8280,18 +8313,18 @@
       </c>
       <c r="N27" s="61" t="str">
         <f t="shared" si="11"/>
-        <v>NBR.Q.Obra</v>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="O27" s="61" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Q.Produzir.Concreto</v>
+        <v>NBR.Q.Ferramenta.de.Acabamento</v>
       </c>
       <c r="P27" s="61" t="s">
-        <v>1443</v>
+        <v>1485</v>
       </c>
       <c r="Q27" s="61" t="str">
         <f t="shared" si="17"/>
-        <v>Producción de hormigón</v>
+        <v>Herramientas de acabado</v>
       </c>
       <c r="R27" s="62" t="s">
         <v>638</v>
@@ -8306,7 +8339,7 @@
       </c>
       <c r="U27" s="61" t="str">
         <f t="shared" si="20"/>
-        <v>NBR.Q.Obra</v>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="V27" s="39" t="s">
         <v>1335</v>
@@ -8322,11 +8355,11 @@
         <v>638</v>
       </c>
       <c r="Z27" s="69" t="s">
-        <v>1424</v>
+        <v>1469</v>
       </c>
       <c r="AA27" s="65" t="str">
         <f t="shared" si="22"/>
-        <v>Produce Concrete</v>
+        <v>Finishing Tools</v>
       </c>
     </row>
     <row r="28" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -8337,16 +8370,16 @@
         <v>1297</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>1440</v>
+        <v>1433</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>1452</v>
+        <v>1492</v>
       </c>
       <c r="F28" s="27" t="s">
-        <v>1407</v>
+        <v>1454</v>
       </c>
       <c r="G28" s="37" t="s">
         <v>638</v>
@@ -8373,18 +8406,18 @@
       </c>
       <c r="N28" s="61" t="str">
         <f t="shared" si="11"/>
-        <v>NBR.Q.Obra</v>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="O28" s="61" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Q.Perfurar.Cortar</v>
+        <v>NBR.Q.Ferramenta.de.Transporte</v>
       </c>
       <c r="P28" s="61" t="s">
-        <v>1445</v>
+        <v>1486</v>
       </c>
       <c r="Q28" s="61" t="str">
         <f t="shared" si="17"/>
-        <v>Taladro y Corte</v>
+        <v>Herramientas de transporte</v>
       </c>
       <c r="R28" s="62" t="s">
         <v>638</v>
@@ -8399,7 +8432,7 @@
       </c>
       <c r="U28" s="61" t="str">
         <f t="shared" si="20"/>
-        <v>NBR.Q.Obra</v>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="V28" s="39" t="s">
         <v>1335</v>
@@ -8415,11 +8448,11 @@
         <v>638</v>
       </c>
       <c r="Z28" s="69" t="s">
-        <v>1425</v>
+        <v>1470</v>
       </c>
       <c r="AA28" s="65" t="str">
         <f t="shared" si="22"/>
-        <v>Drill &amp; Cut</v>
+        <v>Transportation Tools</v>
       </c>
     </row>
     <row r="29" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -8430,16 +8463,16 @@
         <v>1297</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>1440</v>
+        <v>1433</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>1452</v>
+        <v>1492</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>1408</v>
+        <v>1455</v>
       </c>
       <c r="G29" s="37" t="s">
         <v>638</v>
@@ -8466,18 +8499,18 @@
       </c>
       <c r="N29" s="61" t="str">
         <f t="shared" si="11"/>
-        <v>NBR.Q.Obra</v>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="O29" s="61" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Q.Demolir.Terraplanar</v>
+        <v>NBR.Q.Ferramenta.Motorizada</v>
       </c>
       <c r="P29" s="61" t="s">
-        <v>1446</v>
+        <v>1490</v>
       </c>
       <c r="Q29" s="61" t="str">
         <f t="shared" si="17"/>
-        <v>Demolición y trabajo de tierra</v>
+        <v>Herramientas eléctricas</v>
       </c>
       <c r="R29" s="62" t="s">
         <v>638</v>
@@ -8492,7 +8525,7 @@
       </c>
       <c r="U29" s="61" t="str">
         <f t="shared" si="20"/>
-        <v>NBR.Q.Obra</v>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="V29" s="39" t="s">
         <v>1335</v>
@@ -8508,11 +8541,11 @@
         <v>638</v>
       </c>
       <c r="Z29" s="69" t="s">
-        <v>1426</v>
+        <v>1471</v>
       </c>
       <c r="AA29" s="65" t="str">
         <f t="shared" si="22"/>
-        <v>Demolish and Earthwork</v>
+        <v>Power Tools</v>
       </c>
     </row>
     <row r="30" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -8523,16 +8556,16 @@
         <v>1297</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>1440</v>
+        <v>1433</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>1452</v>
+        <v>1492</v>
       </c>
       <c r="F30" s="27" t="s">
-        <v>1409</v>
+        <v>1456</v>
       </c>
       <c r="G30" s="37" t="s">
         <v>638</v>
@@ -8559,18 +8592,18 @@
       </c>
       <c r="N30" s="61" t="str">
         <f t="shared" si="11"/>
-        <v>NBR.Q.Obra</v>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="O30" s="61" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Q.Limpar.Fachada</v>
+        <v>NBR.Q.Ferramenta.de.Controle</v>
       </c>
       <c r="P30" s="61" t="s">
-        <v>1447</v>
+        <v>1487</v>
       </c>
       <c r="Q30" s="61" t="str">
         <f t="shared" si="17"/>
-        <v>Limpiar y mantener la fachada</v>
+        <v>Herramientas de control</v>
       </c>
       <c r="R30" s="62" t="s">
         <v>638</v>
@@ -8585,7 +8618,7 @@
       </c>
       <c r="U30" s="61" t="str">
         <f t="shared" si="20"/>
-        <v>NBR.Q.Obra</v>
+        <v>NBR.Equipamentos</v>
       </c>
       <c r="V30" s="39" t="s">
         <v>1335</v>
@@ -8601,46 +8634,870 @@
         <v>638</v>
       </c>
       <c r="Z30" s="69" t="s">
-        <v>1427</v>
+        <v>1472</v>
       </c>
       <c r="AA30" s="65" t="str">
         <f t="shared" si="22"/>
-        <v>Clean and Maintain Facade</v>
+        <v>Control Tools</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="57">
+        <v>31</v>
+      </c>
+      <c r="B31" s="33" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D31" s="33" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E31" s="33" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F31" s="27" t="s">
+        <v>1457</v>
+      </c>
+      <c r="G31" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="H31" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="I31" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="J31" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="K31" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="L31" s="61" t="str">
+        <f t="shared" si="9"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="M31" s="61" t="str">
+        <f t="shared" si="10"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="N31" s="61" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="O31" s="61" t="str">
+        <f t="shared" si="12"/>
+        <v>NBR.Q.Ferramenta.de.EPI</v>
+      </c>
+      <c r="P31" s="61" t="s">
+        <v>1491</v>
+      </c>
+      <c r="Q31" s="61" t="str">
+        <f t="shared" si="17"/>
+        <v>Herramientas de protección individual individual (EPP)</v>
+      </c>
+      <c r="R31" s="62" t="s">
+        <v>638</v>
+      </c>
+      <c r="S31" s="63" t="str">
+        <f t="shared" si="18"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T31" s="63" t="str">
+        <f t="shared" si="19"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U31" s="61" t="str">
+        <f t="shared" si="20"/>
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="V31" s="39" t="s">
+        <v>1335</v>
+      </c>
+      <c r="W31" s="64" t="str">
+        <f t="shared" si="21"/>
+        <v>Key.ABNT.31</v>
+      </c>
+      <c r="X31" s="39" t="s">
+        <v>638</v>
+      </c>
+      <c r="Y31" s="39" t="s">
+        <v>638</v>
+      </c>
+      <c r="Z31" s="69" t="s">
+        <v>1473</v>
+      </c>
+      <c r="AA31" s="65" t="str">
+        <f t="shared" si="22"/>
+        <v>PPE Personal Protective Tools</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="57">
+        <v>32</v>
+      </c>
+      <c r="B32" s="33" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D32" s="33" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E32" s="33" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F32" s="27" t="s">
+        <v>1458</v>
+      </c>
+      <c r="G32" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="H32" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="I32" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="J32" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="K32" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="L32" s="61" t="str">
+        <f t="shared" ref="L32:L39" si="23">CONCATENATE("", C32)</f>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="M32" s="61" t="str">
+        <f t="shared" ref="M32:M39" si="24">CONCATENATE("", D32)</f>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="N32" s="61" t="str">
+        <f t="shared" ref="N32:N39" si="25">CONCATENATE("", E32)</f>
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="O32" s="61" t="str">
+        <f t="shared" ref="O32:O39" si="26">F32</f>
+        <v>NBR.Q.Ferramenta.de.Construção.Geral</v>
+      </c>
+      <c r="P32" s="61" t="s">
+        <v>1488</v>
+      </c>
+      <c r="Q32" s="61" t="str">
+        <f t="shared" ref="Q32:Q39" si="27">_xlfn.TRANSLATE(P32,"pt","es")</f>
+        <v>Herramientas generales de construcción</v>
+      </c>
+      <c r="R32" s="62" t="s">
+        <v>638</v>
+      </c>
+      <c r="S32" s="63" t="str">
+        <f t="shared" ref="S32:S39" si="28">SUBSTITUTE(C32, "_", " ")</f>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T32" s="63" t="str">
+        <f t="shared" ref="T32:T39" si="29">SUBSTITUTE(D32, "_", " ")</f>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U32" s="61" t="str">
+        <f t="shared" ref="U32:U39" si="30">SUBSTITUTE(E32, "_", " ")</f>
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="V32" s="39" t="s">
+        <v>1335</v>
+      </c>
+      <c r="W32" s="64" t="str">
+        <f t="shared" ref="W32:W39" si="31">CONCATENATE("Key.ABNT.",A32)</f>
+        <v>Key.ABNT.32</v>
+      </c>
+      <c r="X32" s="39" t="s">
+        <v>638</v>
+      </c>
+      <c r="Y32" s="39" t="s">
+        <v>638</v>
+      </c>
+      <c r="Z32" s="69" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AA32" s="65" t="str">
+        <f t="shared" si="22"/>
+        <v>General Construction Tools</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="57">
+        <v>33</v>
+      </c>
+      <c r="B33" s="33" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D33" s="33" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E33" s="33" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F33" s="27" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G33" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="H33" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="I33" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="J33" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="K33" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="L33" s="61" t="str">
+        <f t="shared" si="23"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="M33" s="61" t="str">
+        <f t="shared" si="24"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="N33" s="61" t="str">
+        <f t="shared" si="25"/>
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="O33" s="61" t="str">
+        <f t="shared" si="26"/>
+        <v>NBR.Q.Ferramenta.de.Canteiro</v>
+      </c>
+      <c r="P33" s="61" t="s">
+        <v>1489</v>
+      </c>
+      <c r="Q33" s="61" t="str">
+        <f t="shared" si="27"/>
+        <v>Herramientas para obras</v>
+      </c>
+      <c r="R33" s="62" t="s">
+        <v>638</v>
+      </c>
+      <c r="S33" s="63" t="str">
+        <f t="shared" si="28"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T33" s="63" t="str">
+        <f t="shared" si="29"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U33" s="61" t="str">
+        <f t="shared" si="30"/>
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="V33" s="39" t="s">
+        <v>1335</v>
+      </c>
+      <c r="W33" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>Key.ABNT.33</v>
+      </c>
+      <c r="X33" s="39" t="s">
+        <v>638</v>
+      </c>
+      <c r="Y33" s="39" t="s">
+        <v>638</v>
+      </c>
+      <c r="Z33" s="69" t="s">
+        <v>1475</v>
+      </c>
+      <c r="AA33" s="65" t="str">
+        <f t="shared" si="22"/>
+        <v>Construction Site Tools</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="57">
+        <v>34</v>
+      </c>
+      <c r="B34" s="33" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C34" s="33" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D34" s="33" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E34" s="33" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F34" s="27" t="s">
+        <v>1468</v>
+      </c>
+      <c r="G34" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="H34" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="I34" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="J34" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="K34" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="L34" s="61" t="str">
+        <f t="shared" si="23"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="M34" s="61" t="str">
+        <f t="shared" si="24"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="N34" s="61" t="str">
+        <f t="shared" si="25"/>
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="O34" s="61" t="str">
+        <f t="shared" si="26"/>
+        <v>NBR.Q.Ferramenta.de.Suporte</v>
+      </c>
+      <c r="P34" s="61" t="s">
+        <v>1483</v>
+      </c>
+      <c r="Q34" s="61" t="str">
+        <f t="shared" si="27"/>
+        <v>Herramientas de soporte</v>
+      </c>
+      <c r="R34" s="62" t="s">
+        <v>638</v>
+      </c>
+      <c r="S34" s="63" t="str">
+        <f t="shared" si="28"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T34" s="63" t="str">
+        <f t="shared" si="29"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U34" s="61" t="str">
+        <f t="shared" si="30"/>
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="V34" s="39" t="s">
+        <v>1335</v>
+      </c>
+      <c r="W34" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>Key.ABNT.34</v>
+      </c>
+      <c r="X34" s="39" t="s">
+        <v>638</v>
+      </c>
+      <c r="Y34" s="39" t="s">
+        <v>638</v>
+      </c>
+      <c r="Z34" s="69" t="s">
+        <v>1476</v>
+      </c>
+      <c r="AA34" s="65" t="str">
+        <f t="shared" si="22"/>
+        <v>Support Tools</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="57">
+        <v>35</v>
+      </c>
+      <c r="B35" s="33" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D35" s="33" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E35" s="33" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F35" s="27" t="s">
+        <v>1410</v>
+      </c>
+      <c r="G35" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="H35" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="I35" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="J35" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="K35" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="L35" s="61" t="str">
+        <f t="shared" si="23"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="M35" s="61" t="str">
+        <f t="shared" si="24"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="N35" s="61" t="str">
+        <f t="shared" si="25"/>
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="O35" s="61" t="str">
+        <f t="shared" si="26"/>
+        <v>NBR.Q.Bombear.Tunelar</v>
+      </c>
+      <c r="P35" s="61" t="s">
+        <v>1478</v>
+      </c>
+      <c r="Q35" s="61" t="str">
+        <f t="shared" si="27"/>
+        <v>Equipos de bombeo y túneles</v>
+      </c>
+      <c r="R35" s="62" t="s">
+        <v>638</v>
+      </c>
+      <c r="S35" s="63" t="str">
+        <f t="shared" si="28"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T35" s="63" t="str">
+        <f t="shared" si="29"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U35" s="61" t="str">
+        <f t="shared" si="30"/>
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="V35" s="39" t="s">
+        <v>1335</v>
+      </c>
+      <c r="W35" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>Key.ABNT.35</v>
+      </c>
+      <c r="X35" s="39" t="s">
+        <v>638</v>
+      </c>
+      <c r="Y35" s="39" t="s">
+        <v>638</v>
+      </c>
+      <c r="Z35" s="69" t="s">
+        <v>1477</v>
+      </c>
+      <c r="AA35" s="65" t="str">
+        <f t="shared" si="22"/>
+        <v>Pumping and Tunneling Equipment</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="57">
+        <v>36</v>
+      </c>
+      <c r="B36" s="33" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C36" s="33" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D36" s="33" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E36" s="33" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F36" s="27" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G36" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="H36" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="I36" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="J36" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="K36" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="L36" s="61" t="str">
+        <f t="shared" si="23"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="M36" s="61" t="str">
+        <f t="shared" si="24"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="N36" s="61" t="str">
+        <f t="shared" si="25"/>
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="O36" s="61" t="str">
+        <f t="shared" si="26"/>
+        <v>NBR.Q.Produzir.Concreto</v>
+      </c>
+      <c r="P36" s="61" t="s">
+        <v>1479</v>
+      </c>
+      <c r="Q36" s="61" t="str">
+        <f t="shared" si="27"/>
+        <v>Equipos de producción de hormigón</v>
+      </c>
+      <c r="R36" s="62" t="s">
+        <v>638</v>
+      </c>
+      <c r="S36" s="63" t="str">
+        <f t="shared" si="28"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T36" s="63" t="str">
+        <f t="shared" si="29"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U36" s="61" t="str">
+        <f t="shared" si="30"/>
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="V36" s="39" t="s">
+        <v>1335</v>
+      </c>
+      <c r="W36" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>Key.ABNT.36</v>
+      </c>
+      <c r="X36" s="39" t="s">
+        <v>638</v>
+      </c>
+      <c r="Y36" s="39" t="s">
+        <v>638</v>
+      </c>
+      <c r="Z36" s="69" t="s">
+        <v>1417</v>
+      </c>
+      <c r="AA36" s="65" t="str">
+        <f t="shared" si="22"/>
+        <v>Concrete Production Equipment</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="57">
+        <v>37</v>
+      </c>
+      <c r="B37" s="33" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C37" s="33" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D37" s="33" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E37" s="33" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F37" s="27" t="s">
+        <v>1406</v>
+      </c>
+      <c r="G37" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="H37" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="I37" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="J37" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="K37" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="L37" s="61" t="str">
+        <f t="shared" si="23"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="M37" s="61" t="str">
+        <f t="shared" si="24"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="N37" s="61" t="str">
+        <f t="shared" si="25"/>
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="O37" s="61" t="str">
+        <f t="shared" si="26"/>
+        <v>NBR.Q.Perfurar.Cortar</v>
+      </c>
+      <c r="P37" s="61" t="s">
+        <v>1480</v>
+      </c>
+      <c r="Q37" s="61" t="str">
+        <f t="shared" si="27"/>
+        <v>Equipos de perforación y corte</v>
+      </c>
+      <c r="R37" s="62" t="s">
+        <v>638</v>
+      </c>
+      <c r="S37" s="63" t="str">
+        <f t="shared" si="28"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T37" s="63" t="str">
+        <f t="shared" si="29"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U37" s="61" t="str">
+        <f t="shared" si="30"/>
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="V37" s="39" t="s">
+        <v>1335</v>
+      </c>
+      <c r="W37" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>Key.ABNT.37</v>
+      </c>
+      <c r="X37" s="39" t="s">
+        <v>638</v>
+      </c>
+      <c r="Y37" s="39" t="s">
+        <v>638</v>
+      </c>
+      <c r="Z37" s="69" t="s">
+        <v>1418</v>
+      </c>
+      <c r="AA37" s="65" t="str">
+        <f t="shared" si="22"/>
+        <v>Drilling &amp; Cutting Equipment</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="57">
+        <v>38</v>
+      </c>
+      <c r="B38" s="33" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C38" s="33" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D38" s="33" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E38" s="33" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F38" s="27" t="s">
+        <v>1407</v>
+      </c>
+      <c r="G38" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="H38" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="I38" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="J38" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="K38" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="L38" s="61" t="str">
+        <f t="shared" si="23"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="M38" s="61" t="str">
+        <f t="shared" si="24"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="N38" s="61" t="str">
+        <f t="shared" si="25"/>
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="O38" s="61" t="str">
+        <f t="shared" si="26"/>
+        <v>NBR.Q.Demolir.Terraplanar</v>
+      </c>
+      <c r="P38" s="61" t="s">
+        <v>1481</v>
+      </c>
+      <c r="Q38" s="61" t="str">
+        <f t="shared" si="27"/>
+        <v>Equipos para demolición y movimiento de tierras</v>
+      </c>
+      <c r="R38" s="62" t="s">
+        <v>638</v>
+      </c>
+      <c r="S38" s="63" t="str">
+        <f t="shared" si="28"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T38" s="63" t="str">
+        <f t="shared" si="29"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U38" s="61" t="str">
+        <f t="shared" si="30"/>
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="V38" s="39" t="s">
+        <v>1335</v>
+      </c>
+      <c r="W38" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>Key.ABNT.38</v>
+      </c>
+      <c r="X38" s="39" t="s">
+        <v>638</v>
+      </c>
+      <c r="Y38" s="39" t="s">
+        <v>638</v>
+      </c>
+      <c r="Z38" s="69" t="s">
+        <v>1419</v>
+      </c>
+      <c r="AA38" s="65" t="str">
+        <f t="shared" si="22"/>
+        <v>Equipment for Demolition and Earthmoving</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="57">
+        <v>39</v>
+      </c>
+      <c r="B39" s="33" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C39" s="33" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D39" s="33" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E39" s="33" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F39" s="27" t="s">
+        <v>1408</v>
+      </c>
+      <c r="G39" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="H39" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="I39" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="J39" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="K39" s="37" t="s">
+        <v>638</v>
+      </c>
+      <c r="L39" s="61" t="str">
+        <f t="shared" si="23"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="M39" s="61" t="str">
+        <f t="shared" si="24"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="N39" s="61" t="str">
+        <f t="shared" si="25"/>
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="O39" s="61" t="str">
+        <f t="shared" si="26"/>
+        <v>NBR.Q.Limpar.Fachada</v>
+      </c>
+      <c r="P39" s="61" t="s">
+        <v>1482</v>
+      </c>
+      <c r="Q39" s="61" t="str">
+        <f t="shared" si="27"/>
+        <v>Equipos para la limpieza y mantenimiento de fachadas</v>
+      </c>
+      <c r="R39" s="62" t="s">
+        <v>638</v>
+      </c>
+      <c r="S39" s="63" t="str">
+        <f t="shared" si="28"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T39" s="63" t="str">
+        <f t="shared" si="29"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U39" s="61" t="str">
+        <f t="shared" si="30"/>
+        <v>NBR.Equipamentos</v>
+      </c>
+      <c r="V39" s="39" t="s">
+        <v>1335</v>
+      </c>
+      <c r="W39" s="64" t="str">
+        <f t="shared" si="31"/>
+        <v>Key.ABNT.39</v>
+      </c>
+      <c r="X39" s="39" t="s">
+        <v>638</v>
+      </c>
+      <c r="Y39" s="39" t="s">
+        <v>638</v>
+      </c>
+      <c r="Z39" s="69" t="s">
+        <v>1420</v>
+      </c>
+      <c r="AA39" s="65" t="str">
+        <f t="shared" si="22"/>
+        <v>Equipment for Cleaning and Maintenance of Facades</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A7:A30">
-    <cfRule type="cellIs" dxfId="15" priority="10" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z20:Z30">
-    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1 AA7:AA30">
-    <cfRule type="cellIs" dxfId="9" priority="14" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A6">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+  <conditionalFormatting sqref="A2:A39">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="AA1:AA39">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:W1 A31:XFD1048576 AB1:XFD1 AB21:XFD30" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:W1 A40:XFD1048576 AB1:XFD1 AB22:XFD31 AB32:XFD39" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -8838,17 +9695,17 @@
   <cols>
     <col min="1" max="1" width="4.296875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.09765625" style="22" customWidth="1"/>
     <col min="4" max="4" width="10.19921875" style="22" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.69921875" style="22" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5" style="22" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.19921875" style="22" customWidth="1"/>
     <col min="8" max="8" width="5" style="22" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.796875" style="22" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5" style="22" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" style="22" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.09765625" style="22" customWidth="1"/>
+    <col min="11" max="11" width="9.69921875" style="22" customWidth="1"/>
     <col min="12" max="12" width="5.796875" style="22" customWidth="1"/>
-    <col min="13" max="13" width="28.69921875" style="22" customWidth="1"/>
+    <col min="13" max="13" width="19.796875" style="22" customWidth="1"/>
     <col min="14" max="14" width="7" style="22" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="49.19921875" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="7.796875" style="22" customWidth="1"/>
@@ -9050,7 +9907,7 @@
         <v>1314</v>
       </c>
       <c r="M3" s="49" t="s">
-        <v>1458</v>
+        <v>1442</v>
       </c>
       <c r="N3" s="54" t="s">
         <v>1</v>
@@ -9127,7 +9984,7 @@
         <v>1314</v>
       </c>
       <c r="M4" s="49" t="s">
-        <v>1459</v>
+        <v>1443</v>
       </c>
       <c r="N4" s="54" t="s">
         <v>1</v>
@@ -9174,7 +10031,7 @@
         <v>645</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D5" s="67" t="s">
         <v>1403</v>
@@ -9251,7 +10108,7 @@
         <v>646</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D6" s="67" t="s">
         <v>1403</v>
@@ -9328,7 +10185,7 @@
         <v>647</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D7" s="67" t="s">
         <v>1403</v>
@@ -9405,7 +10262,7 @@
         <v>648</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D8" s="67" t="s">
         <v>1403</v>
@@ -9482,7 +10339,7 @@
         <v>649</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D9" s="67" t="s">
         <v>1403</v>
@@ -9559,7 +10416,7 @@
         <v>650</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D10" s="67" t="s">
         <v>1403</v>
@@ -9636,7 +10493,7 @@
         <v>651</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D11" s="67" t="s">
         <v>1403</v>
@@ -9713,7 +10570,7 @@
         <v>652</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D12" s="67" t="s">
         <v>1403</v>
@@ -9790,7 +10647,7 @@
         <v>653</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D13" s="67" t="s">
         <v>1403</v>
@@ -9867,7 +10724,7 @@
         <v>654</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D14" s="67" t="s">
         <v>1403</v>
@@ -9944,7 +10801,7 @@
         <v>655</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D15" s="67" t="s">
         <v>1403</v>
@@ -10021,7 +10878,7 @@
         <v>656</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D16" s="67" t="s">
         <v>1403</v>
@@ -10098,7 +10955,7 @@
         <v>657</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D17" s="67" t="s">
         <v>1403</v>
@@ -10175,7 +11032,7 @@
         <v>658</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D18" s="67" t="s">
         <v>1403</v>
@@ -10252,7 +11109,7 @@
         <v>659</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D19" s="67" t="s">
         <v>1403</v>
@@ -10329,7 +11186,7 @@
         <v>660</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D20" s="67" t="s">
         <v>1403</v>
@@ -10406,7 +11263,7 @@
         <v>661</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D21" s="67" t="s">
         <v>1403</v>
@@ -10483,7 +11340,7 @@
         <v>662</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D22" s="67" t="s">
         <v>1403</v>
@@ -10560,7 +11417,7 @@
         <v>663</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D23" s="67" t="s">
         <v>1403</v>
@@ -10637,7 +11494,7 @@
         <v>664</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D24" s="67" t="s">
         <v>1403</v>
@@ -10714,7 +11571,7 @@
         <v>665</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D25" s="67" t="s">
         <v>1403</v>
@@ -10791,7 +11648,7 @@
         <v>666</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D26" s="67" t="s">
         <v>1403</v>
@@ -10868,7 +11725,7 @@
         <v>667</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D27" s="67" t="s">
         <v>1403</v>
@@ -10945,7 +11802,7 @@
         <v>668</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D28" s="67" t="s">
         <v>1403</v>
@@ -11022,7 +11879,7 @@
         <v>669</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D29" s="67" t="s">
         <v>1403</v>
@@ -11099,7 +11956,7 @@
         <v>1320</v>
       </c>
       <c r="C30" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D30" s="67" t="s">
         <v>1403</v>
@@ -11176,7 +12033,7 @@
         <v>670</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D31" s="67" t="s">
         <v>1403</v>
@@ -11253,7 +12110,7 @@
         <v>671</v>
       </c>
       <c r="C32" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D32" s="67" t="s">
         <v>1403</v>
@@ -11330,7 +12187,7 @@
         <v>672</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D33" s="67" t="s">
         <v>1403</v>
@@ -11407,7 +12264,7 @@
         <v>673</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D34" s="67" t="s">
         <v>1403</v>
@@ -11484,7 +12341,7 @@
         <v>674</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D35" s="67" t="s">
         <v>1403</v>
@@ -11561,7 +12418,7 @@
         <v>675</v>
       </c>
       <c r="C36" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D36" s="67" t="s">
         <v>1403</v>
@@ -11638,7 +12495,7 @@
         <v>676</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D37" s="67" t="s">
         <v>1403</v>
@@ -11715,7 +12572,7 @@
         <v>677</v>
       </c>
       <c r="C38" s="27" t="s">
-        <v>1416</v>
+        <v>1493</v>
       </c>
       <c r="D38" s="67" t="s">
         <v>1403</v>
@@ -11792,7 +12649,7 @@
         <v>678</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>1416</v>
+        <v>1497</v>
       </c>
       <c r="D39" s="67" t="s">
         <v>1403</v>
@@ -11869,7 +12726,7 @@
         <v>679</v>
       </c>
       <c r="C40" s="27" t="s">
-        <v>1416</v>
+        <v>1497</v>
       </c>
       <c r="D40" s="67" t="s">
         <v>1403</v>
@@ -11946,7 +12803,7 @@
         <v>680</v>
       </c>
       <c r="C41" s="27" t="s">
-        <v>1416</v>
+        <v>1497</v>
       </c>
       <c r="D41" s="67" t="s">
         <v>1403</v>
@@ -12023,7 +12880,7 @@
         <v>681</v>
       </c>
       <c r="C42" s="27" t="s">
-        <v>1416</v>
+        <v>1497</v>
       </c>
       <c r="D42" s="67" t="s">
         <v>1403</v>
@@ -12100,7 +12957,7 @@
         <v>682</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D43" s="67" t="s">
         <v>1403</v>
@@ -12177,7 +13034,7 @@
         <v>683</v>
       </c>
       <c r="C44" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D44" s="67" t="s">
         <v>1403</v>
@@ -12254,7 +13111,7 @@
         <v>684</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D45" s="67" t="s">
         <v>1403</v>
@@ -12331,7 +13188,7 @@
         <v>685</v>
       </c>
       <c r="C46" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D46" s="67" t="s">
         <v>1403</v>
@@ -12408,7 +13265,7 @@
         <v>686</v>
       </c>
       <c r="C47" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D47" s="67" t="s">
         <v>1403</v>
@@ -12485,7 +13342,7 @@
         <v>687</v>
       </c>
       <c r="C48" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D48" s="67" t="s">
         <v>1403</v>
@@ -12562,7 +13419,7 @@
         <v>688</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D49" s="67" t="s">
         <v>1403</v>
@@ -12639,7 +13496,7 @@
         <v>689</v>
       </c>
       <c r="C50" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D50" s="67" t="s">
         <v>1403</v>
@@ -12716,7 +13573,7 @@
         <v>690</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D51" s="67" t="s">
         <v>1403</v>
@@ -12793,7 +13650,7 @@
         <v>691</v>
       </c>
       <c r="C52" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D52" s="67" t="s">
         <v>1403</v>
@@ -12870,7 +13727,7 @@
         <v>692</v>
       </c>
       <c r="C53" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D53" s="67" t="s">
         <v>1403</v>
@@ -12947,7 +13804,7 @@
         <v>693</v>
       </c>
       <c r="C54" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D54" s="67" t="s">
         <v>1403</v>
@@ -13024,7 +13881,7 @@
         <v>694</v>
       </c>
       <c r="C55" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D55" s="67" t="s">
         <v>1403</v>
@@ -13101,7 +13958,7 @@
         <v>695</v>
       </c>
       <c r="C56" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D56" s="67" t="s">
         <v>1403</v>
@@ -13178,7 +14035,7 @@
         <v>696</v>
       </c>
       <c r="C57" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D57" s="67" t="s">
         <v>1403</v>
@@ -13255,7 +14112,7 @@
         <v>697</v>
       </c>
       <c r="C58" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D58" s="67" t="s">
         <v>1403</v>
@@ -13332,7 +14189,7 @@
         <v>698</v>
       </c>
       <c r="C59" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D59" s="67" t="s">
         <v>1403</v>
@@ -13409,7 +14266,7 @@
         <v>699</v>
       </c>
       <c r="C60" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D60" s="67" t="s">
         <v>1403</v>
@@ -13486,7 +14343,7 @@
         <v>700</v>
       </c>
       <c r="C61" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D61" s="67" t="s">
         <v>1403</v>
@@ -13563,7 +14420,7 @@
         <v>701</v>
       </c>
       <c r="C62" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D62" s="67" t="s">
         <v>1403</v>
@@ -13640,7 +14497,7 @@
         <v>702</v>
       </c>
       <c r="C63" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D63" s="67" t="s">
         <v>1403</v>
@@ -13717,7 +14574,7 @@
         <v>703</v>
       </c>
       <c r="C64" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D64" s="67" t="s">
         <v>1403</v>
@@ -13794,7 +14651,7 @@
         <v>704</v>
       </c>
       <c r="C65" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D65" s="67" t="s">
         <v>1403</v>
@@ -13871,7 +14728,7 @@
         <v>705</v>
       </c>
       <c r="C66" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D66" s="67" t="s">
         <v>1403</v>
@@ -13948,7 +14805,7 @@
         <v>706</v>
       </c>
       <c r="C67" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D67" s="67" t="s">
         <v>1403</v>
@@ -14025,7 +14882,7 @@
         <v>707</v>
       </c>
       <c r="C68" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D68" s="67" t="s">
         <v>1403</v>
@@ -14102,7 +14959,7 @@
         <v>708</v>
       </c>
       <c r="C69" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D69" s="67" t="s">
         <v>1403</v>
@@ -14179,7 +15036,7 @@
         <v>709</v>
       </c>
       <c r="C70" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D70" s="67" t="s">
         <v>1403</v>
@@ -14256,7 +15113,7 @@
         <v>710</v>
       </c>
       <c r="C71" s="27" t="s">
-        <v>1406</v>
+        <v>1494</v>
       </c>
       <c r="D71" s="67" t="s">
         <v>1403</v>
@@ -14333,7 +15190,7 @@
         <v>711</v>
       </c>
       <c r="C72" s="27" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="D72" s="67" t="s">
         <v>1403</v>
@@ -14410,7 +15267,7 @@
         <v>712</v>
       </c>
       <c r="C73" s="27" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="D73" s="67" t="s">
         <v>1403</v>
@@ -14487,7 +15344,7 @@
         <v>713</v>
       </c>
       <c r="C74" s="27" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="D74" s="67" t="s">
         <v>1403</v>
@@ -14564,7 +15421,7 @@
         <v>714</v>
       </c>
       <c r="C75" s="27" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="D75" s="67" t="s">
         <v>1403</v>
@@ -14641,7 +15498,7 @@
         <v>715</v>
       </c>
       <c r="C76" s="27" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="D76" s="67" t="s">
         <v>1403</v>
@@ -14718,7 +15575,7 @@
         <v>716</v>
       </c>
       <c r="C77" s="27" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="D77" s="67" t="s">
         <v>1403</v>
@@ -14795,7 +15652,7 @@
         <v>717</v>
       </c>
       <c r="C78" s="27" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="D78" s="67" t="s">
         <v>1403</v>
@@ -14872,7 +15729,7 @@
         <v>718</v>
       </c>
       <c r="C79" s="27" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="D79" s="67" t="s">
         <v>1403</v>
@@ -14949,7 +15806,7 @@
         <v>719</v>
       </c>
       <c r="C80" s="27" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="D80" s="67" t="s">
         <v>1403</v>
@@ -15026,7 +15883,7 @@
         <v>720</v>
       </c>
       <c r="C81" s="27" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="D81" s="67" t="s">
         <v>1403</v>
@@ -15103,7 +15960,7 @@
         <v>721</v>
       </c>
       <c r="C82" s="27" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="D82" s="67" t="s">
         <v>1403</v>
@@ -15180,7 +16037,7 @@
         <v>722</v>
       </c>
       <c r="C83" s="27" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="D83" s="67" t="s">
         <v>1403</v>
@@ -15257,7 +16114,7 @@
         <v>723</v>
       </c>
       <c r="C84" s="27" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="D84" s="67" t="s">
         <v>1403</v>
@@ -15334,7 +16191,7 @@
         <v>724</v>
       </c>
       <c r="C85" s="27" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="D85" s="67" t="s">
         <v>1403</v>
@@ -15411,7 +16268,7 @@
         <v>725</v>
       </c>
       <c r="C86" s="27" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="D86" s="67" t="s">
         <v>1403</v>
@@ -15488,7 +16345,7 @@
         <v>726</v>
       </c>
       <c r="C87" s="27" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="D87" s="67" t="s">
         <v>1403</v>
@@ -15565,7 +16422,7 @@
         <v>727</v>
       </c>
       <c r="C88" s="27" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="D88" s="67" t="s">
         <v>1403</v>
@@ -15642,7 +16499,7 @@
         <v>728</v>
       </c>
       <c r="C89" s="27" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="D89" s="67" t="s">
         <v>1403</v>
@@ -15719,7 +16576,7 @@
         <v>729</v>
       </c>
       <c r="C90" s="27" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="D90" s="67" t="s">
         <v>1403</v>
@@ -15796,7 +16653,7 @@
         <v>730</v>
       </c>
       <c r="C91" s="27" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="D91" s="67" t="s">
         <v>1403</v>
@@ -15873,7 +16730,7 @@
         <v>731</v>
       </c>
       <c r="C92" s="27" t="s">
-        <v>1415</v>
+        <v>1459</v>
       </c>
       <c r="D92" s="67" t="s">
         <v>1403</v>
@@ -15950,7 +16807,7 @@
         <v>732</v>
       </c>
       <c r="C93" s="27" t="s">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="D93" s="67" t="s">
         <v>1403</v>
@@ -16027,7 +16884,7 @@
         <v>733</v>
       </c>
       <c r="C94" s="27" t="s">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="D94" s="67" t="s">
         <v>1403</v>
@@ -16104,7 +16961,7 @@
         <v>734</v>
       </c>
       <c r="C95" s="27" t="s">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="D95" s="67" t="s">
         <v>1403</v>
@@ -16181,7 +17038,7 @@
         <v>735</v>
       </c>
       <c r="C96" s="27" t="s">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="D96" s="67" t="s">
         <v>1403</v>
@@ -16258,7 +17115,7 @@
         <v>736</v>
       </c>
       <c r="C97" s="27" t="s">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="D97" s="67" t="s">
         <v>1403</v>
@@ -16335,7 +17192,7 @@
         <v>737</v>
       </c>
       <c r="C98" s="27" t="s">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="D98" s="67" t="s">
         <v>1403</v>
@@ -16412,7 +17269,7 @@
         <v>738</v>
       </c>
       <c r="C99" s="27" t="s">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="D99" s="67" t="s">
         <v>1403</v>
@@ -16489,7 +17346,7 @@
         <v>739</v>
       </c>
       <c r="C100" s="27" t="s">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="D100" s="67" t="s">
         <v>1403</v>
@@ -16566,7 +17423,7 @@
         <v>740</v>
       </c>
       <c r="C101" s="27" t="s">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="D101" s="67" t="s">
         <v>1403</v>
@@ -16643,7 +17500,7 @@
         <v>741</v>
       </c>
       <c r="C102" s="27" t="s">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="D102" s="67" t="s">
         <v>1403</v>
@@ -16720,7 +17577,7 @@
         <v>742</v>
       </c>
       <c r="C103" s="27" t="s">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="D103" s="67" t="s">
         <v>1403</v>
@@ -16797,7 +17654,7 @@
         <v>743</v>
       </c>
       <c r="C104" s="27" t="s">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="D104" s="67" t="s">
         <v>1403</v>
@@ -16874,7 +17731,7 @@
         <v>744</v>
       </c>
       <c r="C105" s="27" t="s">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="D105" s="67" t="s">
         <v>1403</v>
@@ -16951,7 +17808,7 @@
         <v>745</v>
       </c>
       <c r="C106" s="27" t="s">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="D106" s="67" t="s">
         <v>1403</v>
@@ -17028,7 +17885,7 @@
         <v>746</v>
       </c>
       <c r="C107" s="27" t="s">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="D107" s="67" t="s">
         <v>1403</v>
@@ -17105,7 +17962,7 @@
         <v>747</v>
       </c>
       <c r="C108" s="27" t="s">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="D108" s="67" t="s">
         <v>1403</v>
@@ -17182,7 +18039,7 @@
         <v>748</v>
       </c>
       <c r="C109" s="27" t="s">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="D109" s="67" t="s">
         <v>1403</v>
@@ -17259,7 +18116,7 @@
         <v>749</v>
       </c>
       <c r="C110" s="27" t="s">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="D110" s="67" t="s">
         <v>1403</v>
@@ -17336,7 +18193,7 @@
         <v>750</v>
       </c>
       <c r="C111" s="27" t="s">
-        <v>1414</v>
+        <v>1460</v>
       </c>
       <c r="D111" s="67" t="s">
         <v>1403</v>
@@ -17413,7 +18270,7 @@
         <v>751</v>
       </c>
       <c r="C112" s="27" t="s">
-        <v>1413</v>
+        <v>1461</v>
       </c>
       <c r="D112" s="67" t="s">
         <v>1403</v>
@@ -17490,7 +18347,7 @@
         <v>752</v>
       </c>
       <c r="C113" s="27" t="s">
-        <v>1413</v>
+        <v>1461</v>
       </c>
       <c r="D113" s="67" t="s">
         <v>1403</v>
@@ -17567,7 +18424,7 @@
         <v>753</v>
       </c>
       <c r="C114" s="27" t="s">
-        <v>1413</v>
+        <v>1461</v>
       </c>
       <c r="D114" s="67" t="s">
         <v>1403</v>
@@ -17644,7 +18501,7 @@
         <v>754</v>
       </c>
       <c r="C115" s="27" t="s">
-        <v>1413</v>
+        <v>1461</v>
       </c>
       <c r="D115" s="67" t="s">
         <v>1403</v>
@@ -17721,7 +18578,7 @@
         <v>755</v>
       </c>
       <c r="C116" s="27" t="s">
-        <v>1413</v>
+        <v>1461</v>
       </c>
       <c r="D116" s="67" t="s">
         <v>1403</v>
@@ -17798,7 +18655,7 @@
         <v>756</v>
       </c>
       <c r="C117" s="27" t="s">
-        <v>1413</v>
+        <v>1461</v>
       </c>
       <c r="D117" s="67" t="s">
         <v>1403</v>
@@ -17875,7 +18732,7 @@
         <v>757</v>
       </c>
       <c r="C118" s="27" t="s">
-        <v>1413</v>
+        <v>1461</v>
       </c>
       <c r="D118" s="67" t="s">
         <v>1403</v>
@@ -17952,7 +18809,7 @@
         <v>758</v>
       </c>
       <c r="C119" s="27" t="s">
-        <v>1413</v>
+        <v>1461</v>
       </c>
       <c r="D119" s="67" t="s">
         <v>1403</v>
@@ -18029,7 +18886,7 @@
         <v>759</v>
       </c>
       <c r="C120" s="27" t="s">
-        <v>1413</v>
+        <v>1461</v>
       </c>
       <c r="D120" s="67" t="s">
         <v>1403</v>
@@ -18106,7 +18963,7 @@
         <v>760</v>
       </c>
       <c r="C121" s="27" t="s">
-        <v>1413</v>
+        <v>1461</v>
       </c>
       <c r="D121" s="67" t="s">
         <v>1403</v>
@@ -18183,7 +19040,7 @@
         <v>761</v>
       </c>
       <c r="C122" s="27" t="s">
-        <v>1413</v>
+        <v>1461</v>
       </c>
       <c r="D122" s="67" t="s">
         <v>1403</v>
@@ -18260,7 +19117,7 @@
         <v>762</v>
       </c>
       <c r="C123" s="27" t="s">
-        <v>1413</v>
+        <v>1461</v>
       </c>
       <c r="D123" s="67" t="s">
         <v>1403</v>
@@ -18337,7 +19194,7 @@
         <v>763</v>
       </c>
       <c r="C124" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D124" s="67" t="s">
         <v>1403</v>
@@ -18414,7 +19271,7 @@
         <v>1321</v>
       </c>
       <c r="C125" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D125" s="67" t="s">
         <v>1403</v>
@@ -18491,7 +19348,7 @@
         <v>1322</v>
       </c>
       <c r="C126" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D126" s="67" t="s">
         <v>1403</v>
@@ -18568,7 +19425,7 @@
         <v>764</v>
       </c>
       <c r="C127" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D127" s="67" t="s">
         <v>1403</v>
@@ -18645,7 +19502,7 @@
         <v>765</v>
       </c>
       <c r="C128" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D128" s="67" t="s">
         <v>1403</v>
@@ -18722,7 +19579,7 @@
         <v>766</v>
       </c>
       <c r="C129" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D129" s="67" t="s">
         <v>1403</v>
@@ -18799,7 +19656,7 @@
         <v>767</v>
       </c>
       <c r="C130" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D130" s="67" t="s">
         <v>1403</v>
@@ -18876,7 +19733,7 @@
         <v>768</v>
       </c>
       <c r="C131" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D131" s="67" t="s">
         <v>1403</v>
@@ -18953,7 +19810,7 @@
         <v>769</v>
       </c>
       <c r="C132" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D132" s="67" t="s">
         <v>1403</v>
@@ -19030,7 +19887,7 @@
         <v>770</v>
       </c>
       <c r="C133" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D133" s="67" t="s">
         <v>1403</v>
@@ -19107,7 +19964,7 @@
         <v>771</v>
       </c>
       <c r="C134" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D134" s="67" t="s">
         <v>1403</v>
@@ -19184,7 +20041,7 @@
         <v>772</v>
       </c>
       <c r="C135" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D135" s="67" t="s">
         <v>1403</v>
@@ -19261,7 +20118,7 @@
         <v>773</v>
       </c>
       <c r="C136" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D136" s="67" t="s">
         <v>1403</v>
@@ -19338,7 +20195,7 @@
         <v>774</v>
       </c>
       <c r="C137" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D137" s="67" t="s">
         <v>1403</v>
@@ -19415,7 +20272,7 @@
         <v>775</v>
       </c>
       <c r="C138" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D138" s="67" t="s">
         <v>1403</v>
@@ -19492,7 +20349,7 @@
         <v>776</v>
       </c>
       <c r="C139" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D139" s="67" t="s">
         <v>1403</v>
@@ -19569,7 +20426,7 @@
         <v>777</v>
       </c>
       <c r="C140" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D140" s="67" t="s">
         <v>1403</v>
@@ -19646,7 +20503,7 @@
         <v>778</v>
       </c>
       <c r="C141" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D141" s="67" t="s">
         <v>1403</v>
@@ -19723,7 +20580,7 @@
         <v>779</v>
       </c>
       <c r="C142" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D142" s="67" t="s">
         <v>1403</v>
@@ -19800,7 +20657,7 @@
         <v>780</v>
       </c>
       <c r="C143" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D143" s="67" t="s">
         <v>1403</v>
@@ -19877,7 +20734,7 @@
         <v>781</v>
       </c>
       <c r="C144" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D144" s="67" t="s">
         <v>1403</v>
@@ -19954,7 +20811,7 @@
         <v>782</v>
       </c>
       <c r="C145" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D145" s="67" t="s">
         <v>1403</v>
@@ -20031,7 +20888,7 @@
         <v>783</v>
       </c>
       <c r="C146" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D146" s="67" t="s">
         <v>1403</v>
@@ -20108,7 +20965,7 @@
         <v>784</v>
       </c>
       <c r="C147" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D147" s="67" t="s">
         <v>1403</v>
@@ -20185,7 +21042,7 @@
         <v>785</v>
       </c>
       <c r="C148" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D148" s="67" t="s">
         <v>1403</v>
@@ -20262,7 +21119,7 @@
         <v>786</v>
       </c>
       <c r="C149" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D149" s="67" t="s">
         <v>1403</v>
@@ -20339,7 +21196,7 @@
         <v>787</v>
       </c>
       <c r="C150" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D150" s="67" t="s">
         <v>1403</v>
@@ -20416,7 +21273,7 @@
         <v>788</v>
       </c>
       <c r="C151" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D151" s="67" t="s">
         <v>1403</v>
@@ -20493,7 +21350,7 @@
         <v>789</v>
       </c>
       <c r="C152" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D152" s="67" t="s">
         <v>1403</v>
@@ -20570,7 +21427,7 @@
         <v>790</v>
       </c>
       <c r="C153" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D153" s="67" t="s">
         <v>1403</v>
@@ -20647,7 +21504,7 @@
         <v>791</v>
       </c>
       <c r="C154" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D154" s="67" t="s">
         <v>1403</v>
@@ -20724,7 +21581,7 @@
         <v>792</v>
       </c>
       <c r="C155" s="27" t="s">
-        <v>1412</v>
+        <v>1451</v>
       </c>
       <c r="D155" s="67" t="s">
         <v>1403</v>
@@ -20801,7 +21658,7 @@
         <v>793</v>
       </c>
       <c r="C156" s="27" t="s">
-        <v>1412</v>
+        <v>1453</v>
       </c>
       <c r="D156" s="67" t="s">
         <v>1403</v>
@@ -20831,7 +21688,7 @@
         <v>1314</v>
       </c>
       <c r="M156" s="49" t="s">
-        <v>1394</v>
+        <v>1462</v>
       </c>
       <c r="N156" s="54" t="s">
         <v>1</v>
@@ -20878,7 +21735,7 @@
         <v>794</v>
       </c>
       <c r="C157" s="27" t="s">
-        <v>1412</v>
+        <v>1453</v>
       </c>
       <c r="D157" s="67" t="s">
         <v>1403</v>
@@ -20908,7 +21765,7 @@
         <v>1314</v>
       </c>
       <c r="M157" s="49" t="s">
-        <v>1394</v>
+        <v>1462</v>
       </c>
       <c r="N157" s="54" t="s">
         <v>1</v>
@@ -20955,7 +21812,7 @@
         <v>795</v>
       </c>
       <c r="C158" s="27" t="s">
-        <v>1412</v>
+        <v>1453</v>
       </c>
       <c r="D158" s="67" t="s">
         <v>1403</v>
@@ -20985,7 +21842,7 @@
         <v>1314</v>
       </c>
       <c r="M158" s="49" t="s">
-        <v>1394</v>
+        <v>1462</v>
       </c>
       <c r="N158" s="54" t="s">
         <v>1</v>
@@ -21032,7 +21889,7 @@
         <v>796</v>
       </c>
       <c r="C159" s="27" t="s">
-        <v>1412</v>
+        <v>1453</v>
       </c>
       <c r="D159" s="67" t="s">
         <v>1403</v>
@@ -21062,7 +21919,7 @@
         <v>1314</v>
       </c>
       <c r="M159" s="49" t="s">
-        <v>1394</v>
+        <v>1462</v>
       </c>
       <c r="N159" s="54" t="s">
         <v>1</v>
@@ -21109,7 +21966,7 @@
         <v>797</v>
       </c>
       <c r="C160" s="27" t="s">
-        <v>1412</v>
+        <v>1453</v>
       </c>
       <c r="D160" s="67" t="s">
         <v>1403</v>
@@ -21139,7 +21996,7 @@
         <v>1314</v>
       </c>
       <c r="M160" s="49" t="s">
-        <v>1394</v>
+        <v>1462</v>
       </c>
       <c r="N160" s="54" t="s">
         <v>1</v>
@@ -21186,7 +22043,7 @@
         <v>798</v>
       </c>
       <c r="C161" s="27" t="s">
-        <v>1412</v>
+        <v>1453</v>
       </c>
       <c r="D161" s="67" t="s">
         <v>1403</v>
@@ -21216,7 +22073,7 @@
         <v>1314</v>
       </c>
       <c r="M161" s="49" t="s">
-        <v>1394</v>
+        <v>1462</v>
       </c>
       <c r="N161" s="54" t="s">
         <v>1</v>
@@ -21263,7 +22120,7 @@
         <v>799</v>
       </c>
       <c r="C162" s="27" t="s">
-        <v>1412</v>
+        <v>1454</v>
       </c>
       <c r="D162" s="67" t="s">
         <v>1403</v>
@@ -21293,7 +22150,7 @@
         <v>1314</v>
       </c>
       <c r="M162" s="49" t="s">
-        <v>1394</v>
+        <v>1463</v>
       </c>
       <c r="N162" s="54" t="s">
         <v>1</v>
@@ -21340,7 +22197,7 @@
         <v>800</v>
       </c>
       <c r="C163" s="27" t="s">
-        <v>1412</v>
+        <v>1454</v>
       </c>
       <c r="D163" s="67" t="s">
         <v>1403</v>
@@ -21370,7 +22227,7 @@
         <v>1314</v>
       </c>
       <c r="M163" s="49" t="s">
-        <v>1394</v>
+        <v>1463</v>
       </c>
       <c r="N163" s="54" t="s">
         <v>1</v>
@@ -21417,7 +22274,7 @@
         <v>801</v>
       </c>
       <c r="C164" s="27" t="s">
-        <v>1412</v>
+        <v>1454</v>
       </c>
       <c r="D164" s="67" t="s">
         <v>1403</v>
@@ -21447,7 +22304,7 @@
         <v>1314</v>
       </c>
       <c r="M164" s="49" t="s">
-        <v>1394</v>
+        <v>1463</v>
       </c>
       <c r="N164" s="54" t="s">
         <v>1</v>
@@ -21494,7 +22351,7 @@
         <v>802</v>
       </c>
       <c r="C165" s="27" t="s">
-        <v>1412</v>
+        <v>1454</v>
       </c>
       <c r="D165" s="67" t="s">
         <v>1403</v>
@@ -21524,7 +22381,7 @@
         <v>1314</v>
       </c>
       <c r="M165" s="49" t="s">
-        <v>1394</v>
+        <v>1463</v>
       </c>
       <c r="N165" s="54" t="s">
         <v>1</v>
@@ -21571,7 +22428,7 @@
         <v>803</v>
       </c>
       <c r="C166" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D166" s="67" t="s">
         <v>1403</v>
@@ -21601,7 +22458,7 @@
         <v>1314</v>
       </c>
       <c r="M166" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N166" s="54" t="s">
         <v>1</v>
@@ -21648,7 +22505,7 @@
         <v>804</v>
       </c>
       <c r="C167" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D167" s="67" t="s">
         <v>1403</v>
@@ -21678,7 +22535,7 @@
         <v>1314</v>
       </c>
       <c r="M167" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N167" s="54" t="s">
         <v>1</v>
@@ -21725,7 +22582,7 @@
         <v>805</v>
       </c>
       <c r="C168" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D168" s="67" t="s">
         <v>1403</v>
@@ -21755,7 +22612,7 @@
         <v>1314</v>
       </c>
       <c r="M168" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N168" s="54" t="s">
         <v>1</v>
@@ -21802,7 +22659,7 @@
         <v>806</v>
       </c>
       <c r="C169" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D169" s="67" t="s">
         <v>1403</v>
@@ -21832,7 +22689,7 @@
         <v>1314</v>
       </c>
       <c r="M169" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N169" s="54" t="s">
         <v>1</v>
@@ -21879,7 +22736,7 @@
         <v>807</v>
       </c>
       <c r="C170" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D170" s="67" t="s">
         <v>1403</v>
@@ -21909,7 +22766,7 @@
         <v>1314</v>
       </c>
       <c r="M170" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N170" s="54" t="s">
         <v>1</v>
@@ -21956,7 +22813,7 @@
         <v>808</v>
       </c>
       <c r="C171" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D171" s="67" t="s">
         <v>1403</v>
@@ -21986,7 +22843,7 @@
         <v>1314</v>
       </c>
       <c r="M171" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N171" s="54" t="s">
         <v>1</v>
@@ -22033,7 +22890,7 @@
         <v>809</v>
       </c>
       <c r="C172" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D172" s="67" t="s">
         <v>1403</v>
@@ -22063,7 +22920,7 @@
         <v>1314</v>
       </c>
       <c r="M172" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N172" s="54" t="s">
         <v>1</v>
@@ -22110,7 +22967,7 @@
         <v>810</v>
       </c>
       <c r="C173" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D173" s="67" t="s">
         <v>1403</v>
@@ -22140,7 +22997,7 @@
         <v>1314</v>
       </c>
       <c r="M173" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N173" s="54" t="s">
         <v>1</v>
@@ -22187,7 +23044,7 @@
         <v>811</v>
       </c>
       <c r="C174" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D174" s="67" t="s">
         <v>1403</v>
@@ -22217,7 +23074,7 @@
         <v>1314</v>
       </c>
       <c r="M174" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N174" s="54" t="s">
         <v>1</v>
@@ -22264,7 +23121,7 @@
         <v>812</v>
       </c>
       <c r="C175" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D175" s="67" t="s">
         <v>1403</v>
@@ -22294,7 +23151,7 @@
         <v>1314</v>
       </c>
       <c r="M175" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N175" s="54" t="s">
         <v>1</v>
@@ -22341,7 +23198,7 @@
         <v>813</v>
       </c>
       <c r="C176" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D176" s="67" t="s">
         <v>1403</v>
@@ -22371,7 +23228,7 @@
         <v>1314</v>
       </c>
       <c r="M176" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N176" s="54" t="s">
         <v>1</v>
@@ -22418,7 +23275,7 @@
         <v>814</v>
       </c>
       <c r="C177" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D177" s="67" t="s">
         <v>1403</v>
@@ -22448,7 +23305,7 @@
         <v>1314</v>
       </c>
       <c r="M177" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N177" s="54" t="s">
         <v>1</v>
@@ -22495,7 +23352,7 @@
         <v>815</v>
       </c>
       <c r="C178" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D178" s="67" t="s">
         <v>1403</v>
@@ -22525,7 +23382,7 @@
         <v>1314</v>
       </c>
       <c r="M178" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N178" s="54" t="s">
         <v>1</v>
@@ -22572,7 +23429,7 @@
         <v>816</v>
       </c>
       <c r="C179" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D179" s="67" t="s">
         <v>1403</v>
@@ -22602,7 +23459,7 @@
         <v>1314</v>
       </c>
       <c r="M179" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N179" s="54" t="s">
         <v>1</v>
@@ -22649,7 +23506,7 @@
         <v>817</v>
       </c>
       <c r="C180" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D180" s="67" t="s">
         <v>1403</v>
@@ -22679,7 +23536,7 @@
         <v>1314</v>
       </c>
       <c r="M180" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N180" s="54" t="s">
         <v>1</v>
@@ -22726,7 +23583,7 @@
         <v>818</v>
       </c>
       <c r="C181" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D181" s="67" t="s">
         <v>1403</v>
@@ -22756,7 +23613,7 @@
         <v>1314</v>
       </c>
       <c r="M181" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N181" s="54" t="s">
         <v>1</v>
@@ -22803,7 +23660,7 @@
         <v>819</v>
       </c>
       <c r="C182" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D182" s="67" t="s">
         <v>1403</v>
@@ -22833,7 +23690,7 @@
         <v>1314</v>
       </c>
       <c r="M182" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N182" s="54" t="s">
         <v>1</v>
@@ -22880,7 +23737,7 @@
         <v>820</v>
       </c>
       <c r="C183" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D183" s="67" t="s">
         <v>1403</v>
@@ -22910,7 +23767,7 @@
         <v>1314</v>
       </c>
       <c r="M183" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N183" s="54" t="s">
         <v>1</v>
@@ -22957,7 +23814,7 @@
         <v>821</v>
       </c>
       <c r="C184" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D184" s="67" t="s">
         <v>1403</v>
@@ -22987,7 +23844,7 @@
         <v>1314</v>
       </c>
       <c r="M184" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N184" s="54" t="s">
         <v>1</v>
@@ -23034,7 +23891,7 @@
         <v>822</v>
       </c>
       <c r="C185" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D185" s="67" t="s">
         <v>1403</v>
@@ -23064,7 +23921,7 @@
         <v>1314</v>
       </c>
       <c r="M185" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N185" s="54" t="s">
         <v>1</v>
@@ -23111,7 +23968,7 @@
         <v>823</v>
       </c>
       <c r="C186" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D186" s="67" t="s">
         <v>1403</v>
@@ -23141,7 +23998,7 @@
         <v>1314</v>
       </c>
       <c r="M186" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N186" s="54" t="s">
         <v>1</v>
@@ -23188,7 +24045,7 @@
         <v>824</v>
       </c>
       <c r="C187" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D187" s="67" t="s">
         <v>1403</v>
@@ -23218,7 +24075,7 @@
         <v>1314</v>
       </c>
       <c r="M187" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N187" s="54" t="s">
         <v>1</v>
@@ -23265,7 +24122,7 @@
         <v>825</v>
       </c>
       <c r="C188" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D188" s="67" t="s">
         <v>1403</v>
@@ -23295,7 +24152,7 @@
         <v>1314</v>
       </c>
       <c r="M188" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N188" s="54" t="s">
         <v>1</v>
@@ -23342,7 +24199,7 @@
         <v>826</v>
       </c>
       <c r="C189" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D189" s="67" t="s">
         <v>1403</v>
@@ -23372,7 +24229,7 @@
         <v>1314</v>
       </c>
       <c r="M189" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N189" s="54" t="s">
         <v>1</v>
@@ -23419,7 +24276,7 @@
         <v>827</v>
       </c>
       <c r="C190" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D190" s="67" t="s">
         <v>1403</v>
@@ -23449,7 +24306,7 @@
         <v>1314</v>
       </c>
       <c r="M190" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N190" s="54" t="s">
         <v>1</v>
@@ -23496,7 +24353,7 @@
         <v>828</v>
       </c>
       <c r="C191" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D191" s="67" t="s">
         <v>1403</v>
@@ -23526,7 +24383,7 @@
         <v>1314</v>
       </c>
       <c r="M191" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N191" s="54" t="s">
         <v>1</v>
@@ -23573,7 +24430,7 @@
         <v>829</v>
       </c>
       <c r="C192" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D192" s="67" t="s">
         <v>1403</v>
@@ -23603,7 +24460,7 @@
         <v>1314</v>
       </c>
       <c r="M192" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N192" s="54" t="s">
         <v>1</v>
@@ -23650,7 +24507,7 @@
         <v>830</v>
       </c>
       <c r="C193" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D193" s="67" t="s">
         <v>1403</v>
@@ -23680,7 +24537,7 @@
         <v>1314</v>
       </c>
       <c r="M193" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N193" s="54" t="s">
         <v>1</v>
@@ -23727,7 +24584,7 @@
         <v>831</v>
       </c>
       <c r="C194" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D194" s="67" t="s">
         <v>1403</v>
@@ -23757,7 +24614,7 @@
         <v>1314</v>
       </c>
       <c r="M194" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N194" s="54" t="s">
         <v>1</v>
@@ -23804,7 +24661,7 @@
         <v>832</v>
       </c>
       <c r="C195" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D195" s="67" t="s">
         <v>1403</v>
@@ -23834,7 +24691,7 @@
         <v>1314</v>
       </c>
       <c r="M195" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N195" s="54" t="s">
         <v>1</v>
@@ -23881,7 +24738,7 @@
         <v>833</v>
       </c>
       <c r="C196" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D196" s="67" t="s">
         <v>1403</v>
@@ -23911,7 +24768,7 @@
         <v>1314</v>
       </c>
       <c r="M196" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N196" s="54" t="s">
         <v>1</v>
@@ -23958,7 +24815,7 @@
         <v>834</v>
       </c>
       <c r="C197" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D197" s="67" t="s">
         <v>1403</v>
@@ -23988,7 +24845,7 @@
         <v>1314</v>
       </c>
       <c r="M197" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N197" s="54" t="s">
         <v>1</v>
@@ -24035,7 +24892,7 @@
         <v>835</v>
       </c>
       <c r="C198" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D198" s="67" t="s">
         <v>1403</v>
@@ -24065,7 +24922,7 @@
         <v>1314</v>
       </c>
       <c r="M198" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N198" s="54" t="s">
         <v>1</v>
@@ -24112,7 +24969,7 @@
         <v>836</v>
       </c>
       <c r="C199" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D199" s="67" t="s">
         <v>1403</v>
@@ -24142,7 +24999,7 @@
         <v>1314</v>
       </c>
       <c r="M199" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N199" s="54" t="s">
         <v>1</v>
@@ -24189,7 +25046,7 @@
         <v>837</v>
       </c>
       <c r="C200" s="27" t="s">
-        <v>1412</v>
+        <v>1455</v>
       </c>
       <c r="D200" s="67" t="s">
         <v>1403</v>
@@ -24219,7 +25076,7 @@
         <v>1314</v>
       </c>
       <c r="M200" s="49" t="s">
-        <v>1394</v>
+        <v>179</v>
       </c>
       <c r="N200" s="54" t="s">
         <v>1</v>
@@ -24266,7 +25123,7 @@
         <v>838</v>
       </c>
       <c r="C201" s="27" t="s">
-        <v>1412</v>
+        <v>1456</v>
       </c>
       <c r="D201" s="67" t="s">
         <v>1403</v>
@@ -24296,7 +25153,7 @@
         <v>1314</v>
       </c>
       <c r="M201" s="49" t="s">
-        <v>1394</v>
+        <v>1464</v>
       </c>
       <c r="N201" s="54" t="s">
         <v>1</v>
@@ -24343,7 +25200,7 @@
         <v>839</v>
       </c>
       <c r="C202" s="27" t="s">
-        <v>1412</v>
+        <v>1456</v>
       </c>
       <c r="D202" s="67" t="s">
         <v>1403</v>
@@ -24373,7 +25230,7 @@
         <v>1314</v>
       </c>
       <c r="M202" s="49" t="s">
-        <v>1394</v>
+        <v>1464</v>
       </c>
       <c r="N202" s="54" t="s">
         <v>1</v>
@@ -24420,7 +25277,7 @@
         <v>840</v>
       </c>
       <c r="C203" s="27" t="s">
-        <v>1412</v>
+        <v>1456</v>
       </c>
       <c r="D203" s="67" t="s">
         <v>1403</v>
@@ -24450,7 +25307,7 @@
         <v>1314</v>
       </c>
       <c r="M203" s="49" t="s">
-        <v>1394</v>
+        <v>1464</v>
       </c>
       <c r="N203" s="54" t="s">
         <v>1</v>
@@ -24497,7 +25354,7 @@
         <v>841</v>
       </c>
       <c r="C204" s="27" t="s">
-        <v>1412</v>
+        <v>1456</v>
       </c>
       <c r="D204" s="67" t="s">
         <v>1403</v>
@@ -24527,7 +25384,7 @@
         <v>1314</v>
       </c>
       <c r="M204" s="49" t="s">
-        <v>1394</v>
+        <v>1464</v>
       </c>
       <c r="N204" s="54" t="s">
         <v>1</v>
@@ -24574,7 +25431,7 @@
         <v>842</v>
       </c>
       <c r="C205" s="27" t="s">
-        <v>1412</v>
+        <v>1456</v>
       </c>
       <c r="D205" s="67" t="s">
         <v>1403</v>
@@ -24604,7 +25461,7 @@
         <v>1314</v>
       </c>
       <c r="M205" s="49" t="s">
-        <v>1394</v>
+        <v>1464</v>
       </c>
       <c r="N205" s="54" t="s">
         <v>1</v>
@@ -24651,7 +25508,7 @@
         <v>843</v>
       </c>
       <c r="C206" s="27" t="s">
-        <v>1412</v>
+        <v>1456</v>
       </c>
       <c r="D206" s="67" t="s">
         <v>1403</v>
@@ -24681,7 +25538,7 @@
         <v>1314</v>
       </c>
       <c r="M206" s="49" t="s">
-        <v>1394</v>
+        <v>1464</v>
       </c>
       <c r="N206" s="54" t="s">
         <v>1</v>
@@ -24728,7 +25585,7 @@
         <v>844</v>
       </c>
       <c r="C207" s="27" t="s">
-        <v>1412</v>
+        <v>1456</v>
       </c>
       <c r="D207" s="67" t="s">
         <v>1403</v>
@@ -24758,7 +25615,7 @@
         <v>1314</v>
       </c>
       <c r="M207" s="49" t="s">
-        <v>1394</v>
+        <v>1464</v>
       </c>
       <c r="N207" s="54" t="s">
         <v>1</v>
@@ -24805,7 +25662,7 @@
         <v>845</v>
       </c>
       <c r="C208" s="27" t="s">
-        <v>1412</v>
+        <v>1456</v>
       </c>
       <c r="D208" s="67" t="s">
         <v>1403</v>
@@ -24835,7 +25692,7 @@
         <v>1314</v>
       </c>
       <c r="M208" s="49" t="s">
-        <v>1394</v>
+        <v>1464</v>
       </c>
       <c r="N208" s="54" t="s">
         <v>1</v>
@@ -24882,7 +25739,7 @@
         <v>846</v>
       </c>
       <c r="C209" s="27" t="s">
-        <v>1412</v>
+        <v>1456</v>
       </c>
       <c r="D209" s="67" t="s">
         <v>1403</v>
@@ -24912,7 +25769,7 @@
         <v>1314</v>
       </c>
       <c r="M209" s="49" t="s">
-        <v>1394</v>
+        <v>1464</v>
       </c>
       <c r="N209" s="54" t="s">
         <v>1</v>
@@ -24959,7 +25816,7 @@
         <v>847</v>
       </c>
       <c r="C210" s="27" t="s">
-        <v>1412</v>
+        <v>1456</v>
       </c>
       <c r="D210" s="67" t="s">
         <v>1403</v>
@@ -24989,7 +25846,7 @@
         <v>1314</v>
       </c>
       <c r="M210" s="49" t="s">
-        <v>1394</v>
+        <v>1464</v>
       </c>
       <c r="N210" s="54" t="s">
         <v>1</v>
@@ -25036,7 +25893,7 @@
         <v>848</v>
       </c>
       <c r="C211" s="27" t="s">
-        <v>1412</v>
+        <v>1456</v>
       </c>
       <c r="D211" s="67" t="s">
         <v>1403</v>
@@ -25066,7 +25923,7 @@
         <v>1314</v>
       </c>
       <c r="M211" s="49" t="s">
-        <v>1394</v>
+        <v>1464</v>
       </c>
       <c r="N211" s="54" t="s">
         <v>1</v>
@@ -25113,7 +25970,7 @@
         <v>849</v>
       </c>
       <c r="C212" s="27" t="s">
-        <v>1412</v>
+        <v>1456</v>
       </c>
       <c r="D212" s="67" t="s">
         <v>1403</v>
@@ -25143,7 +26000,7 @@
         <v>1314</v>
       </c>
       <c r="M212" s="49" t="s">
-        <v>1394</v>
+        <v>1464</v>
       </c>
       <c r="N212" s="54" t="s">
         <v>1</v>
@@ -25190,7 +26047,7 @@
         <v>850</v>
       </c>
       <c r="C213" s="27" t="s">
-        <v>1412</v>
+        <v>1456</v>
       </c>
       <c r="D213" s="67" t="s">
         <v>1403</v>
@@ -25220,7 +26077,7 @@
         <v>1314</v>
       </c>
       <c r="M213" s="49" t="s">
-        <v>1394</v>
+        <v>1464</v>
       </c>
       <c r="N213" s="54" t="s">
         <v>1</v>
@@ -25267,7 +26124,7 @@
         <v>851</v>
       </c>
       <c r="C214" s="27" t="s">
-        <v>1412</v>
+        <v>1457</v>
       </c>
       <c r="D214" s="67" t="s">
         <v>1403</v>
@@ -25297,7 +26154,7 @@
         <v>1314</v>
       </c>
       <c r="M214" s="49" t="s">
-        <v>1394</v>
+        <v>1465</v>
       </c>
       <c r="N214" s="54" t="s">
         <v>1</v>
@@ -25344,7 +26201,7 @@
         <v>852</v>
       </c>
       <c r="C215" s="27" t="s">
-        <v>1412</v>
+        <v>1457</v>
       </c>
       <c r="D215" s="67" t="s">
         <v>1403</v>
@@ -25374,7 +26231,7 @@
         <v>1314</v>
       </c>
       <c r="M215" s="49" t="s">
-        <v>1394</v>
+        <v>1465</v>
       </c>
       <c r="N215" s="54" t="s">
         <v>1</v>
@@ -25421,7 +26278,7 @@
         <v>853</v>
       </c>
       <c r="C216" s="27" t="s">
-        <v>1412</v>
+        <v>1457</v>
       </c>
       <c r="D216" s="67" t="s">
         <v>1403</v>
@@ -25451,7 +26308,7 @@
         <v>1314</v>
       </c>
       <c r="M216" s="49" t="s">
-        <v>1394</v>
+        <v>1465</v>
       </c>
       <c r="N216" s="54" t="s">
         <v>1</v>
@@ -25498,7 +26355,7 @@
         <v>854</v>
       </c>
       <c r="C217" s="27" t="s">
-        <v>1412</v>
+        <v>1457</v>
       </c>
       <c r="D217" s="67" t="s">
         <v>1403</v>
@@ -25528,7 +26385,7 @@
         <v>1314</v>
       </c>
       <c r="M217" s="49" t="s">
-        <v>1394</v>
+        <v>1465</v>
       </c>
       <c r="N217" s="54" t="s">
         <v>1</v>
@@ -25575,7 +26432,7 @@
         <v>855</v>
       </c>
       <c r="C218" s="27" t="s">
-        <v>1412</v>
+        <v>1457</v>
       </c>
       <c r="D218" s="67" t="s">
         <v>1403</v>
@@ -25605,7 +26462,7 @@
         <v>1314</v>
       </c>
       <c r="M218" s="49" t="s">
-        <v>1394</v>
+        <v>1465</v>
       </c>
       <c r="N218" s="54" t="s">
         <v>1</v>
@@ -25652,7 +26509,7 @@
         <v>856</v>
       </c>
       <c r="C219" s="27" t="s">
-        <v>1412</v>
+        <v>1457</v>
       </c>
       <c r="D219" s="67" t="s">
         <v>1403</v>
@@ -25682,7 +26539,7 @@
         <v>1314</v>
       </c>
       <c r="M219" s="49" t="s">
-        <v>1394</v>
+        <v>1465</v>
       </c>
       <c r="N219" s="54" t="s">
         <v>1</v>
@@ -25729,7 +26586,7 @@
         <v>857</v>
       </c>
       <c r="C220" s="27" t="s">
-        <v>1412</v>
+        <v>1457</v>
       </c>
       <c r="D220" s="67" t="s">
         <v>1403</v>
@@ -25759,7 +26616,7 @@
         <v>1314</v>
       </c>
       <c r="M220" s="49" t="s">
-        <v>1394</v>
+        <v>1465</v>
       </c>
       <c r="N220" s="54" t="s">
         <v>1</v>
@@ -25806,7 +26663,7 @@
         <v>858</v>
       </c>
       <c r="C221" s="27" t="s">
-        <v>1412</v>
+        <v>1457</v>
       </c>
       <c r="D221" s="67" t="s">
         <v>1403</v>
@@ -25836,7 +26693,7 @@
         <v>1314</v>
       </c>
       <c r="M221" s="49" t="s">
-        <v>1394</v>
+        <v>1465</v>
       </c>
       <c r="N221" s="54" t="s">
         <v>1</v>
@@ -25883,7 +26740,7 @@
         <v>859</v>
       </c>
       <c r="C222" s="27" t="s">
-        <v>1412</v>
+        <v>1457</v>
       </c>
       <c r="D222" s="67" t="s">
         <v>1403</v>
@@ -25913,7 +26770,7 @@
         <v>1314</v>
       </c>
       <c r="M222" s="49" t="s">
-        <v>1394</v>
+        <v>1465</v>
       </c>
       <c r="N222" s="54" t="s">
         <v>1</v>
@@ -25960,7 +26817,7 @@
         <v>860</v>
       </c>
       <c r="C223" s="27" t="s">
-        <v>1412</v>
+        <v>1457</v>
       </c>
       <c r="D223" s="67" t="s">
         <v>1403</v>
@@ -25990,7 +26847,7 @@
         <v>1314</v>
       </c>
       <c r="M223" s="49" t="s">
-        <v>1394</v>
+        <v>1465</v>
       </c>
       <c r="N223" s="54" t="s">
         <v>1</v>
@@ -26037,7 +26894,7 @@
         <v>861</v>
       </c>
       <c r="C224" s="27" t="s">
-        <v>1412</v>
+        <v>1458</v>
       </c>
       <c r="D224" s="67" t="s">
         <v>1403</v>
@@ -26114,7 +26971,7 @@
         <v>862</v>
       </c>
       <c r="C225" s="27" t="s">
-        <v>1412</v>
+        <v>1458</v>
       </c>
       <c r="D225" s="67" t="s">
         <v>1403</v>
@@ -26191,7 +27048,7 @@
         <v>863</v>
       </c>
       <c r="C226" s="27" t="s">
-        <v>1412</v>
+        <v>1458</v>
       </c>
       <c r="D226" s="67" t="s">
         <v>1403</v>
@@ -26268,7 +27125,7 @@
         <v>864</v>
       </c>
       <c r="C227" s="27" t="s">
-        <v>1412</v>
+        <v>1458</v>
       </c>
       <c r="D227" s="67" t="s">
         <v>1403</v>
@@ -26345,7 +27202,7 @@
         <v>865</v>
       </c>
       <c r="C228" s="27" t="s">
-        <v>1412</v>
+        <v>1458</v>
       </c>
       <c r="D228" s="67" t="s">
         <v>1403</v>
@@ -26422,7 +27279,7 @@
         <v>866</v>
       </c>
       <c r="C229" s="27" t="s">
-        <v>1412</v>
+        <v>1458</v>
       </c>
       <c r="D229" s="67" t="s">
         <v>1403</v>
@@ -26499,7 +27356,7 @@
         <v>867</v>
       </c>
       <c r="C230" s="27" t="s">
-        <v>1412</v>
+        <v>1458</v>
       </c>
       <c r="D230" s="67" t="s">
         <v>1403</v>
@@ -26576,7 +27433,7 @@
         <v>868</v>
       </c>
       <c r="C231" s="27" t="s">
-        <v>1412</v>
+        <v>1458</v>
       </c>
       <c r="D231" s="67" t="s">
         <v>1403</v>
@@ -26653,7 +27510,7 @@
         <v>869</v>
       </c>
       <c r="C232" s="27" t="s">
-        <v>1412</v>
+        <v>1458</v>
       </c>
       <c r="D232" s="67" t="s">
         <v>1403</v>
@@ -26730,7 +27587,7 @@
         <v>870</v>
       </c>
       <c r="C233" s="27" t="s">
-        <v>1412</v>
+        <v>1458</v>
       </c>
       <c r="D233" s="67" t="s">
         <v>1403</v>
@@ -26807,7 +27664,7 @@
         <v>871</v>
       </c>
       <c r="C234" s="27" t="s">
-        <v>1412</v>
+        <v>1458</v>
       </c>
       <c r="D234" s="67" t="s">
         <v>1403</v>
@@ -26884,7 +27741,7 @@
         <v>872</v>
       </c>
       <c r="C235" s="27" t="s">
-        <v>1412</v>
+        <v>1458</v>
       </c>
       <c r="D235" s="67" t="s">
         <v>1403</v>
@@ -26961,7 +27818,7 @@
         <v>873</v>
       </c>
       <c r="C236" s="27" t="s">
-        <v>1412</v>
+        <v>1458</v>
       </c>
       <c r="D236" s="67" t="s">
         <v>1403</v>
@@ -27038,7 +27895,7 @@
         <v>874</v>
       </c>
       <c r="C237" s="27" t="s">
-        <v>1412</v>
+        <v>1458</v>
       </c>
       <c r="D237" s="67" t="s">
         <v>1403</v>
@@ -27115,7 +27972,7 @@
         <v>875</v>
       </c>
       <c r="C238" s="27" t="s">
-        <v>1412</v>
+        <v>1458</v>
       </c>
       <c r="D238" s="67" t="s">
         <v>1403</v>
@@ -27192,7 +28049,7 @@
         <v>876</v>
       </c>
       <c r="C239" s="27" t="s">
-        <v>1412</v>
+        <v>1458</v>
       </c>
       <c r="D239" s="67" t="s">
         <v>1403</v>
@@ -27269,7 +28126,7 @@
         <v>877</v>
       </c>
       <c r="C240" s="27" t="s">
-        <v>1412</v>
+        <v>1458</v>
       </c>
       <c r="D240" s="67" t="s">
         <v>1403</v>
@@ -27346,7 +28203,7 @@
         <v>878</v>
       </c>
       <c r="C241" s="27" t="s">
-        <v>1412</v>
+        <v>1452</v>
       </c>
       <c r="D241" s="67" t="s">
         <v>1403</v>
@@ -27376,7 +28233,7 @@
         <v>1314</v>
       </c>
       <c r="M241" s="49" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="N241" s="54" t="s">
         <v>1</v>
@@ -27423,7 +28280,7 @@
         <v>879</v>
       </c>
       <c r="C242" s="27" t="s">
-        <v>1412</v>
+        <v>1452</v>
       </c>
       <c r="D242" s="67" t="s">
         <v>1403</v>
@@ -27453,7 +28310,7 @@
         <v>1314</v>
       </c>
       <c r="M242" s="49" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="N242" s="54" t="s">
         <v>1</v>
@@ -27500,7 +28357,7 @@
         <v>880</v>
       </c>
       <c r="C243" s="27" t="s">
-        <v>1412</v>
+        <v>1452</v>
       </c>
       <c r="D243" s="67" t="s">
         <v>1403</v>
@@ -27530,7 +28387,7 @@
         <v>1314</v>
       </c>
       <c r="M243" s="49" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="N243" s="54" t="s">
         <v>1</v>
@@ -27577,7 +28434,7 @@
         <v>881</v>
       </c>
       <c r="C244" s="27" t="s">
-        <v>1412</v>
+        <v>1452</v>
       </c>
       <c r="D244" s="67" t="s">
         <v>1403</v>
@@ -27607,7 +28464,7 @@
         <v>1314</v>
       </c>
       <c r="M244" s="49" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="N244" s="54" t="s">
         <v>1</v>
@@ -27654,7 +28511,7 @@
         <v>882</v>
       </c>
       <c r="C245" s="27" t="s">
-        <v>1412</v>
+        <v>1452</v>
       </c>
       <c r="D245" s="67" t="s">
         <v>1403</v>
@@ -27684,7 +28541,7 @@
         <v>1314</v>
       </c>
       <c r="M245" s="49" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="N245" s="54" t="s">
         <v>1</v>
@@ -27731,7 +28588,7 @@
         <v>883</v>
       </c>
       <c r="C246" s="27" t="s">
-        <v>1412</v>
+        <v>1452</v>
       </c>
       <c r="D246" s="67" t="s">
         <v>1403</v>
@@ -27761,7 +28618,7 @@
         <v>1314</v>
       </c>
       <c r="M246" s="49" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="N246" s="54" t="s">
         <v>1</v>
@@ -27808,7 +28665,7 @@
         <v>884</v>
       </c>
       <c r="C247" s="27" t="s">
-        <v>1412</v>
+        <v>1452</v>
       </c>
       <c r="D247" s="67" t="s">
         <v>1403</v>
@@ -27838,7 +28695,7 @@
         <v>1314</v>
       </c>
       <c r="M247" s="49" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="N247" s="54" t="s">
         <v>1</v>
@@ -27885,7 +28742,7 @@
         <v>885</v>
       </c>
       <c r="C248" s="27" t="s">
-        <v>1412</v>
+        <v>1452</v>
       </c>
       <c r="D248" s="67" t="s">
         <v>1403</v>
@@ -27915,7 +28772,7 @@
         <v>1314</v>
       </c>
       <c r="M248" s="49" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="N248" s="54" t="s">
         <v>1</v>
@@ -27962,7 +28819,7 @@
         <v>886</v>
       </c>
       <c r="C249" s="27" t="s">
-        <v>1412</v>
+        <v>1452</v>
       </c>
       <c r="D249" s="67" t="s">
         <v>1403</v>
@@ -27992,7 +28849,7 @@
         <v>1314</v>
       </c>
       <c r="M249" s="49" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="N249" s="54" t="s">
         <v>1</v>
@@ -28039,7 +28896,7 @@
         <v>887</v>
       </c>
       <c r="C250" s="27" t="s">
-        <v>1412</v>
+        <v>1452</v>
       </c>
       <c r="D250" s="67" t="s">
         <v>1403</v>
@@ -28069,7 +28926,7 @@
         <v>1314</v>
       </c>
       <c r="M250" s="49" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="N250" s="54" t="s">
         <v>1</v>
@@ -28116,7 +28973,7 @@
         <v>888</v>
       </c>
       <c r="C251" s="27" t="s">
-        <v>1412</v>
+        <v>1452</v>
       </c>
       <c r="D251" s="67" t="s">
         <v>1403</v>
@@ -28146,7 +29003,7 @@
         <v>1314</v>
       </c>
       <c r="M251" s="49" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="N251" s="54" t="s">
         <v>1</v>
@@ -28193,7 +29050,7 @@
         <v>889</v>
       </c>
       <c r="C252" s="27" t="s">
-        <v>1412</v>
+        <v>1452</v>
       </c>
       <c r="D252" s="67" t="s">
         <v>1403</v>
@@ -28223,7 +29080,7 @@
         <v>1314</v>
       </c>
       <c r="M252" s="49" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="N252" s="54" t="s">
         <v>1</v>
@@ -28270,7 +29127,7 @@
         <v>890</v>
       </c>
       <c r="C253" s="27" t="s">
-        <v>1412</v>
+        <v>1452</v>
       </c>
       <c r="D253" s="67" t="s">
         <v>1403</v>
@@ -28300,7 +29157,7 @@
         <v>1314</v>
       </c>
       <c r="M253" s="49" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="N253" s="54" t="s">
         <v>1</v>
@@ -28347,7 +29204,7 @@
         <v>891</v>
       </c>
       <c r="C254" s="27" t="s">
-        <v>1412</v>
+        <v>1452</v>
       </c>
       <c r="D254" s="67" t="s">
         <v>1403</v>
@@ -28377,7 +29234,7 @@
         <v>1314</v>
       </c>
       <c r="M254" s="49" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="N254" s="54" t="s">
         <v>1</v>
@@ -28424,7 +29281,7 @@
         <v>892</v>
       </c>
       <c r="C255" s="27" t="s">
-        <v>1412</v>
+        <v>1452</v>
       </c>
       <c r="D255" s="67" t="s">
         <v>1403</v>
@@ -28454,7 +29311,7 @@
         <v>1314</v>
       </c>
       <c r="M255" s="49" t="s">
-        <v>1394</v>
+        <v>1466</v>
       </c>
       <c r="N255" s="54" t="s">
         <v>1</v>
@@ -28501,7 +29358,7 @@
         <v>893</v>
       </c>
       <c r="C256" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D256" s="67" t="s">
         <v>1403</v>
@@ -28531,7 +29388,7 @@
         <v>1314</v>
       </c>
       <c r="M256" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N256" s="54" t="s">
         <v>1</v>
@@ -28578,7 +29435,7 @@
         <v>894</v>
       </c>
       <c r="C257" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D257" s="67" t="s">
         <v>1403</v>
@@ -28608,7 +29465,7 @@
         <v>1314</v>
       </c>
       <c r="M257" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N257" s="54" t="s">
         <v>1</v>
@@ -28655,7 +29512,7 @@
         <v>895</v>
       </c>
       <c r="C258" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D258" s="67" t="s">
         <v>1403</v>
@@ -28685,7 +29542,7 @@
         <v>1314</v>
       </c>
       <c r="M258" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N258" s="54" t="s">
         <v>1</v>
@@ -28732,7 +29589,7 @@
         <v>896</v>
       </c>
       <c r="C259" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D259" s="67" t="s">
         <v>1403</v>
@@ -28762,7 +29619,7 @@
         <v>1314</v>
       </c>
       <c r="M259" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N259" s="54" t="s">
         <v>1</v>
@@ -28809,7 +29666,7 @@
         <v>897</v>
       </c>
       <c r="C260" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D260" s="67" t="s">
         <v>1403</v>
@@ -28839,7 +29696,7 @@
         <v>1314</v>
       </c>
       <c r="M260" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N260" s="54" t="s">
         <v>1</v>
@@ -28886,7 +29743,7 @@
         <v>898</v>
       </c>
       <c r="C261" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D261" s="67" t="s">
         <v>1403</v>
@@ -28916,7 +29773,7 @@
         <v>1314</v>
       </c>
       <c r="M261" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N261" s="54" t="s">
         <v>1</v>
@@ -28963,7 +29820,7 @@
         <v>899</v>
       </c>
       <c r="C262" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D262" s="67" t="s">
         <v>1403</v>
@@ -28993,7 +29850,7 @@
         <v>1314</v>
       </c>
       <c r="M262" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N262" s="54" t="s">
         <v>1</v>
@@ -29040,7 +29897,7 @@
         <v>900</v>
       </c>
       <c r="C263" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D263" s="67" t="s">
         <v>1403</v>
@@ -29070,7 +29927,7 @@
         <v>1314</v>
       </c>
       <c r="M263" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N263" s="54" t="s">
         <v>1</v>
@@ -29117,7 +29974,7 @@
         <v>901</v>
       </c>
       <c r="C264" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D264" s="67" t="s">
         <v>1403</v>
@@ -29147,7 +30004,7 @@
         <v>1314</v>
       </c>
       <c r="M264" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N264" s="54" t="s">
         <v>1</v>
@@ -29194,7 +30051,7 @@
         <v>902</v>
       </c>
       <c r="C265" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D265" s="67" t="s">
         <v>1403</v>
@@ -29224,7 +30081,7 @@
         <v>1314</v>
       </c>
       <c r="M265" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N265" s="54" t="s">
         <v>1</v>
@@ -29271,7 +30128,7 @@
         <v>903</v>
       </c>
       <c r="C266" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D266" s="67" t="s">
         <v>1403</v>
@@ -29301,7 +30158,7 @@
         <v>1314</v>
       </c>
       <c r="M266" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N266" s="54" t="s">
         <v>1</v>
@@ -29348,7 +30205,7 @@
         <v>904</v>
       </c>
       <c r="C267" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D267" s="67" t="s">
         <v>1403</v>
@@ -29378,7 +30235,7 @@
         <v>1314</v>
       </c>
       <c r="M267" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N267" s="54" t="s">
         <v>1</v>
@@ -29425,7 +30282,7 @@
         <v>905</v>
       </c>
       <c r="C268" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D268" s="67" t="s">
         <v>1403</v>
@@ -29455,7 +30312,7 @@
         <v>1314</v>
       </c>
       <c r="M268" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N268" s="54" t="s">
         <v>1</v>
@@ -29502,7 +30359,7 @@
         <v>906</v>
       </c>
       <c r="C269" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D269" s="67" t="s">
         <v>1403</v>
@@ -29532,7 +30389,7 @@
         <v>1314</v>
       </c>
       <c r="M269" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N269" s="54" t="s">
         <v>1</v>
@@ -29579,7 +30436,7 @@
         <v>907</v>
       </c>
       <c r="C270" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D270" s="67" t="s">
         <v>1403</v>
@@ -29609,7 +30466,7 @@
         <v>1314</v>
       </c>
       <c r="M270" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N270" s="54" t="s">
         <v>1</v>
@@ -29656,7 +30513,7 @@
         <v>908</v>
       </c>
       <c r="C271" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D271" s="67" t="s">
         <v>1403</v>
@@ -29686,7 +30543,7 @@
         <v>1314</v>
       </c>
       <c r="M271" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N271" s="54" t="s">
         <v>1</v>
@@ -29733,7 +30590,7 @@
         <v>909</v>
       </c>
       <c r="C272" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D272" s="67" t="s">
         <v>1403</v>
@@ -29763,7 +30620,7 @@
         <v>1314</v>
       </c>
       <c r="M272" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N272" s="54" t="s">
         <v>1</v>
@@ -29810,7 +30667,7 @@
         <v>910</v>
       </c>
       <c r="C273" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D273" s="67" t="s">
         <v>1403</v>
@@ -29840,7 +30697,7 @@
         <v>1314</v>
       </c>
       <c r="M273" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N273" s="54" t="s">
         <v>1</v>
@@ -29887,7 +30744,7 @@
         <v>911</v>
       </c>
       <c r="C274" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D274" s="67" t="s">
         <v>1403</v>
@@ -29917,7 +30774,7 @@
         <v>1314</v>
       </c>
       <c r="M274" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N274" s="54" t="s">
         <v>1</v>
@@ -29964,7 +30821,7 @@
         <v>912</v>
       </c>
       <c r="C275" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D275" s="67" t="s">
         <v>1403</v>
@@ -29994,7 +30851,7 @@
         <v>1314</v>
       </c>
       <c r="M275" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N275" s="54" t="s">
         <v>1</v>
@@ -30041,7 +30898,7 @@
         <v>913</v>
       </c>
       <c r="C276" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D276" s="67" t="s">
         <v>1403</v>
@@ -30071,7 +30928,7 @@
         <v>1314</v>
       </c>
       <c r="M276" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N276" s="54" t="s">
         <v>1</v>
@@ -30118,7 +30975,7 @@
         <v>914</v>
       </c>
       <c r="C277" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D277" s="67" t="s">
         <v>1403</v>
@@ -30148,7 +31005,7 @@
         <v>1314</v>
       </c>
       <c r="M277" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N277" s="54" t="s">
         <v>1</v>
@@ -30195,7 +31052,7 @@
         <v>915</v>
       </c>
       <c r="C278" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D278" s="67" t="s">
         <v>1403</v>
@@ -30225,7 +31082,7 @@
         <v>1314</v>
       </c>
       <c r="M278" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N278" s="54" t="s">
         <v>1</v>
@@ -30272,7 +31129,7 @@
         <v>916</v>
       </c>
       <c r="C279" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D279" s="67" t="s">
         <v>1403</v>
@@ -30302,7 +31159,7 @@
         <v>1314</v>
       </c>
       <c r="M279" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N279" s="54" t="s">
         <v>1</v>
@@ -30349,7 +31206,7 @@
         <v>917</v>
       </c>
       <c r="C280" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D280" s="67" t="s">
         <v>1403</v>
@@ -30379,7 +31236,7 @@
         <v>1314</v>
       </c>
       <c r="M280" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N280" s="54" t="s">
         <v>1</v>
@@ -30426,7 +31283,7 @@
         <v>918</v>
       </c>
       <c r="C281" s="27" t="s">
-        <v>1412</v>
+        <v>1468</v>
       </c>
       <c r="D281" s="67" t="s">
         <v>1403</v>
@@ -30456,7 +31313,7 @@
         <v>1314</v>
       </c>
       <c r="M281" s="49" t="s">
-        <v>1394</v>
+        <v>1467</v>
       </c>
       <c r="N281" s="54" t="s">
         <v>1</v>
@@ -30503,7 +31360,7 @@
         <v>919</v>
       </c>
       <c r="C282" s="27" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="D282" s="67" t="s">
         <v>1403</v>
@@ -30533,7 +31390,7 @@
         <v>1314</v>
       </c>
       <c r="M282" s="49" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="N282" s="54" t="s">
         <v>1</v>
@@ -30580,7 +31437,7 @@
         <v>920</v>
       </c>
       <c r="C283" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D283" s="67" t="s">
         <v>1403</v>
@@ -30657,7 +31514,7 @@
         <v>921</v>
       </c>
       <c r="C284" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D284" s="67" t="s">
         <v>1403</v>
@@ -30734,7 +31591,7 @@
         <v>922</v>
       </c>
       <c r="C285" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D285" s="67" t="s">
         <v>1403</v>
@@ -30811,7 +31668,7 @@
         <v>923</v>
       </c>
       <c r="C286" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D286" s="67" t="s">
         <v>1403</v>
@@ -30888,7 +31745,7 @@
         <v>924</v>
       </c>
       <c r="C287" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D287" s="67" t="s">
         <v>1403</v>
@@ -30965,7 +31822,7 @@
         <v>925</v>
       </c>
       <c r="C288" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D288" s="67" t="s">
         <v>1403</v>
@@ -31042,7 +31899,7 @@
         <v>926</v>
       </c>
       <c r="C289" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D289" s="67" t="s">
         <v>1403</v>
@@ -31119,7 +31976,7 @@
         <v>927</v>
       </c>
       <c r="C290" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D290" s="67" t="s">
         <v>1403</v>
@@ -31196,7 +32053,7 @@
         <v>928</v>
       </c>
       <c r="C291" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D291" s="67" t="s">
         <v>1403</v>
@@ -31273,7 +32130,7 @@
         <v>929</v>
       </c>
       <c r="C292" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D292" s="67" t="s">
         <v>1403</v>
@@ -31350,7 +32207,7 @@
         <v>930</v>
       </c>
       <c r="C293" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D293" s="67" t="s">
         <v>1403</v>
@@ -31427,7 +32284,7 @@
         <v>931</v>
       </c>
       <c r="C294" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D294" s="67" t="s">
         <v>1403</v>
@@ -31504,7 +32361,7 @@
         <v>932</v>
       </c>
       <c r="C295" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D295" s="67" t="s">
         <v>1403</v>
@@ -31581,7 +32438,7 @@
         <v>933</v>
       </c>
       <c r="C296" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D296" s="67" t="s">
         <v>1403</v>
@@ -31658,7 +32515,7 @@
         <v>934</v>
       </c>
       <c r="C297" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D297" s="67" t="s">
         <v>1403</v>
@@ -31735,7 +32592,7 @@
         <v>935</v>
       </c>
       <c r="C298" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D298" s="67" t="s">
         <v>1403</v>
@@ -31812,7 +32669,7 @@
         <v>936</v>
       </c>
       <c r="C299" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D299" s="67" t="s">
         <v>1403</v>
@@ -31889,7 +32746,7 @@
         <v>937</v>
       </c>
       <c r="C300" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D300" s="67" t="s">
         <v>1403</v>
@@ -31966,7 +32823,7 @@
         <v>938</v>
       </c>
       <c r="C301" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D301" s="67" t="s">
         <v>1403</v>
@@ -32043,7 +32900,7 @@
         <v>939</v>
       </c>
       <c r="C302" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D302" s="67" t="s">
         <v>1403</v>
@@ -32120,7 +32977,7 @@
         <v>940</v>
       </c>
       <c r="C303" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D303" s="67" t="s">
         <v>1403</v>
@@ -32197,7 +33054,7 @@
         <v>941</v>
       </c>
       <c r="C304" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D304" s="67" t="s">
         <v>1403</v>
@@ -32274,7 +33131,7 @@
         <v>942</v>
       </c>
       <c r="C305" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D305" s="67" t="s">
         <v>1403</v>
@@ -32351,7 +33208,7 @@
         <v>943</v>
       </c>
       <c r="C306" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D306" s="67" t="s">
         <v>1403</v>
@@ -32428,7 +33285,7 @@
         <v>944</v>
       </c>
       <c r="C307" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D307" s="67" t="s">
         <v>1403</v>
@@ -32505,7 +33362,7 @@
         <v>945</v>
       </c>
       <c r="C308" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D308" s="67" t="s">
         <v>1403</v>
@@ -32582,7 +33439,7 @@
         <v>946</v>
       </c>
       <c r="C309" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D309" s="67" t="s">
         <v>1403</v>
@@ -32659,7 +33516,7 @@
         <v>947</v>
       </c>
       <c r="C310" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D310" s="67" t="s">
         <v>1403</v>
@@ -32736,7 +33593,7 @@
         <v>948</v>
       </c>
       <c r="C311" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D311" s="67" t="s">
         <v>1403</v>
@@ -32813,7 +33670,7 @@
         <v>949</v>
       </c>
       <c r="C312" s="27" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D312" s="67" t="s">
         <v>1403</v>
@@ -32890,7 +33747,7 @@
         <v>950</v>
       </c>
       <c r="C313" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D313" s="67" t="s">
         <v>1403</v>
@@ -32967,7 +33824,7 @@
         <v>951</v>
       </c>
       <c r="C314" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D314" s="67" t="s">
         <v>1403</v>
@@ -33044,7 +33901,7 @@
         <v>952</v>
       </c>
       <c r="C315" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D315" s="67" t="s">
         <v>1403</v>
@@ -33121,7 +33978,7 @@
         <v>953</v>
       </c>
       <c r="C316" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D316" s="67" t="s">
         <v>1403</v>
@@ -33198,7 +34055,7 @@
         <v>954</v>
       </c>
       <c r="C317" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D317" s="67" t="s">
         <v>1403</v>
@@ -33275,7 +34132,7 @@
         <v>955</v>
       </c>
       <c r="C318" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D318" s="67" t="s">
         <v>1403</v>
@@ -33352,7 +34209,7 @@
         <v>956</v>
       </c>
       <c r="C319" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D319" s="67" t="s">
         <v>1403</v>
@@ -33429,7 +34286,7 @@
         <v>957</v>
       </c>
       <c r="C320" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D320" s="67" t="s">
         <v>1403</v>
@@ -33506,7 +34363,7 @@
         <v>958</v>
       </c>
       <c r="C321" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D321" s="67" t="s">
         <v>1403</v>
@@ -33583,7 +34440,7 @@
         <v>959</v>
       </c>
       <c r="C322" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D322" s="67" t="s">
         <v>1403</v>
@@ -33660,7 +34517,7 @@
         <v>960</v>
       </c>
       <c r="C323" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D323" s="67" t="s">
         <v>1403</v>
@@ -33737,7 +34594,7 @@
         <v>961</v>
       </c>
       <c r="C324" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D324" s="67" t="s">
         <v>1403</v>
@@ -33814,7 +34671,7 @@
         <v>962</v>
       </c>
       <c r="C325" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D325" s="67" t="s">
         <v>1403</v>
@@ -33891,7 +34748,7 @@
         <v>963</v>
       </c>
       <c r="C326" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D326" s="67" t="s">
         <v>1403</v>
@@ -33968,7 +34825,7 @@
         <v>964</v>
       </c>
       <c r="C327" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D327" s="67" t="s">
         <v>1403</v>
@@ -34045,7 +34902,7 @@
         <v>965</v>
       </c>
       <c r="C328" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D328" s="67" t="s">
         <v>1403</v>
@@ -34122,7 +34979,7 @@
         <v>966</v>
       </c>
       <c r="C329" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D329" s="67" t="s">
         <v>1403</v>
@@ -34199,7 +35056,7 @@
         <v>967</v>
       </c>
       <c r="C330" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D330" s="67" t="s">
         <v>1403</v>
@@ -34276,7 +35133,7 @@
         <v>968</v>
       </c>
       <c r="C331" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D331" s="67" t="s">
         <v>1403</v>
@@ -34353,7 +35210,7 @@
         <v>969</v>
       </c>
       <c r="C332" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D332" s="67" t="s">
         <v>1403</v>
@@ -34430,7 +35287,7 @@
         <v>970</v>
       </c>
       <c r="C333" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D333" s="67" t="s">
         <v>1403</v>
@@ -34507,7 +35364,7 @@
         <v>971</v>
       </c>
       <c r="C334" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D334" s="67" t="s">
         <v>1403</v>
@@ -34584,7 +35441,7 @@
         <v>972</v>
       </c>
       <c r="C335" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D335" s="67" t="s">
         <v>1403</v>
@@ -34661,7 +35518,7 @@
         <v>973</v>
       </c>
       <c r="C336" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D336" s="67" t="s">
         <v>1403</v>
@@ -34738,7 +35595,7 @@
         <v>974</v>
       </c>
       <c r="C337" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D337" s="67" t="s">
         <v>1403</v>
@@ -34815,7 +35672,7 @@
         <v>975</v>
       </c>
       <c r="C338" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D338" s="67" t="s">
         <v>1403</v>
@@ -34892,7 +35749,7 @@
         <v>976</v>
       </c>
       <c r="C339" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D339" s="67" t="s">
         <v>1403</v>
@@ -34969,7 +35826,7 @@
         <v>977</v>
       </c>
       <c r="C340" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D340" s="67" t="s">
         <v>1403</v>
@@ -35046,7 +35903,7 @@
         <v>978</v>
       </c>
       <c r="C341" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D341" s="67" t="s">
         <v>1403</v>
@@ -35123,7 +35980,7 @@
         <v>979</v>
       </c>
       <c r="C342" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D342" s="67" t="s">
         <v>1403</v>
@@ -35200,7 +36057,7 @@
         <v>980</v>
       </c>
       <c r="C343" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D343" s="67" t="s">
         <v>1403</v>
@@ -35277,7 +36134,7 @@
         <v>981</v>
       </c>
       <c r="C344" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D344" s="67" t="s">
         <v>1403</v>
@@ -35354,7 +36211,7 @@
         <v>982</v>
       </c>
       <c r="C345" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D345" s="67" t="s">
         <v>1403</v>
@@ -35431,7 +36288,7 @@
         <v>983</v>
       </c>
       <c r="C346" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D346" s="67" t="s">
         <v>1403</v>
@@ -35508,7 +36365,7 @@
         <v>984</v>
       </c>
       <c r="C347" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D347" s="67" t="s">
         <v>1403</v>
@@ -35585,7 +36442,7 @@
         <v>985</v>
       </c>
       <c r="C348" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D348" s="67" t="s">
         <v>1403</v>
@@ -35662,7 +36519,7 @@
         <v>986</v>
       </c>
       <c r="C349" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D349" s="67" t="s">
         <v>1403</v>
@@ -35739,7 +36596,7 @@
         <v>987</v>
       </c>
       <c r="C350" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D350" s="67" t="s">
         <v>1403</v>
@@ -35816,7 +36673,7 @@
         <v>988</v>
       </c>
       <c r="C351" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D351" s="67" t="s">
         <v>1403</v>
@@ -35893,7 +36750,7 @@
         <v>989</v>
       </c>
       <c r="C352" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D352" s="67" t="s">
         <v>1403</v>
@@ -35970,7 +36827,7 @@
         <v>990</v>
       </c>
       <c r="C353" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D353" s="67" t="s">
         <v>1403</v>
@@ -36047,7 +36904,7 @@
         <v>991</v>
       </c>
       <c r="C354" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D354" s="67" t="s">
         <v>1403</v>
@@ -36124,7 +36981,7 @@
         <v>992</v>
       </c>
       <c r="C355" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D355" s="67" t="s">
         <v>1403</v>
@@ -36201,7 +37058,7 @@
         <v>993</v>
       </c>
       <c r="C356" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D356" s="67" t="s">
         <v>1403</v>
@@ -36278,7 +37135,7 @@
         <v>994</v>
       </c>
       <c r="C357" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D357" s="67" t="s">
         <v>1403</v>
@@ -36355,7 +37212,7 @@
         <v>995</v>
       </c>
       <c r="C358" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D358" s="67" t="s">
         <v>1403</v>
@@ -36432,7 +37289,7 @@
         <v>996</v>
       </c>
       <c r="C359" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D359" s="67" t="s">
         <v>1403</v>
@@ -36509,7 +37366,7 @@
         <v>997</v>
       </c>
       <c r="C360" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D360" s="67" t="s">
         <v>1403</v>
@@ -36586,7 +37443,7 @@
         <v>998</v>
       </c>
       <c r="C361" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D361" s="67" t="s">
         <v>1403</v>
@@ -36663,7 +37520,7 @@
         <v>999</v>
       </c>
       <c r="C362" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D362" s="67" t="s">
         <v>1403</v>
@@ -36740,7 +37597,7 @@
         <v>1000</v>
       </c>
       <c r="C363" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D363" s="67" t="s">
         <v>1403</v>
@@ -36817,7 +37674,7 @@
         <v>1001</v>
       </c>
       <c r="C364" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D364" s="67" t="s">
         <v>1403</v>
@@ -36894,7 +37751,7 @@
         <v>1002</v>
       </c>
       <c r="C365" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D365" s="67" t="s">
         <v>1403</v>
@@ -36971,7 +37828,7 @@
         <v>1003</v>
       </c>
       <c r="C366" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D366" s="67" t="s">
         <v>1403</v>
@@ -37048,7 +37905,7 @@
         <v>1004</v>
       </c>
       <c r="C367" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D367" s="67" t="s">
         <v>1403</v>
@@ -37125,7 +37982,7 @@
         <v>1005</v>
       </c>
       <c r="C368" s="27" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D368" s="67" t="s">
         <v>1403</v>
@@ -37202,7 +38059,7 @@
         <v>1006</v>
       </c>
       <c r="C369" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D369" s="67" t="s">
         <v>1403</v>
@@ -37279,7 +38136,7 @@
         <v>1007</v>
       </c>
       <c r="C370" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D370" s="67" t="s">
         <v>1403</v>
@@ -37356,7 +38213,7 @@
         <v>1008</v>
       </c>
       <c r="C371" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D371" s="67" t="s">
         <v>1403</v>
@@ -37433,7 +38290,7 @@
         <v>1009</v>
       </c>
       <c r="C372" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D372" s="67" t="s">
         <v>1403</v>
@@ -37510,7 +38367,7 @@
         <v>1010</v>
       </c>
       <c r="C373" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D373" s="67" t="s">
         <v>1403</v>
@@ -37587,7 +38444,7 @@
         <v>1011</v>
       </c>
       <c r="C374" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D374" s="67" t="s">
         <v>1403</v>
@@ -37664,7 +38521,7 @@
         <v>1012</v>
       </c>
       <c r="C375" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D375" s="67" t="s">
         <v>1403</v>
@@ -37741,7 +38598,7 @@
         <v>1013</v>
       </c>
       <c r="C376" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D376" s="67" t="s">
         <v>1403</v>
@@ -37818,7 +38675,7 @@
         <v>1014</v>
       </c>
       <c r="C377" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D377" s="67" t="s">
         <v>1403</v>
@@ -37895,7 +38752,7 @@
         <v>1015</v>
       </c>
       <c r="C378" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D378" s="67" t="s">
         <v>1403</v>
@@ -37972,7 +38829,7 @@
         <v>1016</v>
       </c>
       <c r="C379" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D379" s="67" t="s">
         <v>1403</v>
@@ -38049,7 +38906,7 @@
         <v>1017</v>
       </c>
       <c r="C380" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D380" s="67" t="s">
         <v>1403</v>
@@ -38126,7 +38983,7 @@
         <v>1018</v>
       </c>
       <c r="C381" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D381" s="67" t="s">
         <v>1403</v>
@@ -38203,7 +39060,7 @@
         <v>1019</v>
       </c>
       <c r="C382" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D382" s="67" t="s">
         <v>1403</v>
@@ -38280,7 +39137,7 @@
         <v>1020</v>
       </c>
       <c r="C383" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D383" s="67" t="s">
         <v>1403</v>
@@ -38357,7 +39214,7 @@
         <v>1021</v>
       </c>
       <c r="C384" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D384" s="67" t="s">
         <v>1403</v>
@@ -38434,7 +39291,7 @@
         <v>1022</v>
       </c>
       <c r="C385" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D385" s="67" t="s">
         <v>1403</v>
@@ -38511,7 +39368,7 @@
         <v>1023</v>
       </c>
       <c r="C386" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D386" s="67" t="s">
         <v>1403</v>
@@ -38588,7 +39445,7 @@
         <v>1024</v>
       </c>
       <c r="C387" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D387" s="67" t="s">
         <v>1403</v>
@@ -38665,7 +39522,7 @@
         <v>1025</v>
       </c>
       <c r="C388" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D388" s="67" t="s">
         <v>1403</v>
@@ -38742,7 +39599,7 @@
         <v>1026</v>
       </c>
       <c r="C389" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D389" s="67" t="s">
         <v>1403</v>
@@ -38819,7 +39676,7 @@
         <v>1027</v>
       </c>
       <c r="C390" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D390" s="67" t="s">
         <v>1403</v>
@@ -38896,7 +39753,7 @@
         <v>1028</v>
       </c>
       <c r="C391" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D391" s="67" t="s">
         <v>1403</v>
@@ -38973,7 +39830,7 @@
         <v>1029</v>
       </c>
       <c r="C392" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D392" s="67" t="s">
         <v>1403</v>
@@ -39050,7 +39907,7 @@
         <v>1030</v>
       </c>
       <c r="C393" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D393" s="67" t="s">
         <v>1403</v>
@@ -39127,7 +39984,7 @@
         <v>1031</v>
       </c>
       <c r="C394" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D394" s="67" t="s">
         <v>1403</v>
@@ -39204,7 +40061,7 @@
         <v>1032</v>
       </c>
       <c r="C395" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D395" s="67" t="s">
         <v>1403</v>
@@ -39281,7 +40138,7 @@
         <v>1033</v>
       </c>
       <c r="C396" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D396" s="67" t="s">
         <v>1403</v>
@@ -39358,7 +40215,7 @@
         <v>1034</v>
       </c>
       <c r="C397" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D397" s="67" t="s">
         <v>1403</v>
@@ -39435,7 +40292,7 @@
         <v>1035</v>
       </c>
       <c r="C398" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D398" s="67" t="s">
         <v>1403</v>
@@ -39512,7 +40369,7 @@
         <v>1036</v>
       </c>
       <c r="C399" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D399" s="67" t="s">
         <v>1403</v>
@@ -39589,7 +40446,7 @@
         <v>1037</v>
       </c>
       <c r="C400" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D400" s="67" t="s">
         <v>1403</v>
@@ -39666,7 +40523,7 @@
         <v>1038</v>
       </c>
       <c r="C401" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D401" s="67" t="s">
         <v>1403</v>
@@ -39743,7 +40600,7 @@
         <v>1039</v>
       </c>
       <c r="C402" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D402" s="67" t="s">
         <v>1403</v>
@@ -39820,7 +40677,7 @@
         <v>1040</v>
       </c>
       <c r="C403" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D403" s="67" t="s">
         <v>1403</v>
@@ -39897,7 +40754,7 @@
         <v>1041</v>
       </c>
       <c r="C404" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D404" s="67" t="s">
         <v>1403</v>
@@ -39974,7 +40831,7 @@
         <v>1042</v>
       </c>
       <c r="C405" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D405" s="67" t="s">
         <v>1403</v>
@@ -40051,7 +40908,7 @@
         <v>1043</v>
       </c>
       <c r="C406" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D406" s="67" t="s">
         <v>1403</v>
@@ -40128,7 +40985,7 @@
         <v>1044</v>
       </c>
       <c r="C407" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D407" s="67" t="s">
         <v>1403</v>
@@ -40205,7 +41062,7 @@
         <v>1045</v>
       </c>
       <c r="C408" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D408" s="67" t="s">
         <v>1403</v>
@@ -40282,7 +41139,7 @@
         <v>1046</v>
       </c>
       <c r="C409" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D409" s="67" t="s">
         <v>1403</v>
@@ -40359,7 +41216,7 @@
         <v>1047</v>
       </c>
       <c r="C410" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D410" s="67" t="s">
         <v>1403</v>
@@ -40436,7 +41293,7 @@
         <v>1048</v>
       </c>
       <c r="C411" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D411" s="67" t="s">
         <v>1403</v>
@@ -40513,7 +41370,7 @@
         <v>1049</v>
       </c>
       <c r="C412" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D412" s="67" t="s">
         <v>1403</v>
@@ -40590,7 +41447,7 @@
         <v>1050</v>
       </c>
       <c r="C413" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D413" s="67" t="s">
         <v>1403</v>
@@ -40667,7 +41524,7 @@
         <v>1051</v>
       </c>
       <c r="C414" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D414" s="67" t="s">
         <v>1403</v>
@@ -40744,7 +41601,7 @@
         <v>1052</v>
       </c>
       <c r="C415" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D415" s="67" t="s">
         <v>1403</v>
@@ -40821,7 +41678,7 @@
         <v>1053</v>
       </c>
       <c r="C416" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D416" s="67" t="s">
         <v>1403</v>
@@ -40898,7 +41755,7 @@
         <v>1054</v>
       </c>
       <c r="C417" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D417" s="67" t="s">
         <v>1403</v>
@@ -40975,7 +41832,7 @@
         <v>1055</v>
       </c>
       <c r="C418" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D418" s="67" t="s">
         <v>1403</v>
@@ -41052,7 +41909,7 @@
         <v>1056</v>
       </c>
       <c r="C419" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D419" s="67" t="s">
         <v>1403</v>
@@ -41129,7 +41986,7 @@
         <v>1057</v>
       </c>
       <c r="C420" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D420" s="67" t="s">
         <v>1403</v>
@@ -41206,7 +42063,7 @@
         <v>1323</v>
       </c>
       <c r="C421" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D421" s="67" t="s">
         <v>1403</v>
@@ -41283,7 +42140,7 @@
         <v>1324</v>
       </c>
       <c r="C422" s="27" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D422" s="67" t="s">
         <v>1403</v>
@@ -41360,7 +42217,7 @@
         <v>1058</v>
       </c>
       <c r="C423" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D423" s="67" t="s">
         <v>1403</v>
@@ -41437,7 +42294,7 @@
         <v>1059</v>
       </c>
       <c r="C424" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D424" s="67" t="s">
         <v>1403</v>
@@ -41514,7 +42371,7 @@
         <v>1060</v>
       </c>
       <c r="C425" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D425" s="67" t="s">
         <v>1403</v>
@@ -41591,7 +42448,7 @@
         <v>1061</v>
       </c>
       <c r="C426" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D426" s="67" t="s">
         <v>1403</v>
@@ -41668,7 +42525,7 @@
         <v>1062</v>
       </c>
       <c r="C427" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D427" s="67" t="s">
         <v>1403</v>
@@ -41745,7 +42602,7 @@
         <v>1063</v>
       </c>
       <c r="C428" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D428" s="67" t="s">
         <v>1403</v>
@@ -41822,7 +42679,7 @@
         <v>1064</v>
       </c>
       <c r="C429" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D429" s="67" t="s">
         <v>1403</v>
@@ -41899,7 +42756,7 @@
         <v>1065</v>
       </c>
       <c r="C430" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D430" s="67" t="s">
         <v>1403</v>
@@ -41976,7 +42833,7 @@
         <v>1066</v>
       </c>
       <c r="C431" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D431" s="67" t="s">
         <v>1403</v>
@@ -42053,7 +42910,7 @@
         <v>1067</v>
       </c>
       <c r="C432" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D432" s="67" t="s">
         <v>1403</v>
@@ -42130,7 +42987,7 @@
         <v>1068</v>
       </c>
       <c r="C433" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D433" s="67" t="s">
         <v>1403</v>
@@ -42207,7 +43064,7 @@
         <v>1069</v>
       </c>
       <c r="C434" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D434" s="67" t="s">
         <v>1403</v>
@@ -42284,7 +43141,7 @@
         <v>1070</v>
       </c>
       <c r="C435" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D435" s="67" t="s">
         <v>1403</v>
@@ -42361,7 +43218,7 @@
         <v>1071</v>
       </c>
       <c r="C436" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D436" s="67" t="s">
         <v>1403</v>
@@ -42438,7 +43295,7 @@
         <v>1072</v>
       </c>
       <c r="C437" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D437" s="67" t="s">
         <v>1403</v>
@@ -42515,7 +43372,7 @@
         <v>1073</v>
       </c>
       <c r="C438" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D438" s="67" t="s">
         <v>1403</v>
@@ -42592,7 +43449,7 @@
         <v>1074</v>
       </c>
       <c r="C439" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D439" s="67" t="s">
         <v>1403</v>
@@ -42669,7 +43526,7 @@
         <v>1075</v>
       </c>
       <c r="C440" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D440" s="67" t="s">
         <v>1403</v>
@@ -42746,7 +43603,7 @@
         <v>1076</v>
       </c>
       <c r="C441" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D441" s="67" t="s">
         <v>1403</v>
@@ -42823,7 +43680,7 @@
         <v>1077</v>
       </c>
       <c r="C442" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D442" s="67" t="s">
         <v>1403</v>
@@ -42900,7 +43757,7 @@
         <v>1078</v>
       </c>
       <c r="C443" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D443" s="67" t="s">
         <v>1403</v>
@@ -42977,7 +43834,7 @@
         <v>1079</v>
       </c>
       <c r="C444" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D444" s="67" t="s">
         <v>1403</v>
@@ -43054,7 +43911,7 @@
         <v>1080</v>
       </c>
       <c r="C445" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D445" s="67" t="s">
         <v>1403</v>
@@ -43131,7 +43988,7 @@
         <v>1081</v>
       </c>
       <c r="C446" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D446" s="67" t="s">
         <v>1403</v>
@@ -43208,7 +44065,7 @@
         <v>1082</v>
       </c>
       <c r="C447" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D447" s="67" t="s">
         <v>1403</v>
@@ -43285,7 +44142,7 @@
         <v>1083</v>
       </c>
       <c r="C448" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D448" s="67" t="s">
         <v>1403</v>
@@ -43362,7 +44219,7 @@
         <v>1084</v>
       </c>
       <c r="C449" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D449" s="67" t="s">
         <v>1403</v>
@@ -43439,7 +44296,7 @@
         <v>1085</v>
       </c>
       <c r="C450" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D450" s="67" t="s">
         <v>1403</v>
@@ -43516,7 +44373,7 @@
         <v>1086</v>
       </c>
       <c r="C451" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D451" s="67" t="s">
         <v>1403</v>
@@ -43593,7 +44450,7 @@
         <v>1087</v>
       </c>
       <c r="C452" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D452" s="67" t="s">
         <v>1403</v>
@@ -43670,7 +44527,7 @@
         <v>1088</v>
       </c>
       <c r="C453" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D453" s="67" t="s">
         <v>1403</v>
@@ -43747,7 +44604,7 @@
         <v>1089</v>
       </c>
       <c r="C454" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D454" s="67" t="s">
         <v>1403</v>
@@ -43824,7 +44681,7 @@
         <v>1090</v>
       </c>
       <c r="C455" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D455" s="67" t="s">
         <v>1403</v>
@@ -43901,7 +44758,7 @@
         <v>1091</v>
       </c>
       <c r="C456" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D456" s="67" t="s">
         <v>1403</v>
@@ -43978,7 +44835,7 @@
         <v>1092</v>
       </c>
       <c r="C457" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D457" s="67" t="s">
         <v>1403</v>
@@ -44055,7 +44912,7 @@
         <v>1093</v>
       </c>
       <c r="C458" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D458" s="67" t="s">
         <v>1403</v>
@@ -44132,7 +44989,7 @@
         <v>1094</v>
       </c>
       <c r="C459" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D459" s="67" t="s">
         <v>1403</v>
@@ -44209,7 +45066,7 @@
         <v>1095</v>
       </c>
       <c r="C460" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D460" s="67" t="s">
         <v>1403</v>
@@ -44286,7 +45143,7 @@
         <v>1096</v>
       </c>
       <c r="C461" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D461" s="67" t="s">
         <v>1403</v>
@@ -44363,7 +45220,7 @@
         <v>1097</v>
       </c>
       <c r="C462" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D462" s="67" t="s">
         <v>1403</v>
@@ -44440,7 +45297,7 @@
         <v>1098</v>
       </c>
       <c r="C463" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D463" s="67" t="s">
         <v>1403</v>
@@ -44517,7 +45374,7 @@
         <v>1099</v>
       </c>
       <c r="C464" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D464" s="67" t="s">
         <v>1403</v>
@@ -44594,7 +45451,7 @@
         <v>1100</v>
       </c>
       <c r="C465" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D465" s="67" t="s">
         <v>1403</v>
@@ -44671,7 +45528,7 @@
         <v>1101</v>
       </c>
       <c r="C466" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D466" s="67" t="s">
         <v>1403</v>
@@ -44748,7 +45605,7 @@
         <v>1102</v>
       </c>
       <c r="C467" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D467" s="67" t="s">
         <v>1403</v>
@@ -44825,7 +45682,7 @@
         <v>1103</v>
       </c>
       <c r="C468" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D468" s="67" t="s">
         <v>1403</v>
@@ -44902,7 +45759,7 @@
         <v>1104</v>
       </c>
       <c r="C469" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D469" s="67" t="s">
         <v>1403</v>
@@ -44979,7 +45836,7 @@
         <v>1105</v>
       </c>
       <c r="C470" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D470" s="67" t="s">
         <v>1403</v>
@@ -45056,7 +45913,7 @@
         <v>1106</v>
       </c>
       <c r="C471" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D471" s="67" t="s">
         <v>1403</v>
@@ -45133,7 +45990,7 @@
         <v>1107</v>
       </c>
       <c r="C472" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D472" s="67" t="s">
         <v>1403</v>
@@ -45210,7 +46067,7 @@
         <v>1108</v>
       </c>
       <c r="C473" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D473" s="67" t="s">
         <v>1403</v>
@@ -45287,7 +46144,7 @@
         <v>1109</v>
       </c>
       <c r="C474" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D474" s="67" t="s">
         <v>1403</v>
@@ -45364,7 +46221,7 @@
         <v>1325</v>
       </c>
       <c r="C475" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D475" s="67" t="s">
         <v>1403</v>
@@ -45441,7 +46298,7 @@
         <v>1326</v>
       </c>
       <c r="C476" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D476" s="67" t="s">
         <v>1403</v>
@@ -45518,7 +46375,7 @@
         <v>1327</v>
       </c>
       <c r="C477" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D477" s="67" t="s">
         <v>1403</v>
@@ -45595,7 +46452,7 @@
         <v>1328</v>
       </c>
       <c r="C478" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D478" s="67" t="s">
         <v>1403</v>
@@ -45672,7 +46529,7 @@
         <v>1110</v>
       </c>
       <c r="C479" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D479" s="67" t="s">
         <v>1403</v>
@@ -45749,7 +46606,7 @@
         <v>1111</v>
       </c>
       <c r="C480" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D480" s="67" t="s">
         <v>1403</v>
@@ -45826,7 +46683,7 @@
         <v>1112</v>
       </c>
       <c r="C481" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D481" s="67" t="s">
         <v>1403</v>
@@ -45903,7 +46760,7 @@
         <v>1113</v>
       </c>
       <c r="C482" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D482" s="67" t="s">
         <v>1403</v>
@@ -45980,7 +46837,7 @@
         <v>1114</v>
       </c>
       <c r="C483" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D483" s="67" t="s">
         <v>1403</v>
@@ -46057,7 +46914,7 @@
         <v>1115</v>
       </c>
       <c r="C484" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D484" s="67" t="s">
         <v>1403</v>
@@ -46134,7 +46991,7 @@
         <v>1116</v>
       </c>
       <c r="C485" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D485" s="67" t="s">
         <v>1403</v>
@@ -46211,7 +47068,7 @@
         <v>1117</v>
       </c>
       <c r="C486" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D486" s="67" t="s">
         <v>1403</v>
@@ -46288,7 +47145,7 @@
         <v>1118</v>
       </c>
       <c r="C487" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D487" s="67" t="s">
         <v>1403</v>
@@ -46365,7 +47222,7 @@
         <v>1119</v>
       </c>
       <c r="C488" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D488" s="67" t="s">
         <v>1403</v>
@@ -46442,7 +47299,7 @@
         <v>1120</v>
       </c>
       <c r="C489" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D489" s="67" t="s">
         <v>1403</v>
@@ -46519,7 +47376,7 @@
         <v>1121</v>
       </c>
       <c r="C490" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D490" s="67" t="s">
         <v>1403</v>
@@ -46596,7 +47453,7 @@
         <v>1122</v>
       </c>
       <c r="C491" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D491" s="67" t="s">
         <v>1403</v>
@@ -46673,7 +47530,7 @@
         <v>1123</v>
       </c>
       <c r="C492" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D492" s="67" t="s">
         <v>1403</v>
@@ -46750,7 +47607,7 @@
         <v>1124</v>
       </c>
       <c r="C493" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D493" s="67" t="s">
         <v>1403</v>
@@ -46827,7 +47684,7 @@
         <v>1125</v>
       </c>
       <c r="C494" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D494" s="67" t="s">
         <v>1403</v>
@@ -46904,7 +47761,7 @@
         <v>1126</v>
       </c>
       <c r="C495" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D495" s="67" t="s">
         <v>1403</v>
@@ -46981,7 +47838,7 @@
         <v>1127</v>
       </c>
       <c r="C496" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D496" s="67" t="s">
         <v>1403</v>
@@ -47058,7 +47915,7 @@
         <v>1128</v>
       </c>
       <c r="C497" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D497" s="67" t="s">
         <v>1403</v>
@@ -47135,7 +47992,7 @@
         <v>1129</v>
       </c>
       <c r="C498" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D498" s="67" t="s">
         <v>1403</v>
@@ -47212,7 +48069,7 @@
         <v>1130</v>
       </c>
       <c r="C499" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D499" s="67" t="s">
         <v>1403</v>
@@ -47289,7 +48146,7 @@
         <v>1131</v>
       </c>
       <c r="C500" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D500" s="67" t="s">
         <v>1403</v>
@@ -47366,7 +48223,7 @@
         <v>1132</v>
       </c>
       <c r="C501" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D501" s="67" t="s">
         <v>1403</v>
@@ -47443,7 +48300,7 @@
         <v>1133</v>
       </c>
       <c r="C502" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D502" s="67" t="s">
         <v>1403</v>
@@ -47520,7 +48377,7 @@
         <v>1134</v>
       </c>
       <c r="C503" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D503" s="67" t="s">
         <v>1403</v>
@@ -47597,7 +48454,7 @@
         <v>1135</v>
       </c>
       <c r="C504" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D504" s="67" t="s">
         <v>1403</v>
@@ -47674,7 +48531,7 @@
         <v>1136</v>
       </c>
       <c r="C505" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D505" s="67" t="s">
         <v>1403</v>
@@ -47751,7 +48608,7 @@
         <v>1329</v>
       </c>
       <c r="C506" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D506" s="67" t="s">
         <v>1403</v>
@@ -47828,7 +48685,7 @@
         <v>1137</v>
       </c>
       <c r="C507" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D507" s="67" t="s">
         <v>1403</v>
@@ -47905,7 +48762,7 @@
         <v>1138</v>
       </c>
       <c r="C508" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D508" s="67" t="s">
         <v>1403</v>
@@ -47982,7 +48839,7 @@
         <v>1139</v>
       </c>
       <c r="C509" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D509" s="67" t="s">
         <v>1403</v>
@@ -48059,7 +48916,7 @@
         <v>1140</v>
       </c>
       <c r="C510" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D510" s="67" t="s">
         <v>1403</v>
@@ -48136,7 +48993,7 @@
         <v>1141</v>
       </c>
       <c r="C511" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D511" s="67" t="s">
         <v>1403</v>
@@ -48213,7 +49070,7 @@
         <v>1142</v>
       </c>
       <c r="C512" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D512" s="67" t="s">
         <v>1403</v>
@@ -48290,7 +49147,7 @@
         <v>1143</v>
       </c>
       <c r="C513" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D513" s="67" t="s">
         <v>1403</v>
@@ -48367,7 +49224,7 @@
         <v>1144</v>
       </c>
       <c r="C514" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D514" s="67" t="s">
         <v>1403</v>
@@ -48444,7 +49301,7 @@
         <v>1145</v>
       </c>
       <c r="C515" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D515" s="67" t="s">
         <v>1403</v>
@@ -48521,7 +49378,7 @@
         <v>1146</v>
       </c>
       <c r="C516" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D516" s="67" t="s">
         <v>1403</v>
@@ -48598,7 +49455,7 @@
         <v>1147</v>
       </c>
       <c r="C517" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D517" s="67" t="s">
         <v>1403</v>
@@ -48675,7 +49532,7 @@
         <v>1148</v>
       </c>
       <c r="C518" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D518" s="67" t="s">
         <v>1403</v>
@@ -48752,7 +49609,7 @@
         <v>1149</v>
       </c>
       <c r="C519" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D519" s="67" t="s">
         <v>1403</v>
@@ -48829,7 +49686,7 @@
         <v>1150</v>
       </c>
       <c r="C520" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D520" s="67" t="s">
         <v>1403</v>
@@ -48906,7 +49763,7 @@
         <v>1151</v>
       </c>
       <c r="C521" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D521" s="67" t="s">
         <v>1403</v>
@@ -48983,7 +49840,7 @@
         <v>1152</v>
       </c>
       <c r="C522" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D522" s="67" t="s">
         <v>1403</v>
@@ -49060,7 +49917,7 @@
         <v>1153</v>
       </c>
       <c r="C523" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D523" s="67" t="s">
         <v>1403</v>
@@ -49137,7 +49994,7 @@
         <v>1154</v>
       </c>
       <c r="C524" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D524" s="67" t="s">
         <v>1403</v>
@@ -49214,7 +50071,7 @@
         <v>1155</v>
       </c>
       <c r="C525" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D525" s="67" t="s">
         <v>1403</v>
@@ -49291,7 +50148,7 @@
         <v>1156</v>
       </c>
       <c r="C526" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D526" s="67" t="s">
         <v>1403</v>
@@ -49368,7 +50225,7 @@
         <v>1157</v>
       </c>
       <c r="C527" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D527" s="67" t="s">
         <v>1403</v>
@@ -49445,7 +50302,7 @@
         <v>1158</v>
       </c>
       <c r="C528" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D528" s="67" t="s">
         <v>1403</v>
@@ -49522,7 +50379,7 @@
         <v>1159</v>
       </c>
       <c r="C529" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D529" s="67" t="s">
         <v>1403</v>
@@ -49599,7 +50456,7 @@
         <v>1160</v>
       </c>
       <c r="C530" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D530" s="67" t="s">
         <v>1403</v>
@@ -49676,7 +50533,7 @@
         <v>1161</v>
       </c>
       <c r="C531" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D531" s="67" t="s">
         <v>1403</v>
@@ -49753,7 +50610,7 @@
         <v>1162</v>
       </c>
       <c r="C532" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D532" s="67" t="s">
         <v>1403</v>
@@ -49830,7 +50687,7 @@
         <v>1163</v>
       </c>
       <c r="C533" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D533" s="67" t="s">
         <v>1403</v>
@@ -49907,7 +50764,7 @@
         <v>1164</v>
       </c>
       <c r="C534" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D534" s="67" t="s">
         <v>1403</v>
@@ -49984,7 +50841,7 @@
         <v>1165</v>
       </c>
       <c r="C535" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D535" s="67" t="s">
         <v>1403</v>
@@ -50061,7 +50918,7 @@
         <v>1166</v>
       </c>
       <c r="C536" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D536" s="67" t="s">
         <v>1403</v>
@@ -50138,7 +50995,7 @@
         <v>1167</v>
       </c>
       <c r="C537" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D537" s="67" t="s">
         <v>1403</v>
@@ -50215,7 +51072,7 @@
         <v>1168</v>
       </c>
       <c r="C538" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D538" s="67" t="s">
         <v>1403</v>
@@ -50292,7 +51149,7 @@
         <v>1169</v>
       </c>
       <c r="C539" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D539" s="67" t="s">
         <v>1403</v>
@@ -50369,7 +51226,7 @@
         <v>1170</v>
       </c>
       <c r="C540" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D540" s="67" t="s">
         <v>1403</v>
@@ -50446,7 +51303,7 @@
         <v>1171</v>
       </c>
       <c r="C541" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D541" s="67" t="s">
         <v>1403</v>
@@ -50523,7 +51380,7 @@
         <v>1172</v>
       </c>
       <c r="C542" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D542" s="67" t="s">
         <v>1403</v>
@@ -50600,7 +51457,7 @@
         <v>1173</v>
       </c>
       <c r="C543" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D543" s="67" t="s">
         <v>1403</v>
@@ -50677,7 +51534,7 @@
         <v>1174</v>
       </c>
       <c r="C544" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D544" s="67" t="s">
         <v>1403</v>
@@ -50754,7 +51611,7 @@
         <v>1175</v>
       </c>
       <c r="C545" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D545" s="67" t="s">
         <v>1403</v>
@@ -50831,7 +51688,7 @@
         <v>1176</v>
       </c>
       <c r="C546" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D546" s="67" t="s">
         <v>1403</v>
@@ -50908,7 +51765,7 @@
         <v>1177</v>
       </c>
       <c r="C547" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D547" s="67" t="s">
         <v>1403</v>
@@ -50985,7 +51842,7 @@
         <v>1178</v>
       </c>
       <c r="C548" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D548" s="67" t="s">
         <v>1403</v>
@@ -51062,7 +51919,7 @@
         <v>1179</v>
       </c>
       <c r="C549" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D549" s="67" t="s">
         <v>1403</v>
@@ -51139,7 +51996,7 @@
         <v>1180</v>
       </c>
       <c r="C550" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D550" s="67" t="s">
         <v>1403</v>
@@ -51216,7 +52073,7 @@
         <v>1181</v>
       </c>
       <c r="C551" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D551" s="67" t="s">
         <v>1403</v>
@@ -51293,7 +52150,7 @@
         <v>1182</v>
       </c>
       <c r="C552" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D552" s="67" t="s">
         <v>1403</v>
@@ -51370,7 +52227,7 @@
         <v>1183</v>
       </c>
       <c r="C553" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D553" s="67" t="s">
         <v>1403</v>
@@ -51447,7 +52304,7 @@
         <v>1184</v>
       </c>
       <c r="C554" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D554" s="67" t="s">
         <v>1403</v>
@@ -51524,7 +52381,7 @@
         <v>1185</v>
       </c>
       <c r="C555" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D555" s="67" t="s">
         <v>1403</v>
@@ -51601,7 +52458,7 @@
         <v>1186</v>
       </c>
       <c r="C556" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D556" s="67" t="s">
         <v>1403</v>
@@ -51678,7 +52535,7 @@
         <v>1187</v>
       </c>
       <c r="C557" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D557" s="67" t="s">
         <v>1403</v>
@@ -51755,7 +52612,7 @@
         <v>1188</v>
       </c>
       <c r="C558" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D558" s="67" t="s">
         <v>1403</v>
@@ -51832,7 +52689,7 @@
         <v>1189</v>
       </c>
       <c r="C559" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D559" s="67" t="s">
         <v>1403</v>
@@ -51909,7 +52766,7 @@
         <v>1190</v>
       </c>
       <c r="C560" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D560" s="67" t="s">
         <v>1403</v>
@@ -51986,7 +52843,7 @@
         <v>1191</v>
       </c>
       <c r="C561" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D561" s="67" t="s">
         <v>1403</v>
@@ -52063,7 +52920,7 @@
         <v>1192</v>
       </c>
       <c r="C562" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D562" s="67" t="s">
         <v>1403</v>
@@ -52140,7 +52997,7 @@
         <v>1193</v>
       </c>
       <c r="C563" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D563" s="67" t="s">
         <v>1403</v>
@@ -52217,7 +53074,7 @@
         <v>1194</v>
       </c>
       <c r="C564" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D564" s="67" t="s">
         <v>1403</v>
@@ -52294,7 +53151,7 @@
         <v>1195</v>
       </c>
       <c r="C565" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D565" s="67" t="s">
         <v>1403</v>
@@ -52371,7 +53228,7 @@
         <v>1196</v>
       </c>
       <c r="C566" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D566" s="67" t="s">
         <v>1403</v>
@@ -52448,7 +53305,7 @@
         <v>1197</v>
       </c>
       <c r="C567" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D567" s="67" t="s">
         <v>1403</v>
@@ -52525,7 +53382,7 @@
         <v>1198</v>
       </c>
       <c r="C568" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D568" s="67" t="s">
         <v>1403</v>
@@ -52602,7 +53459,7 @@
         <v>1199</v>
       </c>
       <c r="C569" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D569" s="67" t="s">
         <v>1403</v>
@@ -52679,7 +53536,7 @@
         <v>1200</v>
       </c>
       <c r="C570" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D570" s="67" t="s">
         <v>1403</v>
@@ -52756,7 +53613,7 @@
         <v>1201</v>
       </c>
       <c r="C571" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D571" s="67" t="s">
         <v>1403</v>
@@ -52833,7 +53690,7 @@
         <v>1202</v>
       </c>
       <c r="C572" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D572" s="67" t="s">
         <v>1403</v>
@@ -52910,7 +53767,7 @@
         <v>1203</v>
       </c>
       <c r="C573" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D573" s="67" t="s">
         <v>1403</v>
@@ -52987,7 +53844,7 @@
         <v>1204</v>
       </c>
       <c r="C574" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D574" s="67" t="s">
         <v>1403</v>
@@ -53064,7 +53921,7 @@
         <v>1205</v>
       </c>
       <c r="C575" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D575" s="67" t="s">
         <v>1403</v>
@@ -53141,7 +53998,7 @@
         <v>1206</v>
       </c>
       <c r="C576" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D576" s="67" t="s">
         <v>1403</v>
@@ -53218,7 +54075,7 @@
         <v>1207</v>
       </c>
       <c r="C577" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D577" s="67" t="s">
         <v>1403</v>
@@ -53295,7 +54152,7 @@
         <v>1208</v>
       </c>
       <c r="C578" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D578" s="67" t="s">
         <v>1403</v>
@@ -53372,7 +54229,7 @@
         <v>1209</v>
       </c>
       <c r="C579" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D579" s="67" t="s">
         <v>1403</v>
@@ -53449,7 +54306,7 @@
         <v>1210</v>
       </c>
       <c r="C580" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D580" s="67" t="s">
         <v>1403</v>
@@ -53526,7 +54383,7 @@
         <v>1211</v>
       </c>
       <c r="C581" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D581" s="67" t="s">
         <v>1403</v>
@@ -53603,7 +54460,7 @@
         <v>1212</v>
       </c>
       <c r="C582" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D582" s="67" t="s">
         <v>1403</v>
@@ -53680,7 +54537,7 @@
         <v>1213</v>
       </c>
       <c r="C583" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D583" s="67" t="s">
         <v>1403</v>
@@ -53757,7 +54614,7 @@
         <v>1214</v>
       </c>
       <c r="C584" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D584" s="67" t="s">
         <v>1403</v>
@@ -53834,7 +54691,7 @@
         <v>1215</v>
       </c>
       <c r="C585" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D585" s="67" t="s">
         <v>1403</v>
@@ -53911,7 +54768,7 @@
         <v>1216</v>
       </c>
       <c r="C586" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D586" s="67" t="s">
         <v>1403</v>
@@ -53988,7 +54845,7 @@
         <v>1217</v>
       </c>
       <c r="C587" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D587" s="67" t="s">
         <v>1403</v>
@@ -54065,7 +54922,7 @@
         <v>1218</v>
       </c>
       <c r="C588" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D588" s="67" t="s">
         <v>1403</v>
@@ -54142,7 +54999,7 @@
         <v>1219</v>
       </c>
       <c r="C589" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D589" s="67" t="s">
         <v>1403</v>
@@ -54219,7 +55076,7 @@
         <v>1220</v>
       </c>
       <c r="C590" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D590" s="67" t="s">
         <v>1403</v>
@@ -54296,7 +55153,7 @@
         <v>1221</v>
       </c>
       <c r="C591" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D591" s="67" t="s">
         <v>1403</v>
@@ -54373,7 +55230,7 @@
         <v>1222</v>
       </c>
       <c r="C592" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D592" s="67" t="s">
         <v>1403</v>
@@ -54450,7 +55307,7 @@
         <v>1223</v>
       </c>
       <c r="C593" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D593" s="67" t="s">
         <v>1403</v>
@@ -54527,7 +55384,7 @@
         <v>1224</v>
       </c>
       <c r="C594" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D594" s="67" t="s">
         <v>1403</v>
@@ -54604,7 +55461,7 @@
         <v>1225</v>
       </c>
       <c r="C595" s="27" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="D595" s="67" t="s">
         <v>1403</v>
@@ -54681,7 +55538,7 @@
         <v>1226</v>
       </c>
       <c r="C596" s="27" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="D596" s="67" t="s">
         <v>1403</v>
@@ -54758,7 +55615,7 @@
         <v>1227</v>
       </c>
       <c r="C597" s="27" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="D597" s="67" t="s">
         <v>1403</v>
@@ -54835,7 +55692,7 @@
         <v>1228</v>
       </c>
       <c r="C598" s="27" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="D598" s="67" t="s">
         <v>1403</v>
@@ -54912,7 +55769,7 @@
         <v>1229</v>
       </c>
       <c r="C599" s="27" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="D599" s="67" t="s">
         <v>1403</v>
@@ -54989,7 +55846,7 @@
         <v>1230</v>
       </c>
       <c r="C600" s="27" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="D600" s="67" t="s">
         <v>1403</v>
@@ -55066,7 +55923,7 @@
         <v>1231</v>
       </c>
       <c r="C601" s="27" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="D601" s="67" t="s">
         <v>1403</v>
@@ -55143,7 +56000,7 @@
         <v>1232</v>
       </c>
       <c r="C602" s="27" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="D602" s="67" t="s">
         <v>1403</v>
@@ -55220,7 +56077,7 @@
         <v>1233</v>
       </c>
       <c r="C603" s="27" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="D603" s="67" t="s">
         <v>1403</v>
@@ -55297,7 +56154,7 @@
         <v>1234</v>
       </c>
       <c r="C604" s="27" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="D604" s="67" t="s">
         <v>1403</v>
@@ -55374,7 +56231,7 @@
         <v>1235</v>
       </c>
       <c r="C605" s="27" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="D605" s="67" t="s">
         <v>1403</v>
@@ -55451,7 +56308,7 @@
         <v>1236</v>
       </c>
       <c r="C606" s="27" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="D606" s="67" t="s">
         <v>1403</v>
@@ -55528,7 +56385,7 @@
         <v>1237</v>
       </c>
       <c r="C607" s="27" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="D607" s="67" t="s">
         <v>1403</v>
@@ -55605,7 +56462,7 @@
         <v>1238</v>
       </c>
       <c r="C608" s="27" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="D608" s="67" t="s">
         <v>1403</v>
@@ -55682,7 +56539,7 @@
         <v>1239</v>
       </c>
       <c r="C609" s="27" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="D609" s="67" t="s">
         <v>1403</v>
@@ -55759,7 +56616,7 @@
         <v>1240</v>
       </c>
       <c r="C610" s="27" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="D610" s="67" t="s">
         <v>1403</v>
@@ -55831,15 +56688,15 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:S4">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_2Q.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_2Q.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="EstaPastaDeTrabalho"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9B2E3E-D5F5-4253-8ECA-CB592AD61095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -5171,14 +5171,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -5234,6 +5226,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46167.463621759256</v>
+        <v>46214.346854976851</v>
       </c>
       <c r="C18" s="43" t="s">
         <v>1309</v>
@@ -9480,18 +9480,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A39">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1:AA39">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56688,15 +56688,15 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:S4">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_2Q.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_2Q.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E0C7D9-C1A3-4FC8-9242-6E82F3C83454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496DD330-599F-47EF-AFC6-D688C3E012DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15425" uniqueCount="1491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15425" uniqueCount="1490">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -4546,9 +4546,6 @@
   </si>
   <si>
     <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
-  </si>
-  <si>
-    <t>Arquitetura</t>
   </si>
   <si>
     <t>[ 5I ]</t>
@@ -5116,63 +5113,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{FD276809-E4C5-4861-8007-253055573830}"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="9">
     <dxf>
       <font>
         <b val="0"/>
@@ -5794,7 +5735,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46216.266689699078</v>
+        <v>46219.569664120369</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>1308</v>
@@ -5899,7 +5840,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1778FB64-75F3-4573-A6F2-8AC25FEAA02B}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA39"/>
-  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.33203125" style="33" customWidth="1"/>
@@ -6002,7 +5943,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="33" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" s="33" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="55">
         <v>2</v>
       </c>
@@ -6074,7 +6015,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V2" s="37" t="s">
-        <v>1485</v>
+        <v>1332</v>
       </c>
       <c r="W2" s="65" t="str">
         <f>CONCATENATE("Key-ABNT-",A2)</f>
@@ -6087,14 +6028,14 @@
         <v>638</v>
       </c>
       <c r="Z2" s="37" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="AA2" s="37" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="33" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" s="33" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="55">
         <v>3</v>
       </c>
@@ -6145,7 +6086,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="37" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="Q3" s="37" t="s">
         <v>1484</v>
@@ -6166,7 +6107,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V3" s="37" t="s">
-        <v>1485</v>
+        <v>1332</v>
       </c>
       <c r="W3" s="65" t="str">
         <f t="shared" ref="W3:W39" si="4">CONCATENATE("Key-ABNT-",A3)</f>
@@ -6186,7 +6127,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="33" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" s="33" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="55">
         <v>4</v>
       </c>
@@ -6237,7 +6178,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="Q4" s="37" t="s">
         <v>1484</v>
@@ -6258,7 +6199,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V4" s="37" t="s">
-        <v>1485</v>
+        <v>1332</v>
       </c>
       <c r="W4" s="65" t="str">
         <f t="shared" si="4"/>
@@ -6278,7 +6219,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="33" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" s="33" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="55">
         <v>5</v>
       </c>
@@ -6329,7 +6270,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="37" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="Q5" s="37" t="s">
         <v>1484</v>
@@ -6350,7 +6291,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V5" s="37" t="s">
-        <v>1485</v>
+        <v>1332</v>
       </c>
       <c r="W5" s="65" t="str">
         <f t="shared" si="4"/>
@@ -6370,7 +6311,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="33" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" s="33" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="55">
         <v>6</v>
       </c>
@@ -6421,7 +6362,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="37" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="Q6" s="37" t="s">
         <v>1484</v>
@@ -6442,7 +6383,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V6" s="37" t="s">
-        <v>1485</v>
+        <v>1332</v>
       </c>
       <c r="W6" s="65" t="str">
         <f t="shared" si="4"/>
@@ -6462,7 +6403,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="55">
         <v>7</v>
       </c>
@@ -6553,7 +6494,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="55">
         <v>8</v>
       </c>
@@ -6644,7 +6585,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="55">
         <v>9</v>
       </c>
@@ -6735,7 +6676,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="55">
         <v>10</v>
       </c>
@@ -6826,7 +6767,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="55">
         <v>11</v>
       </c>
@@ -6917,7 +6858,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="55">
         <v>12</v>
       </c>
@@ -7008,7 +6949,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="55">
         <v>13</v>
       </c>
@@ -7099,7 +7040,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="55">
         <v>14</v>
       </c>
@@ -7190,7 +7131,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="55">
         <v>15</v>
       </c>
@@ -7281,7 +7222,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="55">
         <v>16</v>
       </c>
@@ -7372,7 +7313,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="55">
         <v>17</v>
       </c>
@@ -7463,7 +7404,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="55">
         <v>18</v>
       </c>
@@ -7554,7 +7495,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="55">
         <v>19</v>
       </c>
@@ -7645,7 +7586,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="55">
         <v>20</v>
       </c>
@@ -7738,7 +7679,7 @@
         <v>Design, Graphic, and IT Hardware Tools</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="55">
         <v>21</v>
       </c>
@@ -7831,7 +7772,7 @@
         <v>IT Network Tools</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="55">
         <v>22</v>
       </c>
@@ -7924,7 +7865,7 @@
         <v>Software tools for design, graphics or management</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="55">
         <v>23</v>
       </c>
@@ -8017,7 +7958,7 @@
         <v>Measurement Tools</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="55">
         <v>24</v>
       </c>
@@ -8110,7 +8051,7 @@
         <v>Monitoring Tools</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="55">
         <v>25</v>
       </c>
@@ -8203,7 +8144,7 @@
         <v>Testing Tools</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="55">
         <v>26</v>
       </c>
@@ -8296,7 +8237,7 @@
         <v>Construction Tools</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="55">
         <v>27</v>
       </c>
@@ -8389,7 +8330,7 @@
         <v>Finishing Tools</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="55">
         <v>28</v>
       </c>
@@ -8482,7 +8423,7 @@
         <v>Transportation Tools</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="55">
         <v>29</v>
       </c>
@@ -8575,7 +8516,7 @@
         <v>Power Tools</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="55">
         <v>30</v>
       </c>
@@ -8668,7 +8609,7 @@
         <v>Control Tools</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="55">
         <v>31</v>
       </c>
@@ -8761,7 +8702,7 @@
         <v>PPE Personal Protective Tools</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="55">
         <v>32</v>
       </c>
@@ -8854,7 +8795,7 @@
         <v>General Construction Tools</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="55">
         <v>33</v>
       </c>
@@ -8947,7 +8888,7 @@
         <v>Construction Site Tools</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="55">
         <v>34</v>
       </c>
@@ -9040,7 +8981,7 @@
         <v>Support Tools</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="55">
         <v>35</v>
       </c>
@@ -9133,7 +9074,7 @@
         <v>Pumping and Tunneling Equipment</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="55">
         <v>36</v>
       </c>
@@ -9226,7 +9167,7 @@
         <v>Concrete Production Equipment</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="55">
         <v>37</v>
       </c>
@@ -9319,7 +9260,7 @@
         <v>Drilling &amp; Cutting Equipment</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="55">
         <v>38</v>
       </c>
@@ -9412,7 +9353,7 @@
         <v>Equipment for Demolition and Earthmoving</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="55">
         <v>39</v>
       </c>
@@ -9506,29 +9447,19 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A7:A39">
-    <cfRule type="cellIs" dxfId="14" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1 AA7:AA39">
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
+  <conditionalFormatting sqref="A2:B39">
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B6 B7:B39">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+  <conditionalFormatting sqref="AA1:AA39">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56725,15 +56656,15 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:S4">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_2Q.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_2Q.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE41D53C-605C-4956-99B1-4031B841BCD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA41B68E-48AF-4F43-8CF6-1DA468F2D821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15425" uniqueCount="1496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15464" uniqueCount="1522">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -4579,13 +4579,91 @@
   </si>
   <si>
     <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 5I. Building Information Codes.</t>
+  </si>
+  <si>
+    <t>Fonte1</t>
+  </si>
+  <si>
+    <t>https://brasil.un.org/pt-br/sdgs</t>
+  </si>
+  <si>
+    <t>Fonte2</t>
+  </si>
+  <si>
+    <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
+  </si>
+  <si>
+    <t>Fonte3</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
+  </si>
+  <si>
+    <t>FonteVegetação1</t>
+  </si>
+  <si>
+    <t>https://museunacional.ufrj.br/hortobotanico</t>
+  </si>
+  <si>
+    <t>FonteVegetação2</t>
+  </si>
+  <si>
+    <t>https://www.embrapa.br/florestas/publicacoes</t>
+  </si>
+  <si>
+    <t>FonteVegetação3</t>
+  </si>
+  <si>
+    <t>https://www.arvoresgigantes.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação4</t>
+  </si>
+  <si>
+    <t>https://www.scielo.br/j/abb</t>
+  </si>
+  <si>
+    <t>FonteVegetação5</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
+  </si>
+  <si>
+    <t>FonteVegetação6</t>
+  </si>
+  <si>
+    <t>https://botanicasaopaulo.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação7</t>
+  </si>
+  <si>
+    <t>https://pesquisa.in.gov.br/imprensa</t>
+  </si>
+  <si>
+    <t>FonteVegetação8</t>
+  </si>
+  <si>
+    <t>https://mapas.florestal.gov.br</t>
+  </si>
+  <si>
+    <t>FonteTSB</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
+  </si>
+  <si>
+    <t>FonteSINAPI</t>
+  </si>
+  <si>
+    <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <color theme="1"/>
@@ -4673,8 +4751,34 @@
       <name val="Arial Nova Cond Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color theme="10"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial Nova Cond"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="6"/>
+      <color theme="10"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="30">
+  <fills count="31">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4849,6 +4953,12 @@
         <bgColor rgb="FFD9E2F3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -4924,11 +5034,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5126,38 +5237,31 @@
     <xf numFmtId="0" fontId="3" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="17" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{FD276809-E4C5-4861-8007-253055573830}"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <font>
         <b val="0"/>
@@ -5191,6 +5295,16 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -5576,7 +5690,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{436D4E89-FEA8-43EC-BA63-D5F572124283}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.796875" bestFit="1" customWidth="1"/>
@@ -5779,7 +5893,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46232.78212048611</v>
+        <v>46233.479419328702</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>1307</v>
@@ -5875,7 +5989,157 @@
         <v>1306</v>
       </c>
     </row>
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="38" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B27" s="67" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="38" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B28" s="68" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="38" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B29" s="68" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="38" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B30" s="69" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="38" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B31" s="69" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C31" s="41" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="38" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B32" s="69" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="38" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B33" s="71" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C33" s="41" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="38" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B34" s="71" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C34" s="41" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="38" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B35" s="69" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C35" s="41" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="38" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B36" s="71" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C36" s="41" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="38" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B37" s="69" t="s">
+        <v>1517</v>
+      </c>
+      <c r="C37" s="41" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B38" s="72" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C38" s="41" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="74" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="38" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B39" s="73" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C39" s="41" t="s">
+        <v>1307</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{B6F4AEAB-55CA-40E0-B5C6-B20EC404D0B7}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{53738B0B-65A9-4EA1-9AD4-B1DCB1D00003}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{5845C205-D424-4BF4-AEDF-CCFC9680767A}"/>
+    <hyperlink ref="B38" r:id="rId4" xr:uid="{AE5E9BFF-18E1-40F9-AB9E-F741BE395C88}"/>
+    <hyperlink ref="B39" r:id="rId5" location="categoria_888" xr:uid="{BE447770-F1A7-4173-A0EC-32BD4D2E6A1E}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -7665,7 +7929,7 @@
         <v>638</v>
       </c>
       <c r="L20" s="58" t="str">
-        <f t="shared" ref="L18:N20" si="8">CONCATENATE("", C20)</f>
+        <f t="shared" ref="L20:N20" si="8">CONCATENATE("", C20)</f>
         <v>Normativo</v>
       </c>
       <c r="M20" s="58" t="str">
@@ -7677,7 +7941,7 @@
         <v>NBR.Equipamentos</v>
       </c>
       <c r="O20" s="58" t="str">
-        <f t="shared" ref="O7:O20" si="9">F20</f>
+        <f t="shared" ref="O20" si="9">F20</f>
         <v>NBR.Q.Ferramenta.Hardware</v>
       </c>
       <c r="P20" s="58" t="s">
@@ -7691,7 +7955,7 @@
         <v>638</v>
       </c>
       <c r="S20" s="59" t="str">
-        <f t="shared" ref="S7:U20" si="10">SUBSTITUTE(C20, "_", " ")</f>
+        <f t="shared" ref="S20:U20" si="10">SUBSTITUTE(C20, "_", " ")</f>
         <v>Normativo</v>
       </c>
       <c r="T20" s="59" t="str">
@@ -9491,32 +9755,22 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B6 A20:B39">
-    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
+  <conditionalFormatting sqref="A2:B39">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA6 AA20:AA39">
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7:B19">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F19">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA19">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+  <conditionalFormatting sqref="AA1:AA39">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56713,15 +56967,15 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:S4">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_2Q.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_2Q.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA41B68E-48AF-4F43-8CF6-1DA468F2D821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF98D073-4B9E-4FB7-BF05-81EDA2F1AEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15464" uniqueCount="1522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15464" uniqueCount="1521">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -4428,9 +4428,6 @@
     <t>[ 2Q.06.06 ]</t>
   </si>
   <si>
-    <t>Conceito</t>
-  </si>
-  <si>
     <t>Contêineres</t>
   </si>
   <si>
@@ -4455,21 +4452,12 @@
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
   </si>
   <si>
-    <t>Normativo</t>
-  </si>
-  <si>
-    <t>NBR.Temática</t>
-  </si>
-  <si>
     <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 0M. Códigos de Materiais.</t>
   </si>
   <si>
     <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 0M. Códigos de materiales.</t>
   </si>
   <si>
-    <t>Interdiciplinar</t>
-  </si>
-  <si>
     <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 0M. Material Codes.</t>
   </si>
   <si>
@@ -4657,6 +4645,15 @@
   </si>
   <si>
     <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
+  </si>
+  <si>
+    <t>Conceitos</t>
+  </si>
+  <si>
+    <t>Normativos</t>
+  </si>
+  <si>
+    <t>NBR.Temáticas</t>
   </si>
 </sst>
 </file>
@@ -5893,7 +5890,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46233.479419328702</v>
+        <v>46243.559799074072</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>1307</v>
@@ -5991,10 +5988,10 @@
     </row>
     <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="38" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="B27" s="67" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
       <c r="C27" s="41" t="s">
         <v>1307</v>
@@ -6002,10 +5999,10 @@
     </row>
     <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="38" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
       <c r="B28" s="68" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="C28" s="41" t="s">
         <v>1307</v>
@@ -6013,10 +6010,10 @@
     </row>
     <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="38" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="B29" s="68" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="C29" s="41" t="s">
         <v>1307</v>
@@ -6024,10 +6021,10 @@
     </row>
     <row r="30" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="38" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
       <c r="B30" s="69" t="s">
-        <v>1503</v>
+        <v>1499</v>
       </c>
       <c r="C30" s="41" t="s">
         <v>1307</v>
@@ -6035,10 +6032,10 @@
     </row>
     <row r="31" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="38" t="s">
-        <v>1504</v>
+        <v>1500</v>
       </c>
       <c r="B31" s="69" t="s">
-        <v>1505</v>
+        <v>1501</v>
       </c>
       <c r="C31" s="41" t="s">
         <v>1307</v>
@@ -6046,10 +6043,10 @@
     </row>
     <row r="32" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="38" t="s">
-        <v>1506</v>
+        <v>1502</v>
       </c>
       <c r="B32" s="69" t="s">
-        <v>1507</v>
+        <v>1503</v>
       </c>
       <c r="C32" s="41" t="s">
         <v>1307</v>
@@ -6057,10 +6054,10 @@
     </row>
     <row r="33" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="38" t="s">
-        <v>1508</v>
+        <v>1504</v>
       </c>
       <c r="B33" s="71" t="s">
-        <v>1509</v>
+        <v>1505</v>
       </c>
       <c r="C33" s="41" t="s">
         <v>1307</v>
@@ -6068,10 +6065,10 @@
     </row>
     <row r="34" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="38" t="s">
-        <v>1510</v>
+        <v>1506</v>
       </c>
       <c r="B34" s="71" t="s">
-        <v>1511</v>
+        <v>1507</v>
       </c>
       <c r="C34" s="41" t="s">
         <v>1307</v>
@@ -6079,10 +6076,10 @@
     </row>
     <row r="35" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="38" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="B35" s="69" t="s">
-        <v>1513</v>
+        <v>1509</v>
       </c>
       <c r="C35" s="41" t="s">
         <v>1307</v>
@@ -6090,10 +6087,10 @@
     </row>
     <row r="36" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="38" t="s">
-        <v>1514</v>
+        <v>1510</v>
       </c>
       <c r="B36" s="71" t="s">
-        <v>1515</v>
+        <v>1511</v>
       </c>
       <c r="C36" s="41" t="s">
         <v>1307</v>
@@ -6101,10 +6098,10 @@
     </row>
     <row r="37" spans="1:3" s="70" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="38" t="s">
-        <v>1516</v>
+        <v>1512</v>
       </c>
       <c r="B37" s="69" t="s">
-        <v>1517</v>
+        <v>1513</v>
       </c>
       <c r="C37" s="41" t="s">
         <v>1307</v>
@@ -6112,10 +6109,10 @@
     </row>
     <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>1518</v>
+        <v>1514</v>
       </c>
       <c r="B38" s="72" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="C38" s="41" t="s">
         <v>1307</v>
@@ -6123,10 +6120,10 @@
     </row>
     <row r="39" spans="1:3" s="74" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="38" t="s">
-        <v>1520</v>
+        <v>1516</v>
       </c>
       <c r="B39" s="73" t="s">
-        <v>1521</v>
+        <v>1517</v>
       </c>
       <c r="C39" s="41" t="s">
         <v>1307</v>
@@ -6148,14 +6145,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1778FB64-75F3-4573-A6F2-8AC25FEAA02B}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA39"/>
-  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="7.3" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.296875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="3.19921875" customWidth="1"/>
+    <col min="2" max="2" width="7" style="33" customWidth="1"/>
     <col min="3" max="3" width="7.796875" style="33" customWidth="1"/>
-    <col min="4" max="4" width="8.5" style="33"/>
+    <col min="4" max="4" width="9.796875" style="33" customWidth="1"/>
     <col min="5" max="5" width="11.69921875" style="33" customWidth="1"/>
-    <col min="6" max="6" width="20.69921875" style="33" customWidth="1"/>
+    <col min="6" max="6" width="20.3984375" style="33" bestFit="1" customWidth="1"/>
     <col min="7" max="11" width="8.5" style="33"/>
     <col min="14" max="14" width="10.5" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="21" customWidth="1"/>
@@ -6251,12 +6248,12 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="33" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" s="33" customFormat="1" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="55">
         <v>2</v>
       </c>
       <c r="B2" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C2" s="56" t="s">
         <v>1328</v>
@@ -6265,7 +6262,7 @@
         <v>1330</v>
       </c>
       <c r="E2" s="57" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="F2" s="57" t="s">
         <v>1329</v>
@@ -6302,10 +6299,10 @@
         <v>Contêiner</v>
       </c>
       <c r="P2" s="37" t="s">
+        <v>1446</v>
+      </c>
+      <c r="Q2" s="37" t="s">
         <v>1447</v>
-      </c>
-      <c r="Q2" s="37" t="s">
-        <v>1448</v>
       </c>
       <c r="R2" s="37" t="s">
         <v>638</v>
@@ -6336,19 +6333,19 @@
         <v>638</v>
       </c>
       <c r="Z2" s="37" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="AA2" s="37" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="33" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" s="33" customFormat="1" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="55">
         <v>3</v>
       </c>
       <c r="B3" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C3" s="56" t="s">
         <v>1328</v>
@@ -6357,7 +6354,7 @@
         <v>1330</v>
       </c>
       <c r="E3" s="57" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="F3" s="57" t="s">
         <v>1332</v>
@@ -6394,10 +6391,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="37" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="Q3" s="37" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="R3" s="37" t="s">
         <v>638</v>
@@ -6435,12 +6432,12 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="33" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" s="33" customFormat="1" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="55">
         <v>4</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C4" s="56" t="s">
         <v>1328</v>
@@ -6449,7 +6446,7 @@
         <v>1330</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="F4" s="57" t="s">
         <v>1333</v>
@@ -6486,10 +6483,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="Q4" s="37" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="R4" s="37" t="s">
         <v>638</v>
@@ -6527,12 +6524,12 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="33" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" s="33" customFormat="1" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="55">
         <v>5</v>
       </c>
       <c r="B5" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C5" s="56" t="s">
         <v>1328</v>
@@ -6541,7 +6538,7 @@
         <v>1330</v>
       </c>
       <c r="E5" s="57" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="F5" s="57" t="s">
         <v>1334</v>
@@ -6578,10 +6575,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="37" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="Q5" s="37" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="R5" s="37" t="s">
         <v>638</v>
@@ -6619,12 +6616,12 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="33" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" s="33" customFormat="1" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="55">
         <v>6</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C6" s="56" t="s">
         <v>1328</v>
@@ -6633,7 +6630,7 @@
         <v>1330</v>
       </c>
       <c r="E6" s="57" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="F6" s="57" t="s">
         <v>1335</v>
@@ -6670,10 +6667,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="37" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="Q6" s="37" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="R6" s="37" t="s">
         <v>638</v>
@@ -6711,15 +6708,15 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="55">
         <v>7</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D7" s="31" t="s">
         <v>1274</v>
@@ -6747,7 +6744,7 @@
       </c>
       <c r="L7" s="58" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M7" s="58" t="str">
         <f t="shared" si="0"/>
@@ -6762,17 +6759,17 @@
         <v>NBR.0M</v>
       </c>
       <c r="P7" s="58" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
       <c r="Q7" s="58" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
       <c r="R7" s="37" t="s">
         <v>638</v>
       </c>
       <c r="S7" s="59" t="str">
         <f t="shared" ref="S7:U19" si="6">SUBSTITUTE(C7, "_", " ")</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T7" s="59" t="str">
         <f t="shared" si="6"/>
@@ -6783,7 +6780,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V7" s="37" t="s">
-        <v>1458</v>
+        <v>1331</v>
       </c>
       <c r="W7" s="65" t="str">
         <f t="shared" si="4"/>
@@ -6799,18 +6796,18 @@
         <v>1336</v>
       </c>
       <c r="AA7" s="60" t="s">
-        <v>1459</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="55">
         <v>8</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D8" s="31" t="s">
         <v>1274</v>
@@ -6838,7 +6835,7 @@
       </c>
       <c r="L8" s="58" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M8" s="58" t="str">
         <f t="shared" si="0"/>
@@ -6853,17 +6850,17 @@
         <v>NBR.0P</v>
       </c>
       <c r="P8" s="58" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="Q8" s="58" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
       <c r="R8" s="37" t="s">
         <v>638</v>
       </c>
       <c r="S8" s="59" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T8" s="59" t="str">
         <f t="shared" si="6"/>
@@ -6874,7 +6871,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V8" s="37" t="s">
-        <v>1458</v>
+        <v>1331</v>
       </c>
       <c r="W8" s="65" t="str">
         <f t="shared" si="4"/>
@@ -6890,18 +6887,18 @@
         <v>1337</v>
       </c>
       <c r="AA8" s="60" t="s">
-        <v>1462</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="55">
         <v>9</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D9" s="31" t="s">
         <v>1274</v>
@@ -6929,7 +6926,7 @@
       </c>
       <c r="L9" s="58" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M9" s="58" t="str">
         <f t="shared" si="0"/>
@@ -6944,17 +6941,17 @@
         <v>NBR.1D</v>
       </c>
       <c r="P9" s="58" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
       <c r="Q9" s="58" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="R9" s="37" t="s">
         <v>638</v>
       </c>
       <c r="S9" s="59" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T9" s="59" t="str">
         <f t="shared" si="6"/>
@@ -6965,7 +6962,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V9" s="37" t="s">
-        <v>1458</v>
+        <v>1331</v>
       </c>
       <c r="W9" s="65" t="str">
         <f t="shared" si="4"/>
@@ -6981,18 +6978,18 @@
         <v>1338</v>
       </c>
       <c r="AA9" s="60" t="s">
-        <v>1465</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="55">
         <v>10</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D10" s="31" t="s">
         <v>1274</v>
@@ -7020,7 +7017,7 @@
       </c>
       <c r="L10" s="58" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M10" s="58" t="str">
         <f t="shared" si="0"/>
@@ -7035,17 +7032,17 @@
         <v>NBR.1F</v>
       </c>
       <c r="P10" s="58" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
       <c r="Q10" s="58" t="s">
-        <v>1467</v>
+        <v>1463</v>
       </c>
       <c r="R10" s="37" t="s">
         <v>638</v>
       </c>
       <c r="S10" s="59" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T10" s="59" t="str">
         <f t="shared" si="6"/>
@@ -7056,7 +7053,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V10" s="37" t="s">
-        <v>1458</v>
+        <v>1331</v>
       </c>
       <c r="W10" s="65" t="str">
         <f t="shared" si="4"/>
@@ -7072,18 +7069,18 @@
         <v>1339</v>
       </c>
       <c r="AA10" s="60" t="s">
-        <v>1468</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="55">
         <v>11</v>
       </c>
       <c r="B11" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D11" s="31" t="s">
         <v>1274</v>
@@ -7111,7 +7108,7 @@
       </c>
       <c r="L11" s="58" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M11" s="58" t="str">
         <f t="shared" si="0"/>
@@ -7126,17 +7123,17 @@
         <v>NBR.1S</v>
       </c>
       <c r="P11" s="58" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
       <c r="Q11" s="58" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
       <c r="R11" s="37" t="s">
         <v>638</v>
       </c>
       <c r="S11" s="59" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T11" s="59" t="str">
         <f t="shared" si="6"/>
@@ -7147,7 +7144,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V11" s="37" t="s">
-        <v>1458</v>
+        <v>1331</v>
       </c>
       <c r="W11" s="65" t="str">
         <f t="shared" si="4"/>
@@ -7163,18 +7160,18 @@
         <v>1340</v>
       </c>
       <c r="AA11" s="60" t="s">
-        <v>1471</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="55">
         <v>12</v>
       </c>
       <c r="B12" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D12" s="31" t="s">
         <v>1274</v>
@@ -7202,7 +7199,7 @@
       </c>
       <c r="L12" s="58" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M12" s="58" t="str">
         <f t="shared" si="0"/>
@@ -7217,17 +7214,17 @@
         <v>NBR.2C</v>
       </c>
       <c r="P12" s="58" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
       <c r="Q12" s="58" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
       <c r="R12" s="37" t="s">
         <v>638</v>
       </c>
       <c r="S12" s="59" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T12" s="59" t="str">
         <f t="shared" si="6"/>
@@ -7238,7 +7235,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V12" s="37" t="s">
-        <v>1458</v>
+        <v>1331</v>
       </c>
       <c r="W12" s="65" t="str">
         <f t="shared" si="4"/>
@@ -7254,18 +7251,18 @@
         <v>1341</v>
       </c>
       <c r="AA12" s="60" t="s">
-        <v>1474</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="55">
         <v>13</v>
       </c>
       <c r="B13" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D13" s="31" t="s">
         <v>1274</v>
@@ -7293,7 +7290,7 @@
       </c>
       <c r="L13" s="58" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M13" s="58" t="str">
         <f t="shared" si="0"/>
@@ -7308,17 +7305,17 @@
         <v>NBR.2N</v>
       </c>
       <c r="P13" s="58" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
       <c r="Q13" s="58" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
       <c r="R13" s="37" t="s">
         <v>638</v>
       </c>
       <c r="S13" s="59" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T13" s="59" t="str">
         <f t="shared" si="6"/>
@@ -7329,7 +7326,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V13" s="37" t="s">
-        <v>1458</v>
+        <v>1331</v>
       </c>
       <c r="W13" s="65" t="str">
         <f t="shared" si="4"/>
@@ -7345,18 +7342,18 @@
         <v>1342</v>
       </c>
       <c r="AA13" s="60" t="s">
-        <v>1477</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="55">
         <v>14</v>
       </c>
       <c r="B14" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D14" s="31" t="s">
         <v>1274</v>
@@ -7384,7 +7381,7 @@
       </c>
       <c r="L14" s="58" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M14" s="58" t="str">
         <f t="shared" si="0"/>
@@ -7399,17 +7396,17 @@
         <v>NBR.2Q</v>
       </c>
       <c r="P14" s="58" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
       <c r="Q14" s="58" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
       <c r="R14" s="37" t="s">
         <v>638</v>
       </c>
       <c r="S14" s="59" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T14" s="59" t="str">
         <f t="shared" si="6"/>
@@ -7420,7 +7417,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V14" s="37" t="s">
-        <v>1458</v>
+        <v>1331</v>
       </c>
       <c r="W14" s="65" t="str">
         <f t="shared" si="4"/>
@@ -7436,18 +7433,18 @@
         <v>1243</v>
       </c>
       <c r="AA14" s="60" t="s">
-        <v>1480</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="55">
         <v>15</v>
       </c>
       <c r="B15" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D15" s="31" t="s">
         <v>1274</v>
@@ -7475,7 +7472,7 @@
       </c>
       <c r="L15" s="58" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M15" s="58" t="str">
         <f t="shared" si="0"/>
@@ -7490,17 +7487,17 @@
         <v>NBR.3E</v>
       </c>
       <c r="P15" s="58" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
       <c r="Q15" s="58" t="s">
-        <v>1482</v>
+        <v>1478</v>
       </c>
       <c r="R15" s="37" t="s">
         <v>638</v>
       </c>
       <c r="S15" s="59" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T15" s="59" t="str">
         <f t="shared" si="6"/>
@@ -7511,7 +7508,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V15" s="37" t="s">
-        <v>1458</v>
+        <v>1331</v>
       </c>
       <c r="W15" s="65" t="str">
         <f t="shared" si="4"/>
@@ -7527,18 +7524,18 @@
         <v>1343</v>
       </c>
       <c r="AA15" s="60" t="s">
-        <v>1483</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="55">
         <v>16</v>
       </c>
       <c r="B16" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D16" s="31" t="s">
         <v>1274</v>
@@ -7566,7 +7563,7 @@
       </c>
       <c r="L16" s="58" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M16" s="58" t="str">
         <f t="shared" si="0"/>
@@ -7581,17 +7578,17 @@
         <v>NBR.3R</v>
       </c>
       <c r="P16" s="58" t="s">
-        <v>1484</v>
+        <v>1480</v>
       </c>
       <c r="Q16" s="58" t="s">
-        <v>1485</v>
+        <v>1481</v>
       </c>
       <c r="R16" s="37" t="s">
         <v>638</v>
       </c>
       <c r="S16" s="59" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T16" s="59" t="str">
         <f t="shared" si="6"/>
@@ -7602,7 +7599,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V16" s="37" t="s">
-        <v>1458</v>
+        <v>1331</v>
       </c>
       <c r="W16" s="65" t="str">
         <f t="shared" si="4"/>
@@ -7618,18 +7615,18 @@
         <v>1344</v>
       </c>
       <c r="AA16" s="60" t="s">
-        <v>1486</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="55">
         <v>17</v>
       </c>
       <c r="B17" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D17" s="31" t="s">
         <v>1274</v>
@@ -7657,7 +7654,7 @@
       </c>
       <c r="L17" s="58" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M17" s="58" t="str">
         <f t="shared" si="0"/>
@@ -7672,17 +7669,17 @@
         <v>NBR.4A</v>
       </c>
       <c r="P17" s="58" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
       <c r="Q17" s="58" t="s">
-        <v>1488</v>
+        <v>1484</v>
       </c>
       <c r="R17" s="37" t="s">
         <v>638</v>
       </c>
       <c r="S17" s="59" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T17" s="59" t="str">
         <f t="shared" si="6"/>
@@ -7693,7 +7690,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V17" s="37" t="s">
-        <v>1458</v>
+        <v>1331</v>
       </c>
       <c r="W17" s="65" t="str">
         <f t="shared" si="4"/>
@@ -7709,18 +7706,18 @@
         <v>1345</v>
       </c>
       <c r="AA17" s="60" t="s">
-        <v>1489</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="55">
         <v>18</v>
       </c>
       <c r="B18" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D18" s="31" t="s">
         <v>1274</v>
@@ -7748,7 +7745,7 @@
       </c>
       <c r="L18" s="58" t="str">
         <f t="shared" ref="L18:N19" si="7">CONCATENATE("", C18)</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M18" s="58" t="str">
         <f t="shared" si="7"/>
@@ -7763,17 +7760,17 @@
         <v>NBR.4U</v>
       </c>
       <c r="P18" s="58" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
       <c r="Q18" s="58" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
       <c r="R18" s="37" t="s">
         <v>638</v>
       </c>
       <c r="S18" s="59" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T18" s="59" t="str">
         <f t="shared" si="6"/>
@@ -7784,7 +7781,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V18" s="37" t="s">
-        <v>1458</v>
+        <v>1331</v>
       </c>
       <c r="W18" s="65" t="str">
         <f t="shared" si="4"/>
@@ -7800,18 +7797,18 @@
         <v>1346</v>
       </c>
       <c r="AA18" s="60" t="s">
-        <v>1492</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="55">
         <v>19</v>
       </c>
       <c r="B19" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D19" s="31" t="s">
         <v>1274</v>
@@ -7839,7 +7836,7 @@
       </c>
       <c r="L19" s="58" t="str">
         <f t="shared" si="7"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M19" s="58" t="str">
         <f t="shared" si="7"/>
@@ -7854,17 +7851,17 @@
         <v>NBR.5I</v>
       </c>
       <c r="P19" s="58" t="s">
-        <v>1493</v>
+        <v>1489</v>
       </c>
       <c r="Q19" s="58" t="s">
-        <v>1494</v>
+        <v>1490</v>
       </c>
       <c r="R19" s="37" t="s">
         <v>638</v>
       </c>
       <c r="S19" s="59" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T19" s="59" t="str">
         <f t="shared" si="6"/>
@@ -7875,7 +7872,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V19" s="37" t="s">
-        <v>1458</v>
+        <v>1331</v>
       </c>
       <c r="W19" s="65" t="str">
         <f t="shared" si="4"/>
@@ -7891,21 +7888,21 @@
         <v>1347</v>
       </c>
       <c r="AA19" s="60" t="s">
-        <v>1495</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="55">
         <v>20</v>
       </c>
       <c r="B20" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>1455</v>
+        <v>1520</v>
       </c>
       <c r="E20" s="31" t="s">
         <v>1437</v>
@@ -7930,11 +7927,11 @@
       </c>
       <c r="L20" s="58" t="str">
         <f t="shared" ref="L20:N20" si="8">CONCATENATE("", C20)</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M20" s="58" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N20" s="58" t="str">
         <f t="shared" si="8"/>
@@ -7956,11 +7953,11 @@
       </c>
       <c r="S20" s="59" t="str">
         <f t="shared" ref="S20:U20" si="10">SUBSTITUTE(C20, "_", " ")</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T20" s="59" t="str">
         <f t="shared" si="10"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U20" s="58" t="str">
         <f t="shared" si="10"/>
@@ -7987,18 +7984,18 @@
         <v>Design, Graphic, and IT Hardware Tools</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="55">
         <v>21</v>
       </c>
       <c r="B21" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>1455</v>
+        <v>1520</v>
       </c>
       <c r="E21" s="31" t="s">
         <v>1437</v>
@@ -8023,11 +8020,11 @@
       </c>
       <c r="L21" s="58" t="str">
         <f t="shared" ref="L21:L31" si="11">CONCATENATE("", C21)</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M21" s="58" t="str">
         <f t="shared" ref="M21:M31" si="12">CONCATENATE("", D21)</f>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N21" s="58" t="str">
         <f t="shared" ref="N21:N31" si="13">CONCATENATE("", E21)</f>
@@ -8049,11 +8046,11 @@
       </c>
       <c r="S21" s="59" t="str">
         <f t="shared" ref="S21" si="15">SUBSTITUTE(C21, "_", " ")</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T21" s="59" t="str">
         <f t="shared" ref="T21" si="16">SUBSTITUTE(D21, "_", " ")</f>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U21" s="58" t="str">
         <f t="shared" ref="U21" si="17">SUBSTITUTE(E21, "_", " ")</f>
@@ -8080,18 +8077,18 @@
         <v>IT Network Tools</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="55">
         <v>22</v>
       </c>
       <c r="B22" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>1455</v>
+        <v>1520</v>
       </c>
       <c r="E22" s="31" t="s">
         <v>1437</v>
@@ -8116,11 +8113,11 @@
       </c>
       <c r="L22" s="58" t="str">
         <f t="shared" si="11"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M22" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N22" s="58" t="str">
         <f t="shared" si="13"/>
@@ -8142,11 +8139,11 @@
       </c>
       <c r="S22" s="59" t="str">
         <f t="shared" ref="S22:S31" si="19">SUBSTITUTE(C22, "_", " ")</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T22" s="59" t="str">
         <f t="shared" ref="T22:T31" si="20">SUBSTITUTE(D22, "_", " ")</f>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U22" s="58" t="str">
         <f t="shared" ref="U22:U31" si="21">SUBSTITUTE(E22, "_", " ")</f>
@@ -8173,18 +8170,18 @@
         <v>Software tools for design, graphics or management</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="55">
         <v>23</v>
       </c>
       <c r="B23" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>1455</v>
+        <v>1520</v>
       </c>
       <c r="E23" s="31" t="s">
         <v>1437</v>
@@ -8209,11 +8206,11 @@
       </c>
       <c r="L23" s="58" t="str">
         <f t="shared" si="11"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M23" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N23" s="58" t="str">
         <f t="shared" si="13"/>
@@ -8235,11 +8232,11 @@
       </c>
       <c r="S23" s="59" t="str">
         <f t="shared" si="19"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T23" s="59" t="str">
         <f t="shared" si="20"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U23" s="58" t="str">
         <f t="shared" si="21"/>
@@ -8266,18 +8263,18 @@
         <v>Measurement Tools</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="55">
         <v>24</v>
       </c>
       <c r="B24" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>1455</v>
+        <v>1520</v>
       </c>
       <c r="E24" s="31" t="s">
         <v>1437</v>
@@ -8302,11 +8299,11 @@
       </c>
       <c r="L24" s="58" t="str">
         <f t="shared" si="11"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M24" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N24" s="58" t="str">
         <f t="shared" si="13"/>
@@ -8328,11 +8325,11 @@
       </c>
       <c r="S24" s="59" t="str">
         <f t="shared" si="19"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T24" s="59" t="str">
         <f t="shared" si="20"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U24" s="58" t="str">
         <f t="shared" si="21"/>
@@ -8359,18 +8356,18 @@
         <v>Monitoring Tools</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="55">
         <v>25</v>
       </c>
       <c r="B25" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C25" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>1455</v>
+        <v>1520</v>
       </c>
       <c r="E25" s="31" t="s">
         <v>1437</v>
@@ -8395,11 +8392,11 @@
       </c>
       <c r="L25" s="58" t="str">
         <f t="shared" si="11"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M25" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N25" s="58" t="str">
         <f t="shared" si="13"/>
@@ -8421,11 +8418,11 @@
       </c>
       <c r="S25" s="59" t="str">
         <f t="shared" si="19"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T25" s="59" t="str">
         <f t="shared" si="20"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U25" s="58" t="str">
         <f t="shared" si="21"/>
@@ -8452,18 +8449,18 @@
         <v>Testing Tools</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="55">
         <v>26</v>
       </c>
       <c r="B26" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C26" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>1455</v>
+        <v>1520</v>
       </c>
       <c r="E26" s="31" t="s">
         <v>1437</v>
@@ -8488,11 +8485,11 @@
       </c>
       <c r="L26" s="58" t="str">
         <f t="shared" si="11"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M26" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N26" s="58" t="str">
         <f t="shared" si="13"/>
@@ -8514,11 +8511,11 @@
       </c>
       <c r="S26" s="59" t="str">
         <f t="shared" si="19"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T26" s="59" t="str">
         <f t="shared" si="20"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U26" s="58" t="str">
         <f t="shared" si="21"/>
@@ -8545,18 +8542,18 @@
         <v>Construction Tools</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="55">
         <v>27</v>
       </c>
       <c r="B27" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>1455</v>
+        <v>1520</v>
       </c>
       <c r="E27" s="31" t="s">
         <v>1437</v>
@@ -8581,11 +8578,11 @@
       </c>
       <c r="L27" s="58" t="str">
         <f t="shared" si="11"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M27" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N27" s="58" t="str">
         <f t="shared" si="13"/>
@@ -8607,11 +8604,11 @@
       </c>
       <c r="S27" s="59" t="str">
         <f t="shared" si="19"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T27" s="59" t="str">
         <f t="shared" si="20"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U27" s="58" t="str">
         <f t="shared" si="21"/>
@@ -8638,18 +8635,18 @@
         <v>Finishing Tools</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="55">
         <v>28</v>
       </c>
       <c r="B28" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>1455</v>
+        <v>1520</v>
       </c>
       <c r="E28" s="31" t="s">
         <v>1437</v>
@@ -8674,11 +8671,11 @@
       </c>
       <c r="L28" s="58" t="str">
         <f t="shared" si="11"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M28" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N28" s="58" t="str">
         <f t="shared" si="13"/>
@@ -8700,11 +8697,11 @@
       </c>
       <c r="S28" s="59" t="str">
         <f t="shared" si="19"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T28" s="59" t="str">
         <f t="shared" si="20"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U28" s="58" t="str">
         <f t="shared" si="21"/>
@@ -8731,18 +8728,18 @@
         <v>Transportation Tools</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="55">
         <v>29</v>
       </c>
       <c r="B29" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C29" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>1455</v>
+        <v>1520</v>
       </c>
       <c r="E29" s="31" t="s">
         <v>1437</v>
@@ -8767,11 +8764,11 @@
       </c>
       <c r="L29" s="58" t="str">
         <f t="shared" si="11"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M29" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N29" s="58" t="str">
         <f t="shared" si="13"/>
@@ -8793,11 +8790,11 @@
       </c>
       <c r="S29" s="59" t="str">
         <f t="shared" si="19"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T29" s="59" t="str">
         <f t="shared" si="20"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U29" s="58" t="str">
         <f t="shared" si="21"/>
@@ -8824,18 +8821,18 @@
         <v>Power Tools</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="55">
         <v>30</v>
       </c>
       <c r="B30" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C30" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>1455</v>
+        <v>1520</v>
       </c>
       <c r="E30" s="31" t="s">
         <v>1437</v>
@@ -8860,11 +8857,11 @@
       </c>
       <c r="L30" s="58" t="str">
         <f t="shared" si="11"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M30" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N30" s="58" t="str">
         <f t="shared" si="13"/>
@@ -8886,11 +8883,11 @@
       </c>
       <c r="S30" s="59" t="str">
         <f t="shared" si="19"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T30" s="59" t="str">
         <f t="shared" si="20"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U30" s="58" t="str">
         <f t="shared" si="21"/>
@@ -8917,18 +8914,18 @@
         <v>Control Tools</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="55">
         <v>31</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>1455</v>
+        <v>1520</v>
       </c>
       <c r="E31" s="31" t="s">
         <v>1437</v>
@@ -8953,11 +8950,11 @@
       </c>
       <c r="L31" s="58" t="str">
         <f t="shared" si="11"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M31" s="58" t="str">
         <f t="shared" si="12"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N31" s="58" t="str">
         <f t="shared" si="13"/>
@@ -8979,11 +8976,11 @@
       </c>
       <c r="S31" s="59" t="str">
         <f t="shared" si="19"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T31" s="59" t="str">
         <f t="shared" si="20"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U31" s="58" t="str">
         <f t="shared" si="21"/>
@@ -9010,18 +9007,18 @@
         <v>PPE Personal Protective Tools</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="55">
         <v>32</v>
       </c>
       <c r="B32" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D32" s="31" t="s">
-        <v>1455</v>
+        <v>1520</v>
       </c>
       <c r="E32" s="31" t="s">
         <v>1437</v>
@@ -9046,11 +9043,11 @@
       </c>
       <c r="L32" s="58" t="str">
         <f t="shared" ref="L32:L39" si="23">CONCATENATE("", C32)</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M32" s="58" t="str">
         <f t="shared" ref="M32:M39" si="24">CONCATENATE("", D32)</f>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N32" s="58" t="str">
         <f t="shared" ref="N32:N39" si="25">CONCATENATE("", E32)</f>
@@ -9072,11 +9069,11 @@
       </c>
       <c r="S32" s="59" t="str">
         <f t="shared" ref="S32:S39" si="28">SUBSTITUTE(C32, "_", " ")</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T32" s="59" t="str">
         <f t="shared" ref="T32:T39" si="29">SUBSTITUTE(D32, "_", " ")</f>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U32" s="58" t="str">
         <f t="shared" ref="U32:U39" si="30">SUBSTITUTE(E32, "_", " ")</f>
@@ -9103,18 +9100,18 @@
         <v>General Construction Tools</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="55">
         <v>33</v>
       </c>
       <c r="B33" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D33" s="31" t="s">
-        <v>1455</v>
+        <v>1520</v>
       </c>
       <c r="E33" s="31" t="s">
         <v>1437</v>
@@ -9139,11 +9136,11 @@
       </c>
       <c r="L33" s="58" t="str">
         <f t="shared" si="23"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M33" s="58" t="str">
         <f t="shared" si="24"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N33" s="58" t="str">
         <f t="shared" si="25"/>
@@ -9165,11 +9162,11 @@
       </c>
       <c r="S33" s="59" t="str">
         <f t="shared" si="28"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T33" s="59" t="str">
         <f t="shared" si="29"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U33" s="58" t="str">
         <f t="shared" si="30"/>
@@ -9196,18 +9193,18 @@
         <v>Construction Site Tools</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="55">
         <v>34</v>
       </c>
       <c r="B34" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C34" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D34" s="31" t="s">
-        <v>1455</v>
+        <v>1520</v>
       </c>
       <c r="E34" s="31" t="s">
         <v>1437</v>
@@ -9232,11 +9229,11 @@
       </c>
       <c r="L34" s="58" t="str">
         <f t="shared" si="23"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M34" s="58" t="str">
         <f t="shared" si="24"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N34" s="58" t="str">
         <f t="shared" si="25"/>
@@ -9258,11 +9255,11 @@
       </c>
       <c r="S34" s="59" t="str">
         <f t="shared" si="28"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T34" s="59" t="str">
         <f t="shared" si="29"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U34" s="58" t="str">
         <f t="shared" si="30"/>
@@ -9289,18 +9286,18 @@
         <v>Support Tools</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="55">
         <v>35</v>
       </c>
       <c r="B35" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D35" s="31" t="s">
-        <v>1455</v>
+        <v>1520</v>
       </c>
       <c r="E35" s="31" t="s">
         <v>1437</v>
@@ -9325,11 +9322,11 @@
       </c>
       <c r="L35" s="58" t="str">
         <f t="shared" si="23"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M35" s="58" t="str">
         <f t="shared" si="24"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N35" s="58" t="str">
         <f t="shared" si="25"/>
@@ -9351,11 +9348,11 @@
       </c>
       <c r="S35" s="59" t="str">
         <f t="shared" si="28"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T35" s="59" t="str">
         <f t="shared" si="29"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U35" s="58" t="str">
         <f t="shared" si="30"/>
@@ -9382,18 +9379,18 @@
         <v>Pumping and Tunneling Equipment</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="55">
         <v>36</v>
       </c>
       <c r="B36" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C36" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D36" s="31" t="s">
-        <v>1455</v>
+        <v>1520</v>
       </c>
       <c r="E36" s="31" t="s">
         <v>1437</v>
@@ -9418,11 +9415,11 @@
       </c>
       <c r="L36" s="58" t="str">
         <f t="shared" si="23"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M36" s="58" t="str">
         <f t="shared" si="24"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N36" s="58" t="str">
         <f t="shared" si="25"/>
@@ -9444,11 +9441,11 @@
       </c>
       <c r="S36" s="59" t="str">
         <f t="shared" si="28"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T36" s="59" t="str">
         <f t="shared" si="29"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U36" s="58" t="str">
         <f t="shared" si="30"/>
@@ -9475,18 +9472,18 @@
         <v>Concrete Production Equipment</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="55">
         <v>37</v>
       </c>
       <c r="B37" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C37" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D37" s="31" t="s">
-        <v>1455</v>
+        <v>1520</v>
       </c>
       <c r="E37" s="31" t="s">
         <v>1437</v>
@@ -9511,11 +9508,11 @@
       </c>
       <c r="L37" s="58" t="str">
         <f t="shared" si="23"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M37" s="58" t="str">
         <f t="shared" si="24"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N37" s="58" t="str">
         <f t="shared" si="25"/>
@@ -9537,11 +9534,11 @@
       </c>
       <c r="S37" s="59" t="str">
         <f t="shared" si="28"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T37" s="59" t="str">
         <f t="shared" si="29"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U37" s="58" t="str">
         <f t="shared" si="30"/>
@@ -9568,18 +9565,18 @@
         <v>Drilling &amp; Cutting Equipment</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="55">
         <v>38</v>
       </c>
       <c r="B38" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D38" s="31" t="s">
-        <v>1455</v>
+        <v>1520</v>
       </c>
       <c r="E38" s="31" t="s">
         <v>1437</v>
@@ -9604,11 +9601,11 @@
       </c>
       <c r="L38" s="58" t="str">
         <f t="shared" si="23"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M38" s="58" t="str">
         <f t="shared" si="24"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N38" s="58" t="str">
         <f t="shared" si="25"/>
@@ -9630,11 +9627,11 @@
       </c>
       <c r="S38" s="59" t="str">
         <f t="shared" si="28"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T38" s="59" t="str">
         <f t="shared" si="29"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U38" s="58" t="str">
         <f t="shared" si="30"/>
@@ -9661,18 +9658,18 @@
         <v>Equipment for Demolition and Earthmoving</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" ht="7.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="55">
         <v>39</v>
       </c>
       <c r="B39" s="56" t="s">
-        <v>1445</v>
+        <v>1518</v>
       </c>
       <c r="C39" s="31" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D39" s="31" t="s">
-        <v>1455</v>
+        <v>1520</v>
       </c>
       <c r="E39" s="31" t="s">
         <v>1437</v>
@@ -9697,11 +9694,11 @@
       </c>
       <c r="L39" s="58" t="str">
         <f t="shared" si="23"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M39" s="58" t="str">
         <f t="shared" si="24"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N39" s="58" t="str">
         <f t="shared" si="25"/>
@@ -9723,11 +9720,11 @@
       </c>
       <c r="S39" s="59" t="str">
         <f t="shared" si="28"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T39" s="59" t="str">
         <f t="shared" si="29"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U39" s="58" t="str">
         <f t="shared" si="30"/>
@@ -10079,7 +10076,7 @@
         <v>1246</v>
       </c>
       <c r="C2" s="45" t="s">
-        <v>1454</v>
+        <v>1519</v>
       </c>
       <c r="D2" s="62" t="s">
         <v>638</v>
